--- a/reports/series_reference.xlsx
+++ b/reports/series_reference.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="143">
   <si>
     <t xml:space="preserve">Theme</t>
   </si>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">Top 25 ranking by citizenship (annual)</t>
   </si>
   <si>
-    <t xml:space="preserve">Country of Citizenship, Country Rank</t>
+    <t xml:space="preserve">Country of Citizenship</t>
   </si>
   <si>
     <t xml:space="preserve">Canada - Asylum Claimants by Top 25 Countries of Citizenship (annual ranking), Province/Territory of Claim and Claim Month/Year</t>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">Top 25 ranking by citizenship (claim year)</t>
   </si>
   <si>
-    <t xml:space="preserve">Claim Office Type, Country of Citizenship, Country Rank</t>
+    <t xml:space="preserve">Claim Office Type, Country of Citizenship</t>
   </si>
   <si>
     <t xml:space="preserve">Canada - Asylum Claimants by Top 25 Countries of Citizenship, Claim Office Type and Claim Year</t>
@@ -140,16 +140,31 @@
     <t xml:space="preserve">International Mobility Program</t>
   </si>
   <si>
-    <t xml:space="preserve">All permits</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Country of Citizenship</t>
+    <t xml:space="preserve">All permits (at December 31)</t>
   </si>
   <si>
     <t xml:space="preserve">Canada – All International Mobility Program (IMP) work permit holders on December 31st by country of citizenship and year</t>
   </si>
   <si>
-    <t xml:space="preserve">All permits (at December 31)</t>
+    <t xml:space="preserve">All permits (Year became effective)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gender, Occupational Skill Level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - International Mobility Program work permit holders by gender, occupational skill level and year in which permit(s) became effective</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intended Occupation (4-Digit NOC 2011)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - International Mobility Program work permit holders by province/territory of intended destination, intended occupation (4-digit NOC 2011) and year in which permit(s) became effective</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Program</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - International Mobility Program work permit holders by province/territory of intended destination, program and year in which permit(s) became effective</t>
   </si>
   <si>
     <t xml:space="preserve">Program, Year in which Permit(s) Became Effective</t>
@@ -158,24 +173,6 @@
     <t xml:space="preserve">Canada - International Mobility Program work permit holders by province/territory, program and year in which permit(s) became effective</t>
   </si>
   <si>
-    <t xml:space="preserve">All permits (Year became effective)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gender, Occupational Skill Level</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canada - International Mobility Program work permit holders by gender, occupational skill level and year in which permit(s) became effective</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Intended Occupation (4-Digit NOC 2011)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canada - International Mobility Program work permit holders by province/territory of intended destination, intended occupation (4-digit NOC 2011) and year in which permit(s) became effective</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canada - International Mobility Program work permit holders by province/territory of intended destination, program and year in which permit(s) became effective</t>
-  </si>
-  <si>
     <t xml:space="preserve">Canada – International Mobility Program Work Permit Holders by Country of Citizenship and Year in which Permit(s) became effective</t>
   </si>
   <si>
@@ -194,21 +191,15 @@
     <t xml:space="preserve">Canada - Work permit holders for Humanitarian and Compassionate purposes by Province/Territory and year in which permit(s) became effective</t>
   </si>
   <si>
-    <t xml:space="preserve">Permits for work purposes only</t>
+    <t xml:space="preserve">Permits for work purposes only (at December 31)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - International Mobility Program work permit holders (work purpose only) on December 31st by province/territory and program</t>
   </si>
   <si>
     <t xml:space="preserve">Canada – International Mobility Program (IMP) work permit holders (for work purposes only) on December 31st by country of citizenship and year</t>
   </si>
   <si>
-    <t xml:space="preserve">Permits for work purposes only (at December 31)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Program</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canada - International Mobility Program work permit holders (work purpose only) on December 31st by province/territory and program</t>
-  </si>
-  <si>
     <t xml:space="preserve">Permits under post-grad employment</t>
   </si>
   <si>
@@ -332,6 +323,18 @@
     <t xml:space="preserve">Refugees</t>
   </si>
   <si>
+    <t xml:space="preserve">Outcome</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Refugee Protection Division (RPD) Decisions; Open Dataset Request 833195 ENG - RPD decisions from 1997-2021 by outcome and province of claimant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Province of Claimant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Dataset Request 833195 ENG - RPD decisions from 1997-2021 by outcome and province of claimant</t>
+  </si>
+  <si>
     <t xml:space="preserve">Refugee Protection Division RPD Decisions</t>
   </si>
   <si>
@@ -341,27 +344,12 @@
     <t xml:space="preserve">Refugee Protection Division (RPD) Decisions</t>
   </si>
   <si>
-    <t xml:space="preserve">Refugee Protection Division RPD Decisions 1997-2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Outcome</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Refugee Protection Division (RPD) Decisions; Open Dataset Request 833195 ENG - RPD decisions from 1997-2021 by outcome and province of claimant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPD decisions from 1997-2021 province of claimant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Outcome, Province of Residence at the Time of the Refugee Claim Decision</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Open Dataset Request 833195 ENG - RPD decisions from 1997-2021 by outcome and province of claimant</t>
-  </si>
-  <si>
     <t xml:space="preserve">Study Permit Holders</t>
   </si>
   <si>
+    <t xml:space="preserve">Canada - Study permit holders by province/territory of intended destination and census metropolitan area (CMA)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Study Level</t>
   </si>
   <si>
@@ -378,9 +366,6 @@
   </si>
   <si>
     <t xml:space="preserve">Canada - Study permit holders by country of citizenship and year in which permit(s) became effective</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canada - Study permit holders by province/territory of intended destination and census metropolitan area (CMA)</t>
   </si>
   <si>
     <t xml:space="preserve">Canada - Study permit holders by province/territory, gender and year in which permit(s) became effective</t>
@@ -503,8 +488,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:F346" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:F346"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:F353" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:F353"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Theme"/>
     <tableColumn id="2" name="Series"/>
@@ -1955,16 +1940,16 @@
         <v>42</v>
       </c>
       <c r="C58" t="s">
+        <v>23</v>
+      </c>
+      <c r="D58" t="s">
+        <v>9</v>
+      </c>
+      <c r="E58" t="s">
+        <v>10</v>
+      </c>
+      <c r="F58" t="s">
         <v>43</v>
-      </c>
-      <c r="D58" t="s">
-        <v>9</v>
-      </c>
-      <c r="E58" t="s">
-        <v>10</v>
-      </c>
-      <c r="F58" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="59">
@@ -1972,19 +1957,19 @@
         <v>41</v>
       </c>
       <c r="B59" t="s">
+        <v>44</v>
+      </c>
+      <c r="C59" t="s">
         <v>45</v>
       </c>
-      <c r="C59" t="s">
+      <c r="D59" t="s">
+        <v>9</v>
+      </c>
+      <c r="E59" t="s">
+        <v>10</v>
+      </c>
+      <c r="F59" t="s">
         <v>46</v>
-      </c>
-      <c r="D59" t="s">
-        <v>9</v>
-      </c>
-      <c r="E59" t="s">
-        <v>10</v>
-      </c>
-      <c r="F59" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="60">
@@ -1992,19 +1977,19 @@
         <v>41</v>
       </c>
       <c r="B60" t="s">
+        <v>44</v>
+      </c>
+      <c r="C60" t="s">
         <v>45</v>
       </c>
-      <c r="C60" t="s">
+      <c r="D60" t="s">
+        <v>9</v>
+      </c>
+      <c r="E60" t="s">
+        <v>12</v>
+      </c>
+      <c r="F60" t="s">
         <v>46</v>
-      </c>
-      <c r="D60" t="s">
-        <v>9</v>
-      </c>
-      <c r="E60" t="s">
-        <v>12</v>
-      </c>
-      <c r="F60" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="61">
@@ -2012,19 +1997,19 @@
         <v>41</v>
       </c>
       <c r="B61" t="s">
+        <v>44</v>
+      </c>
+      <c r="C61" t="s">
         <v>45</v>
       </c>
-      <c r="C61" t="s">
+      <c r="D61" t="s">
+        <v>9</v>
+      </c>
+      <c r="E61" t="s">
+        <v>13</v>
+      </c>
+      <c r="F61" t="s">
         <v>46</v>
-      </c>
-      <c r="D61" t="s">
-        <v>9</v>
-      </c>
-      <c r="E61" t="s">
-        <v>13</v>
-      </c>
-      <c r="F61" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="62">
@@ -2032,19 +2017,19 @@
         <v>41</v>
       </c>
       <c r="B62" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C62" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D62" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E62" t="s">
         <v>10</v>
       </c>
       <c r="F62" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="63">
@@ -2052,19 +2037,19 @@
         <v>41</v>
       </c>
       <c r="B63" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C63" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D63" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E63" t="s">
         <v>12</v>
       </c>
       <c r="F63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="64">
@@ -2072,19 +2057,19 @@
         <v>41</v>
       </c>
       <c r="B64" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C64" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D64" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E64" t="s">
         <v>13</v>
       </c>
       <c r="F64" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="65">
@@ -2092,19 +2077,19 @@
         <v>41</v>
       </c>
       <c r="B65" t="s">
+        <v>44</v>
+      </c>
+      <c r="C65" t="s">
+        <v>47</v>
+      </c>
+      <c r="D65" t="s">
+        <v>14</v>
+      </c>
+      <c r="E65" t="s">
+        <v>10</v>
+      </c>
+      <c r="F65" t="s">
         <v>48</v>
-      </c>
-      <c r="C65" t="s">
-        <v>49</v>
-      </c>
-      <c r="D65" t="s">
-        <v>9</v>
-      </c>
-      <c r="E65" t="s">
-        <v>10</v>
-      </c>
-      <c r="F65" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="66">
@@ -2112,19 +2097,19 @@
         <v>41</v>
       </c>
       <c r="B66" t="s">
+        <v>44</v>
+      </c>
+      <c r="C66" t="s">
+        <v>47</v>
+      </c>
+      <c r="D66" t="s">
+        <v>14</v>
+      </c>
+      <c r="E66" t="s">
+        <v>12</v>
+      </c>
+      <c r="F66" t="s">
         <v>48</v>
-      </c>
-      <c r="C66" t="s">
-        <v>49</v>
-      </c>
-      <c r="D66" t="s">
-        <v>9</v>
-      </c>
-      <c r="E66" t="s">
-        <v>12</v>
-      </c>
-      <c r="F66" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="67">
@@ -2132,19 +2117,19 @@
         <v>41</v>
       </c>
       <c r="B67" t="s">
+        <v>44</v>
+      </c>
+      <c r="C67" t="s">
+        <v>47</v>
+      </c>
+      <c r="D67" t="s">
+        <v>14</v>
+      </c>
+      <c r="E67" t="s">
+        <v>13</v>
+      </c>
+      <c r="F67" t="s">
         <v>48</v>
-      </c>
-      <c r="C67" t="s">
-        <v>49</v>
-      </c>
-      <c r="D67" t="s">
-        <v>9</v>
-      </c>
-      <c r="E67" t="s">
-        <v>13</v>
-      </c>
-      <c r="F67" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="68">
@@ -2152,10 +2137,10 @@
         <v>41</v>
       </c>
       <c r="B68" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C68" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D68" t="s">
         <v>9</v>
@@ -2164,7 +2149,7 @@
         <v>10</v>
       </c>
       <c r="F68" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="69">
@@ -2172,10 +2157,10 @@
         <v>41</v>
       </c>
       <c r="B69" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C69" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D69" t="s">
         <v>9</v>
@@ -2184,7 +2169,7 @@
         <v>12</v>
       </c>
       <c r="F69" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="70">
@@ -2192,10 +2177,10 @@
         <v>41</v>
       </c>
       <c r="B70" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C70" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D70" t="s">
         <v>9</v>
@@ -2204,7 +2189,7 @@
         <v>13</v>
       </c>
       <c r="F70" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="71">
@@ -2212,10 +2197,10 @@
         <v>41</v>
       </c>
       <c r="B71" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C71" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D71" t="s">
         <v>14</v>
@@ -2224,7 +2209,7 @@
         <v>10</v>
       </c>
       <c r="F71" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="72">
@@ -2232,10 +2217,10 @@
         <v>41</v>
       </c>
       <c r="B72" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C72" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D72" t="s">
         <v>14</v>
@@ -2244,7 +2229,7 @@
         <v>12</v>
       </c>
       <c r="F72" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="73">
@@ -2252,10 +2237,10 @@
         <v>41</v>
       </c>
       <c r="B73" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C73" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D73" t="s">
         <v>14</v>
@@ -2264,7 +2249,7 @@
         <v>13</v>
       </c>
       <c r="F73" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="74">
@@ -2272,10 +2257,10 @@
         <v>41</v>
       </c>
       <c r="B74" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C74" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="D74" t="s">
         <v>9</v>
@@ -2284,7 +2269,7 @@
         <v>10</v>
       </c>
       <c r="F74" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="75">
@@ -2292,10 +2277,10 @@
         <v>41</v>
       </c>
       <c r="B75" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C75" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="D75" t="s">
         <v>9</v>
@@ -2304,7 +2289,7 @@
         <v>12</v>
       </c>
       <c r="F75" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="76">
@@ -2312,10 +2297,10 @@
         <v>41</v>
       </c>
       <c r="B76" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C76" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="D76" t="s">
         <v>9</v>
@@ -2324,7 +2309,7 @@
         <v>13</v>
       </c>
       <c r="F76" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="77">
@@ -2332,10 +2317,10 @@
         <v>41</v>
       </c>
       <c r="B77" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C77" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="D77" t="s">
         <v>14</v>
@@ -2344,7 +2329,7 @@
         <v>10</v>
       </c>
       <c r="F77" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="78">
@@ -2352,10 +2337,10 @@
         <v>41</v>
       </c>
       <c r="B78" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C78" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="D78" t="s">
         <v>14</v>
@@ -2364,7 +2349,7 @@
         <v>12</v>
       </c>
       <c r="F78" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="79">
@@ -2372,10 +2357,10 @@
         <v>41</v>
       </c>
       <c r="B79" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C79" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="D79" t="s">
         <v>14</v>
@@ -2384,7 +2369,7 @@
         <v>13</v>
       </c>
       <c r="F79" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="80">
@@ -2392,10 +2377,10 @@
         <v>41</v>
       </c>
       <c r="B80" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C80" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D80" t="s">
         <v>9</v>
@@ -2404,7 +2389,7 @@
         <v>10</v>
       </c>
       <c r="F80" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="81">
@@ -2412,10 +2397,10 @@
         <v>41</v>
       </c>
       <c r="B81" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C81" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D81" t="s">
         <v>9</v>
@@ -2424,7 +2409,7 @@
         <v>12</v>
       </c>
       <c r="F81" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="82">
@@ -2432,10 +2417,10 @@
         <v>41</v>
       </c>
       <c r="B82" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C82" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D82" t="s">
         <v>9</v>
@@ -2444,7 +2429,7 @@
         <v>13</v>
       </c>
       <c r="F82" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="83">
@@ -2452,19 +2437,19 @@
         <v>41</v>
       </c>
       <c r="B83" t="s">
+        <v>54</v>
+      </c>
+      <c r="C83" t="s">
+        <v>23</v>
+      </c>
+      <c r="D83" t="s">
+        <v>9</v>
+      </c>
+      <c r="E83" t="s">
+        <v>10</v>
+      </c>
+      <c r="F83" t="s">
         <v>55</v>
-      </c>
-      <c r="C83" t="s">
-        <v>43</v>
-      </c>
-      <c r="D83" t="s">
-        <v>9</v>
-      </c>
-      <c r="E83" t="s">
-        <v>10</v>
-      </c>
-      <c r="F83" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="84">
@@ -2472,19 +2457,19 @@
         <v>41</v>
       </c>
       <c r="B84" t="s">
+        <v>54</v>
+      </c>
+      <c r="C84" t="s">
+        <v>23</v>
+      </c>
+      <c r="D84" t="s">
+        <v>9</v>
+      </c>
+      <c r="E84" t="s">
+        <v>12</v>
+      </c>
+      <c r="F84" t="s">
         <v>55</v>
-      </c>
-      <c r="C84" t="s">
-        <v>43</v>
-      </c>
-      <c r="D84" t="s">
-        <v>9</v>
-      </c>
-      <c r="E84" t="s">
-        <v>12</v>
-      </c>
-      <c r="F84" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="85">
@@ -2492,19 +2477,19 @@
         <v>41</v>
       </c>
       <c r="B85" t="s">
+        <v>54</v>
+      </c>
+      <c r="C85" t="s">
+        <v>23</v>
+      </c>
+      <c r="D85" t="s">
+        <v>9</v>
+      </c>
+      <c r="E85" t="s">
+        <v>13</v>
+      </c>
+      <c r="F85" t="s">
         <v>55</v>
-      </c>
-      <c r="C85" t="s">
-        <v>43</v>
-      </c>
-      <c r="D85" t="s">
-        <v>9</v>
-      </c>
-      <c r="E85" t="s">
-        <v>13</v>
-      </c>
-      <c r="F85" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="86">
@@ -2512,19 +2497,19 @@
         <v>41</v>
       </c>
       <c r="B86" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C86" t="s">
+        <v>56</v>
+      </c>
+      <c r="D86" t="s">
+        <v>9</v>
+      </c>
+      <c r="E86" t="s">
+        <v>10</v>
+      </c>
+      <c r="F86" t="s">
         <v>57</v>
-      </c>
-      <c r="D86" t="s">
-        <v>9</v>
-      </c>
-      <c r="E86" t="s">
-        <v>10</v>
-      </c>
-      <c r="F86" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="87">
@@ -2532,19 +2517,19 @@
         <v>41</v>
       </c>
       <c r="B87" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C87" t="s">
+        <v>56</v>
+      </c>
+      <c r="D87" t="s">
+        <v>9</v>
+      </c>
+      <c r="E87" t="s">
+        <v>12</v>
+      </c>
+      <c r="F87" t="s">
         <v>57</v>
-      </c>
-      <c r="D87" t="s">
-        <v>9</v>
-      </c>
-      <c r="E87" t="s">
-        <v>12</v>
-      </c>
-      <c r="F87" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="88">
@@ -2552,19 +2537,19 @@
         <v>41</v>
       </c>
       <c r="B88" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C88" t="s">
+        <v>56</v>
+      </c>
+      <c r="D88" t="s">
+        <v>9</v>
+      </c>
+      <c r="E88" t="s">
+        <v>13</v>
+      </c>
+      <c r="F88" t="s">
         <v>57</v>
-      </c>
-      <c r="D88" t="s">
-        <v>9</v>
-      </c>
-      <c r="E88" t="s">
-        <v>13</v>
-      </c>
-      <c r="F88" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="89">
@@ -2572,7 +2557,7 @@
         <v>41</v>
       </c>
       <c r="B89" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C89" t="s">
         <v>20</v>
@@ -2584,7 +2569,7 @@
         <v>10</v>
       </c>
       <c r="F89" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="90">
@@ -2592,7 +2577,7 @@
         <v>41</v>
       </c>
       <c r="B90" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C90" t="s">
         <v>20</v>
@@ -2604,7 +2589,7 @@
         <v>12</v>
       </c>
       <c r="F90" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="91">
@@ -2612,7 +2597,7 @@
         <v>41</v>
       </c>
       <c r="B91" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C91" t="s">
         <v>20</v>
@@ -2624,7 +2609,7 @@
         <v>13</v>
       </c>
       <c r="F91" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="92">
@@ -2632,7 +2617,7 @@
         <v>41</v>
       </c>
       <c r="B92" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C92" t="s">
         <v>20</v>
@@ -2644,7 +2629,7 @@
         <v>10</v>
       </c>
       <c r="F92" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="93">
@@ -2652,7 +2637,7 @@
         <v>41</v>
       </c>
       <c r="B93" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C93" t="s">
         <v>20</v>
@@ -2664,7 +2649,7 @@
         <v>12</v>
       </c>
       <c r="F93" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="94">
@@ -2672,7 +2657,7 @@
         <v>41</v>
       </c>
       <c r="B94" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C94" t="s">
         <v>20</v>
@@ -2684,7 +2669,7 @@
         <v>13</v>
       </c>
       <c r="F94" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="95">
@@ -2692,19 +2677,19 @@
         <v>41</v>
       </c>
       <c r="B95" t="s">
+        <v>59</v>
+      </c>
+      <c r="C95" t="s">
+        <v>49</v>
+      </c>
+      <c r="D95" t="s">
+        <v>9</v>
+      </c>
+      <c r="E95" t="s">
+        <v>10</v>
+      </c>
+      <c r="F95" t="s">
         <v>60</v>
-      </c>
-      <c r="C95" t="s">
-        <v>43</v>
-      </c>
-      <c r="D95" t="s">
-        <v>9</v>
-      </c>
-      <c r="E95" t="s">
-        <v>10</v>
-      </c>
-      <c r="F95" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="96">
@@ -2712,19 +2697,19 @@
         <v>41</v>
       </c>
       <c r="B96" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C96" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="D96" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E96" t="s">
         <v>10</v>
       </c>
       <c r="F96" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="97">
@@ -2732,19 +2717,19 @@
         <v>41</v>
       </c>
       <c r="B97" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C97" t="s">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="D97" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E97" t="s">
         <v>10</v>
       </c>
       <c r="F97" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="98">
@@ -2752,19 +2737,19 @@
         <v>41</v>
       </c>
       <c r="B98" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C98" t="s">
         <v>20</v>
       </c>
       <c r="D98" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E98" t="s">
         <v>10</v>
       </c>
       <c r="F98" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="99">
@@ -2772,19 +2757,19 @@
         <v>41</v>
       </c>
       <c r="B99" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C99" t="s">
         <v>20</v>
       </c>
       <c r="D99" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E99" t="s">
         <v>12</v>
       </c>
       <c r="F99" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="100">
@@ -2792,19 +2777,19 @@
         <v>41</v>
       </c>
       <c r="B100" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C100" t="s">
         <v>20</v>
       </c>
       <c r="D100" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E100" t="s">
         <v>13</v>
       </c>
       <c r="F100" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="101">
@@ -2812,19 +2797,19 @@
         <v>41</v>
       </c>
       <c r="B101" t="s">
+        <v>62</v>
+      </c>
+      <c r="C101" t="s">
+        <v>20</v>
+      </c>
+      <c r="D101" t="s">
         <v>65</v>
       </c>
-      <c r="C101" t="s">
-        <v>20</v>
-      </c>
-      <c r="D101" t="s">
-        <v>68</v>
-      </c>
       <c r="E101" t="s">
         <v>10</v>
       </c>
       <c r="F101" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="102">
@@ -2832,19 +2817,19 @@
         <v>41</v>
       </c>
       <c r="B102" t="s">
+        <v>62</v>
+      </c>
+      <c r="C102" t="s">
+        <v>20</v>
+      </c>
+      <c r="D102" t="s">
         <v>65</v>
       </c>
-      <c r="C102" t="s">
-        <v>20</v>
-      </c>
-      <c r="D102" t="s">
-        <v>68</v>
-      </c>
       <c r="E102" t="s">
         <v>12</v>
       </c>
       <c r="F102" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="103">
@@ -2852,19 +2837,19 @@
         <v>41</v>
       </c>
       <c r="B103" t="s">
+        <v>62</v>
+      </c>
+      <c r="C103" t="s">
+        <v>20</v>
+      </c>
+      <c r="D103" t="s">
         <v>65</v>
       </c>
-      <c r="C103" t="s">
-        <v>20</v>
-      </c>
-      <c r="D103" t="s">
-        <v>68</v>
-      </c>
       <c r="E103" t="s">
         <v>13</v>
       </c>
       <c r="F103" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="104">
@@ -2872,7 +2857,7 @@
         <v>41</v>
       </c>
       <c r="B104" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C104" t="s">
         <v>20</v>
@@ -2884,7 +2869,7 @@
         <v>10</v>
       </c>
       <c r="F104" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="105">
@@ -2892,7 +2877,7 @@
         <v>41</v>
       </c>
       <c r="B105" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C105" t="s">
         <v>20</v>
@@ -2904,7 +2889,7 @@
         <v>12</v>
       </c>
       <c r="F105" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="106">
@@ -2912,7 +2897,7 @@
         <v>41</v>
       </c>
       <c r="B106" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C106" t="s">
         <v>20</v>
@@ -2924,7 +2909,7 @@
         <v>13</v>
       </c>
       <c r="F106" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="107">
@@ -2932,7 +2917,7 @@
         <v>41</v>
       </c>
       <c r="B107" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C107" t="s">
         <v>20</v>
@@ -2944,7 +2929,7 @@
         <v>10</v>
       </c>
       <c r="F107" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="108">
@@ -2952,7 +2937,7 @@
         <v>41</v>
       </c>
       <c r="B108" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C108" t="s">
         <v>20</v>
@@ -2964,7 +2949,7 @@
         <v>12</v>
       </c>
       <c r="F108" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="109">
@@ -2972,7 +2957,7 @@
         <v>41</v>
       </c>
       <c r="B109" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C109" t="s">
         <v>20</v>
@@ -2984,7 +2969,7 @@
         <v>13</v>
       </c>
       <c r="F109" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="110">
@@ -2992,19 +2977,19 @@
         <v>41</v>
       </c>
       <c r="B110" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C110" t="s">
         <v>20</v>
       </c>
       <c r="D110" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E110" t="s">
         <v>10</v>
       </c>
       <c r="F110" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="111">
@@ -3012,7 +2997,7 @@
         <v>41</v>
       </c>
       <c r="B111" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C111" t="s">
         <v>20</v>
@@ -3024,7 +3009,7 @@
         <v>10</v>
       </c>
       <c r="F111" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="112">
@@ -3032,7 +3017,7 @@
         <v>41</v>
       </c>
       <c r="B112" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C112" t="s">
         <v>20</v>
@@ -3044,7 +3029,7 @@
         <v>10</v>
       </c>
       <c r="F112" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="113">
@@ -3052,19 +3037,19 @@
         <v>41</v>
       </c>
       <c r="B113" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C113" t="s">
         <v>20</v>
       </c>
       <c r="D113" t="s">
+        <v>67</v>
+      </c>
+      <c r="E113" t="s">
+        <v>10</v>
+      </c>
+      <c r="F113" t="s">
         <v>70</v>
-      </c>
-      <c r="E113" t="s">
-        <v>10</v>
-      </c>
-      <c r="F113" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="114">
@@ -3072,19 +3057,19 @@
         <v>41</v>
       </c>
       <c r="B114" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C114" t="s">
         <v>20</v>
       </c>
       <c r="D114" t="s">
+        <v>67</v>
+      </c>
+      <c r="E114" t="s">
+        <v>12</v>
+      </c>
+      <c r="F114" t="s">
         <v>70</v>
-      </c>
-      <c r="E114" t="s">
-        <v>12</v>
-      </c>
-      <c r="F114" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="115">
@@ -3092,19 +3077,19 @@
         <v>41</v>
       </c>
       <c r="B115" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C115" t="s">
         <v>20</v>
       </c>
       <c r="D115" t="s">
+        <v>67</v>
+      </c>
+      <c r="E115" t="s">
+        <v>13</v>
+      </c>
+      <c r="F115" t="s">
         <v>70</v>
-      </c>
-      <c r="E115" t="s">
-        <v>13</v>
-      </c>
-      <c r="F115" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="116">
@@ -3112,7 +3097,7 @@
         <v>41</v>
       </c>
       <c r="B116" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C116" t="s">
         <v>20</v>
@@ -3124,7 +3109,7 @@
         <v>10</v>
       </c>
       <c r="F116" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="117">
@@ -3132,7 +3117,7 @@
         <v>41</v>
       </c>
       <c r="B117" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C117" t="s">
         <v>20</v>
@@ -3144,7 +3129,7 @@
         <v>12</v>
       </c>
       <c r="F117" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="118">
@@ -3152,7 +3137,7 @@
         <v>41</v>
       </c>
       <c r="B118" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C118" t="s">
         <v>20</v>
@@ -3164,7 +3149,7 @@
         <v>13</v>
       </c>
       <c r="F118" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="119">
@@ -3172,7 +3157,7 @@
         <v>41</v>
       </c>
       <c r="B119" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C119" t="s">
         <v>20</v>
@@ -3184,7 +3169,7 @@
         <v>10</v>
       </c>
       <c r="F119" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="120">
@@ -3192,7 +3177,7 @@
         <v>41</v>
       </c>
       <c r="B120" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C120" t="s">
         <v>20</v>
@@ -3204,7 +3189,7 @@
         <v>12</v>
       </c>
       <c r="F120" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="121">
@@ -3212,7 +3197,7 @@
         <v>41</v>
       </c>
       <c r="B121" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C121" t="s">
         <v>20</v>
@@ -3224,78 +3209,78 @@
         <v>13</v>
       </c>
       <c r="F121" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
+        <v>71</v>
+      </c>
+      <c r="B122" t="s">
+        <v>72</v>
+      </c>
+      <c r="C122" t="s">
+        <v>73</v>
+      </c>
+      <c r="D122" t="s">
+        <v>9</v>
+      </c>
+      <c r="E122" t="s">
+        <v>10</v>
+      </c>
+      <c r="F122" t="s">
         <v>74</v>
-      </c>
-      <c r="B122" t="s">
-        <v>75</v>
-      </c>
-      <c r="C122" t="s">
-        <v>76</v>
-      </c>
-      <c r="D122" t="s">
-        <v>9</v>
-      </c>
-      <c r="E122" t="s">
-        <v>10</v>
-      </c>
-      <c r="F122" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
+        <v>71</v>
+      </c>
+      <c r="B123" t="s">
+        <v>72</v>
+      </c>
+      <c r="C123" t="s">
+        <v>73</v>
+      </c>
+      <c r="D123" t="s">
+        <v>9</v>
+      </c>
+      <c r="E123" t="s">
+        <v>12</v>
+      </c>
+      <c r="F123" t="s">
         <v>74</v>
-      </c>
-      <c r="B123" t="s">
-        <v>75</v>
-      </c>
-      <c r="C123" t="s">
-        <v>76</v>
-      </c>
-      <c r="D123" t="s">
-        <v>9</v>
-      </c>
-      <c r="E123" t="s">
-        <v>12</v>
-      </c>
-      <c r="F123" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
+        <v>71</v>
+      </c>
+      <c r="B124" t="s">
+        <v>72</v>
+      </c>
+      <c r="C124" t="s">
+        <v>73</v>
+      </c>
+      <c r="D124" t="s">
+        <v>9</v>
+      </c>
+      <c r="E124" t="s">
+        <v>13</v>
+      </c>
+      <c r="F124" t="s">
         <v>74</v>
-      </c>
-      <c r="B124" t="s">
-        <v>75</v>
-      </c>
-      <c r="C124" t="s">
-        <v>76</v>
-      </c>
-      <c r="D124" t="s">
-        <v>9</v>
-      </c>
-      <c r="E124" t="s">
-        <v>13</v>
-      </c>
-      <c r="F124" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B125" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C125" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D125" t="s">
         <v>9</v>
@@ -3304,18 +3289,18 @@
         <v>10</v>
       </c>
       <c r="F125" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B126" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C126" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D126" t="s">
         <v>9</v>
@@ -3324,18 +3309,18 @@
         <v>12</v>
       </c>
       <c r="F126" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B127" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C127" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D127" t="s">
         <v>9</v>
@@ -3344,19 +3329,19 @@
         <v>13</v>
       </c>
       <c r="F127" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B128" t="s">
+        <v>75</v>
+      </c>
+      <c r="C128" t="s">
         <v>78</v>
       </c>
-      <c r="C128" t="s">
-        <v>81</v>
-      </c>
       <c r="D128" t="s">
         <v>9</v>
       </c>
@@ -3364,19 +3349,19 @@
         <v>10</v>
       </c>
       <c r="F128" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B129" t="s">
+        <v>75</v>
+      </c>
+      <c r="C129" t="s">
         <v>78</v>
       </c>
-      <c r="C129" t="s">
-        <v>81</v>
-      </c>
       <c r="D129" t="s">
         <v>9</v>
       </c>
@@ -3384,19 +3369,19 @@
         <v>12</v>
       </c>
       <c r="F129" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B130" t="s">
+        <v>75</v>
+      </c>
+      <c r="C130" t="s">
         <v>78</v>
       </c>
-      <c r="C130" t="s">
-        <v>81</v>
-      </c>
       <c r="D130" t="s">
         <v>9</v>
       </c>
@@ -3404,19 +3389,19 @@
         <v>13</v>
       </c>
       <c r="F130" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B131" t="s">
+        <v>75</v>
+      </c>
+      <c r="C131" t="s">
         <v>78</v>
       </c>
-      <c r="C131" t="s">
-        <v>81</v>
-      </c>
       <c r="D131" t="s">
         <v>14</v>
       </c>
@@ -3424,19 +3409,19 @@
         <v>10</v>
       </c>
       <c r="F131" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B132" t="s">
+        <v>75</v>
+      </c>
+      <c r="C132" t="s">
         <v>78</v>
       </c>
-      <c r="C132" t="s">
-        <v>81</v>
-      </c>
       <c r="D132" t="s">
         <v>14</v>
       </c>
@@ -3444,19 +3429,19 @@
         <v>12</v>
       </c>
       <c r="F132" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B133" t="s">
+        <v>75</v>
+      </c>
+      <c r="C133" t="s">
         <v>78</v>
       </c>
-      <c r="C133" t="s">
-        <v>81</v>
-      </c>
       <c r="D133" t="s">
         <v>14</v>
       </c>
@@ -3464,75 +3449,75 @@
         <v>13</v>
       </c>
       <c r="F133" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B134" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C134" t="s">
         <v>20</v>
       </c>
       <c r="D134" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E134" t="s">
         <v>10</v>
       </c>
       <c r="F134" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B135" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C135" t="s">
         <v>20</v>
       </c>
       <c r="D135" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E135" t="s">
         <v>12</v>
       </c>
       <c r="F135" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B136" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C136" t="s">
         <v>20</v>
       </c>
       <c r="D136" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E136" t="s">
         <v>13</v>
       </c>
       <c r="F136" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B137" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C137" t="s">
         <v>20</v>
@@ -3544,15 +3529,15 @@
         <v>10</v>
       </c>
       <c r="F137" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B138" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C138" t="s">
         <v>20</v>
@@ -3564,15 +3549,15 @@
         <v>12</v>
       </c>
       <c r="F138" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B139" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C139" t="s">
         <v>20</v>
@@ -3584,15 +3569,15 @@
         <v>13</v>
       </c>
       <c r="F139" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B140" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C140" t="s">
         <v>20</v>
@@ -3604,15 +3589,15 @@
         <v>10</v>
       </c>
       <c r="F140" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B141" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C141" t="s">
         <v>20</v>
@@ -3624,15 +3609,15 @@
         <v>12</v>
       </c>
       <c r="F141" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B142" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C142" t="s">
         <v>20</v>
@@ -3644,15 +3629,15 @@
         <v>13</v>
       </c>
       <c r="F142" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B143" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C143" t="s">
         <v>17</v>
@@ -3664,15 +3649,15 @@
         <v>10</v>
       </c>
       <c r="F143" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B144" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C144" t="s">
         <v>17</v>
@@ -3684,15 +3669,15 @@
         <v>12</v>
       </c>
       <c r="F144" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B145" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C145" t="s">
         <v>17</v>
@@ -3704,15 +3689,15 @@
         <v>13</v>
       </c>
       <c r="F145" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B146" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C146" t="s">
         <v>17</v>
@@ -3724,15 +3709,15 @@
         <v>10</v>
       </c>
       <c r="F146" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B147" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C147" t="s">
         <v>17</v>
@@ -3744,15 +3729,15 @@
         <v>12</v>
       </c>
       <c r="F147" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B148" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C148" t="s">
         <v>17</v>
@@ -3764,18 +3749,18 @@
         <v>13</v>
       </c>
       <c r="F148" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B149" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C149" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D149" t="s">
         <v>9</v>
@@ -3784,18 +3769,18 @@
         <v>10</v>
       </c>
       <c r="F149" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B150" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C150" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D150" t="s">
         <v>9</v>
@@ -3804,18 +3789,18 @@
         <v>12</v>
       </c>
       <c r="F150" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B151" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C151" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D151" t="s">
         <v>9</v>
@@ -3824,18 +3809,18 @@
         <v>13</v>
       </c>
       <c r="F151" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B152" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C152" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D152" t="s">
         <v>14</v>
@@ -3844,18 +3829,18 @@
         <v>10</v>
       </c>
       <c r="F152" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B153" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C153" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D153" t="s">
         <v>14</v>
@@ -3864,18 +3849,18 @@
         <v>12</v>
       </c>
       <c r="F153" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B154" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C154" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D154" t="s">
         <v>14</v>
@@ -3884,18 +3869,18 @@
         <v>13</v>
       </c>
       <c r="F154" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B155" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C155" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D155" t="s">
         <v>9</v>
@@ -3904,18 +3889,18 @@
         <v>10</v>
       </c>
       <c r="F155" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B156" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C156" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D156" t="s">
         <v>9</v>
@@ -3924,18 +3909,18 @@
         <v>12</v>
       </c>
       <c r="F156" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B157" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C157" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D157" t="s">
         <v>9</v>
@@ -3944,18 +3929,18 @@
         <v>13</v>
       </c>
       <c r="F157" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B158" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C158" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D158" t="s">
         <v>14</v>
@@ -3964,18 +3949,18 @@
         <v>10</v>
       </c>
       <c r="F158" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B159" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C159" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D159" t="s">
         <v>14</v>
@@ -3984,18 +3969,18 @@
         <v>12</v>
       </c>
       <c r="F159" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B160" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C160" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D160" t="s">
         <v>14</v>
@@ -4004,135 +3989,135 @@
         <v>13</v>
       </c>
       <c r="F160" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B161" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C161" t="s">
         <v>20</v>
       </c>
       <c r="D161" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E161" t="s">
         <v>10</v>
       </c>
       <c r="F161" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B162" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C162" t="s">
         <v>20</v>
       </c>
       <c r="D162" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E162" t="s">
         <v>12</v>
       </c>
       <c r="F162" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B163" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C163" t="s">
         <v>20</v>
       </c>
       <c r="D163" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E163" t="s">
         <v>13</v>
       </c>
       <c r="F163" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B164" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C164" t="s">
         <v>20</v>
       </c>
       <c r="D164" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E164" t="s">
         <v>10</v>
       </c>
       <c r="F164" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B165" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C165" t="s">
         <v>20</v>
       </c>
       <c r="D165" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E165" t="s">
         <v>12</v>
       </c>
       <c r="F165" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B166" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C166" t="s">
         <v>20</v>
       </c>
       <c r="D166" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E166" t="s">
         <v>13</v>
       </c>
       <c r="F166" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B167" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C167" t="s">
         <v>20</v>
@@ -4144,15 +4129,15 @@
         <v>10</v>
       </c>
       <c r="F167" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B168" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C168" t="s">
         <v>20</v>
@@ -4164,15 +4149,15 @@
         <v>12</v>
       </c>
       <c r="F168" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B169" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C169" t="s">
         <v>20</v>
@@ -4184,15 +4169,15 @@
         <v>13</v>
       </c>
       <c r="F169" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B170" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C170" t="s">
         <v>20</v>
@@ -4204,15 +4189,15 @@
         <v>10</v>
       </c>
       <c r="F170" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B171" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C171" t="s">
         <v>20</v>
@@ -4224,15 +4209,15 @@
         <v>12</v>
       </c>
       <c r="F171" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B172" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C172" t="s">
         <v>20</v>
@@ -4244,18 +4229,18 @@
         <v>13</v>
       </c>
       <c r="F172" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B173" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C173" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D173" t="s">
         <v>9</v>
@@ -4264,18 +4249,18 @@
         <v>10</v>
       </c>
       <c r="F173" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B174" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C174" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D174" t="s">
         <v>9</v>
@@ -4284,18 +4269,18 @@
         <v>12</v>
       </c>
       <c r="F174" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B175" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C175" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D175" t="s">
         <v>9</v>
@@ -4304,258 +4289,258 @@
         <v>13</v>
       </c>
       <c r="F175" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B176" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C176" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D176" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E176" t="s">
         <v>10</v>
       </c>
       <c r="F176" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B177" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C177" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D177" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E177" t="s">
         <v>12</v>
       </c>
       <c r="F177" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B178" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C178" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D178" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E178" t="s">
         <v>13</v>
       </c>
       <c r="F178" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B179" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C179" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="D179" t="s">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="E179" t="s">
         <v>10</v>
       </c>
       <c r="F179" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B180" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C180" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="D180" t="s">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="E180" t="s">
         <v>12</v>
       </c>
       <c r="F180" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B181" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C181" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="D181" t="s">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="E181" t="s">
         <v>13</v>
       </c>
       <c r="F181" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B182" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C182" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="D182" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E182" t="s">
         <v>10</v>
       </c>
       <c r="F182" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B183" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C183" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="D183" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E183" t="s">
         <v>12</v>
       </c>
       <c r="F183" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B184" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C184" t="s">
-        <v>20</v>
+        <v>82</v>
       </c>
       <c r="D184" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E184" t="s">
         <v>13</v>
       </c>
       <c r="F184" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B185" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C185" t="s">
         <v>20</v>
       </c>
       <c r="D185" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="E185" t="s">
         <v>10</v>
       </c>
       <c r="F185" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B186" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C186" t="s">
         <v>20</v>
       </c>
       <c r="D186" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="E186" t="s">
         <v>12</v>
       </c>
       <c r="F186" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B187" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C187" t="s">
         <v>20</v>
       </c>
       <c r="D187" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="E187" t="s">
         <v>13</v>
       </c>
       <c r="F187" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B188" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C188" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D188" t="s">
         <v>9</v>
@@ -4564,18 +4549,18 @@
         <v>10</v>
       </c>
       <c r="F188" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B189" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C189" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D189" t="s">
         <v>9</v>
@@ -4584,18 +4569,18 @@
         <v>12</v>
       </c>
       <c r="F189" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B190" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C190" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D190" t="s">
         <v>9</v>
@@ -4604,18 +4589,18 @@
         <v>13</v>
       </c>
       <c r="F190" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B191" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C191" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D191" t="s">
         <v>14</v>
@@ -4624,18 +4609,18 @@
         <v>10</v>
       </c>
       <c r="F191" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B192" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C192" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D192" t="s">
         <v>14</v>
@@ -4644,18 +4629,18 @@
         <v>12</v>
       </c>
       <c r="F192" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B193" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C193" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D193" t="s">
         <v>14</v>
@@ -4664,18 +4649,18 @@
         <v>13</v>
       </c>
       <c r="F193" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B194" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C194" t="s">
-        <v>96</v>
+        <v>17</v>
       </c>
       <c r="D194" t="s">
         <v>9</v>
@@ -4684,18 +4669,18 @@
         <v>10</v>
       </c>
       <c r="F194" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B195" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C195" t="s">
-        <v>96</v>
+        <v>17</v>
       </c>
       <c r="D195" t="s">
         <v>9</v>
@@ -4704,18 +4689,18 @@
         <v>12</v>
       </c>
       <c r="F195" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B196" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C196" t="s">
-        <v>96</v>
+        <v>17</v>
       </c>
       <c r="D196" t="s">
         <v>9</v>
@@ -4724,18 +4709,18 @@
         <v>13</v>
       </c>
       <c r="F196" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B197" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C197" t="s">
-        <v>96</v>
+        <v>17</v>
       </c>
       <c r="D197" t="s">
         <v>14</v>
@@ -4744,18 +4729,18 @@
         <v>10</v>
       </c>
       <c r="F197" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B198" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C198" t="s">
-        <v>96</v>
+        <v>17</v>
       </c>
       <c r="D198" t="s">
         <v>14</v>
@@ -4764,18 +4749,18 @@
         <v>12</v>
       </c>
       <c r="F198" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B199" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C199" t="s">
-        <v>96</v>
+        <v>17</v>
       </c>
       <c r="D199" t="s">
         <v>14</v>
@@ -4784,19 +4769,19 @@
         <v>13</v>
       </c>
       <c r="F199" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B200" t="s">
+        <v>90</v>
+      </c>
+      <c r="C200" t="s">
         <v>93</v>
       </c>
-      <c r="C200" t="s">
-        <v>43</v>
-      </c>
       <c r="D200" t="s">
         <v>9</v>
       </c>
@@ -4804,19 +4789,19 @@
         <v>10</v>
       </c>
       <c r="F200" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B201" t="s">
+        <v>90</v>
+      </c>
+      <c r="C201" t="s">
         <v>93</v>
       </c>
-      <c r="C201" t="s">
-        <v>43</v>
-      </c>
       <c r="D201" t="s">
         <v>9</v>
       </c>
@@ -4824,19 +4809,19 @@
         <v>12</v>
       </c>
       <c r="F201" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B202" t="s">
+        <v>90</v>
+      </c>
+      <c r="C202" t="s">
         <v>93</v>
       </c>
-      <c r="C202" t="s">
-        <v>43</v>
-      </c>
       <c r="D202" t="s">
         <v>9</v>
       </c>
@@ -4844,78 +4829,78 @@
         <v>13</v>
       </c>
       <c r="F202" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B203" t="s">
+        <v>90</v>
+      </c>
+      <c r="C203" t="s">
         <v>93</v>
       </c>
-      <c r="C203" t="s">
-        <v>85</v>
-      </c>
       <c r="D203" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E203" t="s">
         <v>10</v>
       </c>
       <c r="F203" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B204" t="s">
+        <v>90</v>
+      </c>
+      <c r="C204" t="s">
         <v>93</v>
       </c>
-      <c r="C204" t="s">
-        <v>85</v>
-      </c>
       <c r="D204" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E204" t="s">
         <v>12</v>
       </c>
       <c r="F204" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B205" t="s">
+        <v>90</v>
+      </c>
+      <c r="C205" t="s">
         <v>93</v>
       </c>
-      <c r="C205" t="s">
-        <v>85</v>
-      </c>
       <c r="D205" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E205" t="s">
         <v>13</v>
       </c>
       <c r="F205" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B206" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C206" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="D206" t="s">
         <v>9</v>
@@ -4924,18 +4909,18 @@
         <v>10</v>
       </c>
       <c r="F206" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B207" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C207" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="D207" t="s">
         <v>9</v>
@@ -4944,18 +4929,18 @@
         <v>12</v>
       </c>
       <c r="F207" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B208" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C208" t="s">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="D208" t="s">
         <v>9</v>
@@ -4964,258 +4949,258 @@
         <v>13</v>
       </c>
       <c r="F208" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B209" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C209" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D209" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E209" t="s">
         <v>10</v>
       </c>
       <c r="F209" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B210" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C210" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D210" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E210" t="s">
         <v>12</v>
       </c>
       <c r="F210" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B211" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C211" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D211" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E211" t="s">
         <v>13</v>
       </c>
       <c r="F211" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B212" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C212" t="s">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="D212" t="s">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="E212" t="s">
         <v>10</v>
       </c>
       <c r="F212" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B213" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C213" t="s">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="D213" t="s">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="E213" t="s">
         <v>12</v>
       </c>
       <c r="F213" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B214" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C214" t="s">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="D214" t="s">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="E214" t="s">
         <v>13</v>
       </c>
       <c r="F214" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B215" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C215" t="s">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="D215" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E215" t="s">
         <v>10</v>
       </c>
       <c r="F215" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B216" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C216" t="s">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="D216" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E216" t="s">
         <v>12</v>
       </c>
       <c r="F216" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B217" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C217" t="s">
-        <v>20</v>
+        <v>78</v>
       </c>
       <c r="D217" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E217" t="s">
         <v>13</v>
       </c>
       <c r="F217" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B218" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C218" t="s">
         <v>20</v>
       </c>
       <c r="D218" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="E218" t="s">
         <v>10</v>
       </c>
       <c r="F218" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B219" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C219" t="s">
         <v>20</v>
       </c>
       <c r="D219" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="E219" t="s">
         <v>12</v>
       </c>
       <c r="F219" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B220" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C220" t="s">
         <v>20</v>
       </c>
       <c r="D220" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="E220" t="s">
         <v>13</v>
       </c>
       <c r="F220" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B221" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C221" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D221" t="s">
         <v>9</v>
@@ -5224,18 +5209,18 @@
         <v>10</v>
       </c>
       <c r="F221" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B222" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C222" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D222" t="s">
         <v>9</v>
@@ -5244,18 +5229,18 @@
         <v>12</v>
       </c>
       <c r="F222" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B223" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C223" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D223" t="s">
         <v>9</v>
@@ -5264,18 +5249,18 @@
         <v>13</v>
       </c>
       <c r="F223" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B224" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C224" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D224" t="s">
         <v>14</v>
@@ -5284,18 +5269,18 @@
         <v>10</v>
       </c>
       <c r="F224" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B225" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C225" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D225" t="s">
         <v>14</v>
@@ -5304,18 +5289,18 @@
         <v>12</v>
       </c>
       <c r="F225" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B226" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C226" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D226" t="s">
         <v>14</v>
@@ -5324,18 +5309,18 @@
         <v>13</v>
       </c>
       <c r="F226" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B227" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C227" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="D227" t="s">
         <v>9</v>
@@ -5344,358 +5329,358 @@
         <v>10</v>
       </c>
       <c r="F227" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B228" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C228" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="D228" t="s">
         <v>9</v>
       </c>
       <c r="E228" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F228" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B229" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C229" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="D229" t="s">
         <v>9</v>
       </c>
       <c r="E229" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F229" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B230" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C230" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="D230" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E230" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F230" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B231" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C231" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="D231" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E231" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F231" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B232" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C232" t="s">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="D232" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E232" t="s">
         <v>13</v>
       </c>
       <c r="F232" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B233" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C233" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D233" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E233" t="s">
         <v>10</v>
       </c>
       <c r="F233" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B234" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C234" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D234" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E234" t="s">
         <v>10</v>
       </c>
       <c r="F234" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B235" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C235" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D235" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E235" t="s">
         <v>12</v>
       </c>
       <c r="F235" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B236" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C236" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D236" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E236" t="s">
         <v>12</v>
       </c>
       <c r="F236" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B237" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C237" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D237" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E237" t="s">
         <v>13</v>
       </c>
       <c r="F237" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B238" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C238" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D238" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E238" t="s">
         <v>13</v>
       </c>
       <c r="F238" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B239" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C239" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D239" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E239" t="s">
         <v>10</v>
       </c>
       <c r="F239" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B240" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C240" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D240" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E240" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F240" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B241" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C241" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D241" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E241" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F241" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="s">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="B242" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="C242" t="s">
-        <v>107</v>
+        <v>82</v>
       </c>
       <c r="D242" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E242" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F242" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="s">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="B243" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="C243" t="s">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="D243" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E243" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F243" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="s">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="B244" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="C244" t="s">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="D244" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E244" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F244" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="s">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="B245" t="s">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="C245" t="s">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="D245" t="s">
         <v>9</v>
@@ -5704,18 +5689,18 @@
         <v>10</v>
       </c>
       <c r="F245" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="s">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="B246" t="s">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="C246" t="s">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="D246" t="s">
         <v>9</v>
@@ -5724,18 +5709,18 @@
         <v>12</v>
       </c>
       <c r="F246" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="s">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="B247" t="s">
-        <v>45</v>
+        <v>90</v>
       </c>
       <c r="C247" t="s">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="D247" t="s">
         <v>9</v>
@@ -5744,78 +5729,78 @@
         <v>13</v>
       </c>
       <c r="F247" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="B248" t="s">
-        <v>45</v>
+        <v>103</v>
       </c>
       <c r="C248" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="D248" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E248" t="s">
         <v>10</v>
       </c>
       <c r="F248" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="B249" t="s">
-        <v>45</v>
+        <v>105</v>
       </c>
       <c r="C249" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="D249" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E249" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F249" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="B250" t="s">
-        <v>45</v>
+        <v>105</v>
       </c>
       <c r="C250" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="D250" t="s">
         <v>14</v>
       </c>
       <c r="E250" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F250" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="B251" t="s">
-        <v>45</v>
+        <v>107</v>
       </c>
       <c r="C251" t="s">
-        <v>43</v>
+        <v>108</v>
       </c>
       <c r="D251" t="s">
         <v>9</v>
@@ -5824,1907 +5809,2047 @@
         <v>10</v>
       </c>
       <c r="F251" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B252" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C252" t="s">
-        <v>116</v>
+        <v>20</v>
       </c>
       <c r="D252" t="s">
-        <v>9</v>
+        <v>67</v>
       </c>
       <c r="E252" t="s">
         <v>10</v>
       </c>
       <c r="F252" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B253" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C253" t="s">
-        <v>116</v>
+        <v>20</v>
       </c>
       <c r="D253" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="E253" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F253" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B254" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C254" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="D254" t="s">
-        <v>9</v>
+        <v>67</v>
       </c>
       <c r="E254" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F254" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B255" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C255" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="D255" t="s">
         <v>9</v>
       </c>
       <c r="E255" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F255" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B256" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C256" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="D256" t="s">
         <v>9</v>
       </c>
       <c r="E256" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F256" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B257" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C257" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="D257" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E257" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F257" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B258" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C258" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="D258" t="s">
         <v>14</v>
       </c>
       <c r="E258" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F258" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B259" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C259" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="D259" t="s">
         <v>14</v>
       </c>
       <c r="E259" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F259" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B260" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C260" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="D260" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E260" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F260" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B261" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C261" t="s">
-        <v>43</v>
+        <v>112</v>
       </c>
       <c r="D261" t="s">
         <v>9</v>
       </c>
       <c r="E261" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F261" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B262" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C262" t="s">
-        <v>43</v>
+        <v>112</v>
       </c>
       <c r="D262" t="s">
         <v>9</v>
       </c>
       <c r="E262" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F262" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B263" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C263" t="s">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="D263" t="s">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="E263" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F263" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B264" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C264" t="s">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="D264" t="s">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="E264" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F264" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B265" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C265" t="s">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="D265" t="s">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="E265" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F265" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B266" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C266" t="s">
-        <v>20</v>
+        <v>112</v>
       </c>
       <c r="D266" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E266" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F266" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B267" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C267" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D267" t="s">
         <v>9</v>
       </c>
       <c r="E267" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F267" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="s">
+        <v>110</v>
+      </c>
+      <c r="B268" t="s">
+        <v>42</v>
+      </c>
+      <c r="C268" t="s">
+        <v>112</v>
+      </c>
+      <c r="D268" t="s">
+        <v>9</v>
+      </c>
+      <c r="E268" t="s">
+        <v>10</v>
+      </c>
+      <c r="F268" t="s">
         <v>115</v>
-      </c>
-      <c r="B268" t="s">
-        <v>48</v>
-      </c>
-      <c r="C268" t="s">
-        <v>20</v>
-      </c>
-      <c r="D268" t="s">
-        <v>9</v>
-      </c>
-      <c r="E268" t="s">
-        <v>13</v>
-      </c>
-      <c r="F268" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="s">
+        <v>110</v>
+      </c>
+      <c r="B269" t="s">
+        <v>42</v>
+      </c>
+      <c r="C269" t="s">
+        <v>112</v>
+      </c>
+      <c r="D269" t="s">
+        <v>14</v>
+      </c>
+      <c r="E269" t="s">
+        <v>10</v>
+      </c>
+      <c r="F269" t="s">
         <v>115</v>
-      </c>
-      <c r="B269" t="s">
-        <v>48</v>
-      </c>
-      <c r="C269" t="s">
-        <v>20</v>
-      </c>
-      <c r="D269" t="s">
-        <v>14</v>
-      </c>
-      <c r="E269" t="s">
-        <v>10</v>
-      </c>
-      <c r="F269" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B270" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C270" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D270" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E270" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F270" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B271" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C271" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D271" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E271" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F271" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B272" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C272" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D272" t="s">
         <v>9</v>
       </c>
       <c r="E272" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F272" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B273" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C273" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D273" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E273" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F273" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B274" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C274" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D274" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E274" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F274" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B275" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C275" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D275" t="s">
         <v>14</v>
       </c>
       <c r="E275" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F275" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B276" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C276" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D276" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E276" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F276" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B277" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C277" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D277" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E277" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F277" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B278" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C278" t="s">
-        <v>116</v>
+        <v>23</v>
       </c>
       <c r="D278" t="s">
         <v>9</v>
       </c>
       <c r="E278" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F278" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B279" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C279" t="s">
-        <v>116</v>
+        <v>17</v>
       </c>
       <c r="D279" t="s">
         <v>9</v>
       </c>
       <c r="E279" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F279" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B280" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C280" t="s">
-        <v>116</v>
+        <v>17</v>
       </c>
       <c r="D280" t="s">
         <v>9</v>
       </c>
       <c r="E280" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F280" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B281" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C281" t="s">
-        <v>116</v>
+        <v>17</v>
       </c>
       <c r="D281" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E281" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F281" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B282" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C282" t="s">
-        <v>116</v>
+        <v>17</v>
       </c>
       <c r="D282" t="s">
         <v>14</v>
       </c>
       <c r="E282" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F282" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B283" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C283" t="s">
-        <v>116</v>
+        <v>17</v>
       </c>
       <c r="D283" t="s">
         <v>14</v>
       </c>
       <c r="E283" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F283" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B284" t="s">
-        <v>125</v>
+        <v>44</v>
       </c>
       <c r="C284" t="s">
-        <v>126</v>
+        <v>17</v>
       </c>
       <c r="D284" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E284" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F284" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B285" t="s">
-        <v>125</v>
+        <v>44</v>
       </c>
       <c r="C285" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="D285" t="s">
         <v>9</v>
       </c>
       <c r="E285" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F285" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B286" t="s">
-        <v>125</v>
+        <v>44</v>
       </c>
       <c r="C286" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="D286" t="s">
         <v>9</v>
       </c>
       <c r="E286" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F286" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B287" t="s">
-        <v>125</v>
+        <v>44</v>
       </c>
       <c r="C287" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="D287" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E287" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F287" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B288" t="s">
-        <v>125</v>
+        <v>44</v>
       </c>
       <c r="C288" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="D288" t="s">
         <v>14</v>
       </c>
       <c r="E288" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F288" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B289" t="s">
-        <v>125</v>
+        <v>44</v>
       </c>
       <c r="C289" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="D289" t="s">
         <v>14</v>
       </c>
       <c r="E289" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F289" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B290" t="s">
-        <v>125</v>
+        <v>44</v>
       </c>
       <c r="C290" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="D290" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E290" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F290" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B291" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C291" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D291" t="s">
         <v>9</v>
       </c>
       <c r="E291" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F291" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B292" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C292" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D292" t="s">
         <v>9</v>
       </c>
       <c r="E292" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F292" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B293" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C293" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D293" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E293" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F293" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B294" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C294" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D294" t="s">
         <v>14</v>
       </c>
       <c r="E294" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F294" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B295" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C295" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="D295" t="s">
         <v>14</v>
       </c>
       <c r="E295" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F295" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B296" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C296" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="D296" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E296" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F296" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B297" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C297" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D297" t="s">
         <v>9</v>
       </c>
       <c r="E297" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F297" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B298" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C298" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D298" t="s">
         <v>9</v>
       </c>
       <c r="E298" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F298" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B299" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C299" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D299" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E299" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F299" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B300" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C300" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D300" t="s">
         <v>14</v>
       </c>
       <c r="E300" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F300" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="B301" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C301" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D301" t="s">
         <v>14</v>
       </c>
       <c r="E301" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F301" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="B302" t="s">
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="C302" t="s">
-        <v>63</v>
+        <v>123</v>
       </c>
       <c r="D302" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E302" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F302" t="s">
-        <v>133</v>
+        <v>124</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="B303" t="s">
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="C303" t="s">
-        <v>63</v>
+        <v>125</v>
       </c>
       <c r="D303" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E303" t="s">
         <v>10</v>
       </c>
       <c r="F303" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="B304" t="s">
-        <v>45</v>
+        <v>120</v>
       </c>
       <c r="C304" t="s">
-        <v>43</v>
+        <v>125</v>
       </c>
       <c r="D304" t="s">
         <v>9</v>
       </c>
       <c r="E304" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F304" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="B305" t="s">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="C305" t="s">
-        <v>49</v>
+        <v>125</v>
       </c>
       <c r="D305" t="s">
         <v>9</v>
       </c>
       <c r="E305" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F305" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="B306" t="s">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="C306" t="s">
-        <v>49</v>
+        <v>125</v>
       </c>
       <c r="D306" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E306" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F306" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="B307" t="s">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="C307" t="s">
-        <v>49</v>
+        <v>125</v>
       </c>
       <c r="D307" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E307" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F307" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="B308" t="s">
-        <v>48</v>
+        <v>120</v>
       </c>
       <c r="C308" t="s">
-        <v>51</v>
+        <v>125</v>
       </c>
       <c r="D308" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E308" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F308" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B309" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C309" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D309" t="s">
         <v>9</v>
       </c>
       <c r="E309" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F309" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B310" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C310" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D310" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E310" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F310" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B311" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C311" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="D311" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E311" t="s">
         <v>10</v>
       </c>
       <c r="F311" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B312" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C312" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D312" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E312" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F312" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B313" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C313" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D313" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E313" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F313" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B314" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C314" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="D314" t="s">
         <v>9</v>
       </c>
       <c r="E314" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F314" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B315" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C315" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="D315" t="s">
         <v>9</v>
       </c>
       <c r="E315" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F315" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B316" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C316" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="D316" t="s">
         <v>9</v>
       </c>
       <c r="E316" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F316" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B317" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C317" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="D317" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E317" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F317" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B318" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C318" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="D318" t="s">
         <v>14</v>
       </c>
       <c r="E318" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F318" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B319" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C319" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="D319" t="s">
         <v>14</v>
       </c>
       <c r="E319" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F319" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B320" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C320" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D320" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E320" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F320" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="s">
+        <v>127</v>
+      </c>
+      <c r="B321" t="s">
+        <v>44</v>
+      </c>
+      <c r="C321" t="s">
+        <v>49</v>
+      </c>
+      <c r="D321" t="s">
+        <v>9</v>
+      </c>
+      <c r="E321" t="s">
+        <v>10</v>
+      </c>
+      <c r="F321" t="s">
         <v>132</v>
-      </c>
-      <c r="B321" t="s">
-        <v>48</v>
-      </c>
-      <c r="C321" t="s">
-        <v>43</v>
-      </c>
-      <c r="D321" t="s">
-        <v>9</v>
-      </c>
-      <c r="E321" t="s">
-        <v>12</v>
-      </c>
-      <c r="F321" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="s">
+        <v>127</v>
+      </c>
+      <c r="B322" t="s">
+        <v>44</v>
+      </c>
+      <c r="C322" t="s">
+        <v>49</v>
+      </c>
+      <c r="D322" t="s">
+        <v>9</v>
+      </c>
+      <c r="E322" t="s">
+        <v>12</v>
+      </c>
+      <c r="F322" t="s">
         <v>132</v>
-      </c>
-      <c r="B322" t="s">
-        <v>48</v>
-      </c>
-      <c r="C322" t="s">
-        <v>43</v>
-      </c>
-      <c r="D322" t="s">
-        <v>9</v>
-      </c>
-      <c r="E322" t="s">
-        <v>13</v>
-      </c>
-      <c r="F322" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="B323" t="s">
-        <v>140</v>
+        <v>44</v>
       </c>
       <c r="C323" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D323" t="s">
         <v>9</v>
       </c>
       <c r="E323" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F323" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="B324" t="s">
-        <v>140</v>
+        <v>44</v>
       </c>
       <c r="C324" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D324" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E324" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F324" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="B325" t="s">
-        <v>140</v>
+        <v>44</v>
       </c>
       <c r="C325" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D325" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E325" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F325" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="B326" t="s">
-        <v>140</v>
+        <v>44</v>
       </c>
       <c r="C326" t="s">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="D326" t="s">
         <v>14</v>
       </c>
       <c r="E326" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F326" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="B327" t="s">
-        <v>140</v>
+        <v>44</v>
       </c>
       <c r="C327" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="D327" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E327" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F327" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="B328" t="s">
-        <v>140</v>
+        <v>44</v>
       </c>
       <c r="C328" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="D328" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E328" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F328" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="B329" t="s">
-        <v>142</v>
+        <v>44</v>
       </c>
       <c r="C329" t="s">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="D329" t="s">
         <v>9</v>
       </c>
       <c r="E329" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F329" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B330" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C330" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D330" t="s">
         <v>9</v>
       </c>
       <c r="E330" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F330" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B331" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C331" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D331" t="s">
         <v>9</v>
       </c>
       <c r="E331" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F331" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B332" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C332" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D332" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E332" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F332" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B333" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C333" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D333" t="s">
         <v>14</v>
       </c>
       <c r="E333" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F333" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B334" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C334" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D334" t="s">
         <v>14</v>
       </c>
       <c r="E334" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F334" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B335" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="C335" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D335" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E335" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F335" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B336" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C336" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D336" t="s">
         <v>9</v>
       </c>
       <c r="E336" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F336" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B337" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C337" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D337" t="s">
         <v>9</v>
       </c>
       <c r="E337" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F337" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B338" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C338" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D338" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E338" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F338" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B339" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C339" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D339" t="s">
         <v>14</v>
       </c>
       <c r="E339" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F339" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B340" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C340" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D340" t="s">
         <v>14</v>
       </c>
       <c r="E340" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F340" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B341" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="C341" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D341" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E341" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F341" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="s">
+        <v>134</v>
+      </c>
+      <c r="B342" t="s">
         <v>139</v>
       </c>
-      <c r="B342" t="s">
-        <v>146</v>
-      </c>
       <c r="C342" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D342" t="s">
         <v>9</v>
       </c>
       <c r="E342" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F342" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="s">
+        <v>134</v>
+      </c>
+      <c r="B343" t="s">
         <v>139</v>
       </c>
-      <c r="B343" t="s">
-        <v>146</v>
-      </c>
       <c r="C343" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D343" t="s">
         <v>9</v>
       </c>
       <c r="E343" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F343" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="s">
+        <v>134</v>
+      </c>
+      <c r="B344" t="s">
         <v>139</v>
       </c>
-      <c r="B344" t="s">
-        <v>146</v>
-      </c>
       <c r="C344" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D344" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E344" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F344" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="s">
+        <v>134</v>
+      </c>
+      <c r="B345" t="s">
         <v>139</v>
       </c>
-      <c r="B345" t="s">
-        <v>146</v>
-      </c>
       <c r="C345" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D345" t="s">
         <v>14</v>
       </c>
       <c r="E345" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F345" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="s">
+        <v>134</v>
+      </c>
+      <c r="B346" t="s">
         <v>139</v>
       </c>
-      <c r="B346" t="s">
-        <v>146</v>
-      </c>
       <c r="C346" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D346" t="s">
         <v>14</v>
       </c>
       <c r="E346" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F346" t="s">
-        <v>147</v>
+        <v>140</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="s">
+        <v>134</v>
+      </c>
+      <c r="B347" t="s">
+        <v>139</v>
+      </c>
+      <c r="C347" t="s">
+        <v>82</v>
+      </c>
+      <c r="D347" t="s">
+        <v>14</v>
+      </c>
+      <c r="E347" t="s">
+        <v>13</v>
+      </c>
+      <c r="F347" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="s">
+        <v>134</v>
+      </c>
+      <c r="B348" t="s">
+        <v>141</v>
+      </c>
+      <c r="C348" t="s">
+        <v>82</v>
+      </c>
+      <c r="D348" t="s">
+        <v>9</v>
+      </c>
+      <c r="E348" t="s">
+        <v>10</v>
+      </c>
+      <c r="F348" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="s">
+        <v>134</v>
+      </c>
+      <c r="B349" t="s">
+        <v>141</v>
+      </c>
+      <c r="C349" t="s">
+        <v>82</v>
+      </c>
+      <c r="D349" t="s">
+        <v>9</v>
+      </c>
+      <c r="E349" t="s">
+        <v>12</v>
+      </c>
+      <c r="F349" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="s">
+        <v>134</v>
+      </c>
+      <c r="B350" t="s">
+        <v>141</v>
+      </c>
+      <c r="C350" t="s">
+        <v>82</v>
+      </c>
+      <c r="D350" t="s">
+        <v>9</v>
+      </c>
+      <c r="E350" t="s">
+        <v>13</v>
+      </c>
+      <c r="F350" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="s">
+        <v>134</v>
+      </c>
+      <c r="B351" t="s">
+        <v>141</v>
+      </c>
+      <c r="C351" t="s">
+        <v>82</v>
+      </c>
+      <c r="D351" t="s">
+        <v>14</v>
+      </c>
+      <c r="E351" t="s">
+        <v>10</v>
+      </c>
+      <c r="F351" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="s">
+        <v>134</v>
+      </c>
+      <c r="B352" t="s">
+        <v>141</v>
+      </c>
+      <c r="C352" t="s">
+        <v>82</v>
+      </c>
+      <c r="D352" t="s">
+        <v>14</v>
+      </c>
+      <c r="E352" t="s">
+        <v>12</v>
+      </c>
+      <c r="F352" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="s">
+        <v>134</v>
+      </c>
+      <c r="B353" t="s">
+        <v>141</v>
+      </c>
+      <c r="C353" t="s">
+        <v>82</v>
+      </c>
+      <c r="D353" t="s">
+        <v>14</v>
+      </c>
+      <c r="E353" t="s">
+        <v>13</v>
+      </c>
+      <c r="F353" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/reports/series_reference.xlsx
+++ b/reports/series_reference.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="145">
   <si>
     <t xml:space="preserve">Theme</t>
   </si>
@@ -83,66 +83,69 @@
     <t xml:space="preserve">Top 25 ranking by citizenship (annual)</t>
   </si>
   <si>
+    <t xml:space="preserve">Country of Citizenship, Country Rank  Fr Label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Asylum Claimants by Top 25 Countries of Citizenship (annual ranking), Province/Territory of Claim and Claim Month/Year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Top 25 ranking by citizenship (claim year)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claim Office Type, Country of Citizenship, Country of Citizenship  Fr Label, Country Rank  Fr Label</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Asylum Claimants by Top 25 Countries of Citizenship, Claim Office Type and Claim Year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Top 25 ranking by citizenship (monthly)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Asylum Claimants by Top 25 Countries of Citizenship (monthly ranking), Claim Office Type and Claim Month/Year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Asylum Claimants by Top 25 Countries of Citizenship (monthly ranking), Province/Territory of Claim and Claim Month/Year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Top 25 ranking by citizenship (most recent complete month)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claim Office Type, Top 25 Countries of Citizenship in the Most Recent Month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Asylum Claimants by Top 25 Countries of Citizenship in the Most Recent Month, Claim Office Type and Claim Month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Top 25 Countries of Citizenship in the Most Recent Month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Asylum Claimants by Top 25 Countries of Citizenship in the Most Recent Month, Province/Territory of Claim and Claim Month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Top 25 ranking by citizenship (most recent complete year)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claim Office Type, Top 25 Countries of Citizenship in the Most Recent Complete Year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Asylum Claimants by Top 25 Countries of Citizenship in the Most Recent Complete Year, Claim Office Type and Claim Month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Top 25 Countries of Citizenship in the Most Recent Complete Year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Asylum Claimants by Top 25 Countries of Citizenship in the Most Recent Complete Year, Province/Territory of Claim, Claim Month</t>
+  </si>
+  <si>
+    <t xml:space="preserve">International Mobility Program</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All permits (at December 31)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Country of Citizenship</t>
   </si>
   <si>
-    <t xml:space="preserve">Canada - Asylum Claimants by Top 25 Countries of Citizenship (annual ranking), Province/Territory of Claim and Claim Month/Year</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Top 25 ranking by citizenship (claim year)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claim Office Type, Country of Citizenship</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canada - Asylum Claimants by Top 25 Countries of Citizenship, Claim Office Type and Claim Year</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Top 25 ranking by citizenship (monthly)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canada - Asylum Claimants by Top 25 Countries of Citizenship (monthly ranking), Claim Office Type and Claim Month/Year</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canada - Asylum Claimants by Top 25 Countries of Citizenship (monthly ranking), Province/Territory of Claim and Claim Month/Year</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Top 25 ranking by citizenship (most recent complete month)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claim Office Type, Top 25 Countries of Citizenship in the Most Recent Month</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canada - Asylum Claimants by Top 25 Countries of Citizenship in the Most Recent Month, Claim Office Type and Claim Month</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Top 25 Countries of Citizenship in the Most Recent Month</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canada - Asylum Claimants by Top 25 Countries of Citizenship in the Most Recent Month, Province/Territory of Claim and Claim Month</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Top 25 ranking by citizenship (most recent complete year)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claim Office Type, Top 25 Countries of Citizenship in the Most Recent Complete Year</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canada - Asylum Claimants by Top 25 Countries of Citizenship in the Most Recent Complete Year, Claim Office Type and Claim Month</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Top 25 Countries of Citizenship in the Most Recent Complete Year</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Canada - Asylum Claimants by Top 25 Countries of Citizenship in the Most Recent Complete Year, Province/Territory of Claim, Claim Month</t>
-  </si>
-  <si>
-    <t xml:space="preserve">International Mobility Program</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All permits (at December 31)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Canada – All International Mobility Program (IMP) work permit holders on December 31st by country of citizenship and year</t>
   </si>
   <si>
@@ -288,6 +291,9 @@
   </si>
   <si>
     <t xml:space="preserve">Canada ex-QC - Admissions of French-Speaking Permanent Residents within Canada (excluding Quebec) by Province/Territory and Census Metropolitan Area of Intended Destination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gender, Gender  Fr Label</t>
   </si>
   <si>
     <t xml:space="preserve">Canada ex-QC - Admissions of French-Speaking Permanent Residents within Canada (excluding Quebec) by Province/Territory of Intended Destination and Gender</t>
@@ -1940,7 +1946,7 @@
         <v>42</v>
       </c>
       <c r="C58" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D58" t="s">
         <v>9</v>
@@ -1949,7 +1955,7 @@
         <v>10</v>
       </c>
       <c r="F58" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="59">
@@ -1957,10 +1963,10 @@
         <v>41</v>
       </c>
       <c r="B59" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C59" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D59" t="s">
         <v>9</v>
@@ -1969,7 +1975,7 @@
         <v>10</v>
       </c>
       <c r="F59" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="60">
@@ -1977,10 +1983,10 @@
         <v>41</v>
       </c>
       <c r="B60" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C60" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D60" t="s">
         <v>9</v>
@@ -1989,7 +1995,7 @@
         <v>12</v>
       </c>
       <c r="F60" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="61">
@@ -1997,10 +2003,10 @@
         <v>41</v>
       </c>
       <c r="B61" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C61" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D61" t="s">
         <v>9</v>
@@ -2009,7 +2015,7 @@
         <v>13</v>
       </c>
       <c r="F61" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="62">
@@ -2017,10 +2023,10 @@
         <v>41</v>
       </c>
       <c r="B62" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C62" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D62" t="s">
         <v>9</v>
@@ -2029,7 +2035,7 @@
         <v>10</v>
       </c>
       <c r="F62" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="63">
@@ -2037,10 +2043,10 @@
         <v>41</v>
       </c>
       <c r="B63" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C63" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D63" t="s">
         <v>9</v>
@@ -2049,7 +2055,7 @@
         <v>12</v>
       </c>
       <c r="F63" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="64">
@@ -2057,10 +2063,10 @@
         <v>41</v>
       </c>
       <c r="B64" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C64" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D64" t="s">
         <v>9</v>
@@ -2069,7 +2075,7 @@
         <v>13</v>
       </c>
       <c r="F64" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="65">
@@ -2077,10 +2083,10 @@
         <v>41</v>
       </c>
       <c r="B65" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C65" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D65" t="s">
         <v>14</v>
@@ -2089,7 +2095,7 @@
         <v>10</v>
       </c>
       <c r="F65" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="66">
@@ -2097,10 +2103,10 @@
         <v>41</v>
       </c>
       <c r="B66" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C66" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D66" t="s">
         <v>14</v>
@@ -2109,7 +2115,7 @@
         <v>12</v>
       </c>
       <c r="F66" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="67">
@@ -2117,10 +2123,10 @@
         <v>41</v>
       </c>
       <c r="B67" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C67" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D67" t="s">
         <v>14</v>
@@ -2129,7 +2135,7 @@
         <v>13</v>
       </c>
       <c r="F67" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="68">
@@ -2137,10 +2143,10 @@
         <v>41</v>
       </c>
       <c r="B68" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C68" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D68" t="s">
         <v>9</v>
@@ -2149,7 +2155,7 @@
         <v>10</v>
       </c>
       <c r="F68" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="69">
@@ -2157,10 +2163,10 @@
         <v>41</v>
       </c>
       <c r="B69" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C69" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D69" t="s">
         <v>9</v>
@@ -2169,7 +2175,7 @@
         <v>12</v>
       </c>
       <c r="F69" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="70">
@@ -2177,10 +2183,10 @@
         <v>41</v>
       </c>
       <c r="B70" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C70" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D70" t="s">
         <v>9</v>
@@ -2189,7 +2195,7 @@
         <v>13</v>
       </c>
       <c r="F70" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="71">
@@ -2197,10 +2203,10 @@
         <v>41</v>
       </c>
       <c r="B71" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C71" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D71" t="s">
         <v>14</v>
@@ -2209,7 +2215,7 @@
         <v>10</v>
       </c>
       <c r="F71" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="72">
@@ -2217,10 +2223,10 @@
         <v>41</v>
       </c>
       <c r="B72" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C72" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D72" t="s">
         <v>14</v>
@@ -2229,7 +2235,7 @@
         <v>12</v>
       </c>
       <c r="F72" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="73">
@@ -2237,10 +2243,10 @@
         <v>41</v>
       </c>
       <c r="B73" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C73" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D73" t="s">
         <v>14</v>
@@ -2249,7 +2255,7 @@
         <v>13</v>
       </c>
       <c r="F73" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="74">
@@ -2257,10 +2263,10 @@
         <v>41</v>
       </c>
       <c r="B74" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C74" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D74" t="s">
         <v>9</v>
@@ -2269,7 +2275,7 @@
         <v>10</v>
       </c>
       <c r="F74" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="75">
@@ -2277,10 +2283,10 @@
         <v>41</v>
       </c>
       <c r="B75" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C75" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D75" t="s">
         <v>9</v>
@@ -2289,7 +2295,7 @@
         <v>12</v>
       </c>
       <c r="F75" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="76">
@@ -2297,10 +2303,10 @@
         <v>41</v>
       </c>
       <c r="B76" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C76" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D76" t="s">
         <v>9</v>
@@ -2309,7 +2315,7 @@
         <v>13</v>
       </c>
       <c r="F76" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="77">
@@ -2317,10 +2323,10 @@
         <v>41</v>
       </c>
       <c r="B77" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C77" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D77" t="s">
         <v>14</v>
@@ -2329,7 +2335,7 @@
         <v>10</v>
       </c>
       <c r="F77" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="78">
@@ -2337,10 +2343,10 @@
         <v>41</v>
       </c>
       <c r="B78" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C78" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D78" t="s">
         <v>14</v>
@@ -2349,7 +2355,7 @@
         <v>12</v>
       </c>
       <c r="F78" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="79">
@@ -2357,10 +2363,10 @@
         <v>41</v>
       </c>
       <c r="B79" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C79" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D79" t="s">
         <v>14</v>
@@ -2369,7 +2375,7 @@
         <v>13</v>
       </c>
       <c r="F79" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="80">
@@ -2377,10 +2383,10 @@
         <v>41</v>
       </c>
       <c r="B80" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C80" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D80" t="s">
         <v>9</v>
@@ -2389,7 +2395,7 @@
         <v>10</v>
       </c>
       <c r="F80" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="81">
@@ -2397,10 +2403,10 @@
         <v>41</v>
       </c>
       <c r="B81" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C81" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D81" t="s">
         <v>9</v>
@@ -2409,7 +2415,7 @@
         <v>12</v>
       </c>
       <c r="F81" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="82">
@@ -2417,10 +2423,10 @@
         <v>41</v>
       </c>
       <c r="B82" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C82" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D82" t="s">
         <v>9</v>
@@ -2429,7 +2435,7 @@
         <v>13</v>
       </c>
       <c r="F82" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="83">
@@ -2437,10 +2443,10 @@
         <v>41</v>
       </c>
       <c r="B83" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C83" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D83" t="s">
         <v>9</v>
@@ -2449,7 +2455,7 @@
         <v>10</v>
       </c>
       <c r="F83" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="84">
@@ -2457,10 +2463,10 @@
         <v>41</v>
       </c>
       <c r="B84" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C84" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D84" t="s">
         <v>9</v>
@@ -2469,7 +2475,7 @@
         <v>12</v>
       </c>
       <c r="F84" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="85">
@@ -2477,10 +2483,10 @@
         <v>41</v>
       </c>
       <c r="B85" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C85" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D85" t="s">
         <v>9</v>
@@ -2489,7 +2495,7 @@
         <v>13</v>
       </c>
       <c r="F85" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="86">
@@ -2497,10 +2503,10 @@
         <v>41</v>
       </c>
       <c r="B86" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C86" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D86" t="s">
         <v>9</v>
@@ -2509,7 +2515,7 @@
         <v>10</v>
       </c>
       <c r="F86" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="87">
@@ -2517,10 +2523,10 @@
         <v>41</v>
       </c>
       <c r="B87" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C87" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D87" t="s">
         <v>9</v>
@@ -2529,7 +2535,7 @@
         <v>12</v>
       </c>
       <c r="F87" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="88">
@@ -2537,10 +2543,10 @@
         <v>41</v>
       </c>
       <c r="B88" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C88" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D88" t="s">
         <v>9</v>
@@ -2549,7 +2555,7 @@
         <v>13</v>
       </c>
       <c r="F88" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="89">
@@ -2557,7 +2563,7 @@
         <v>41</v>
       </c>
       <c r="B89" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C89" t="s">
         <v>20</v>
@@ -2569,7 +2575,7 @@
         <v>10</v>
       </c>
       <c r="F89" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="90">
@@ -2577,7 +2583,7 @@
         <v>41</v>
       </c>
       <c r="B90" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C90" t="s">
         <v>20</v>
@@ -2589,7 +2595,7 @@
         <v>12</v>
       </c>
       <c r="F90" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="91">
@@ -2597,7 +2603,7 @@
         <v>41</v>
       </c>
       <c r="B91" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C91" t="s">
         <v>20</v>
@@ -2609,7 +2615,7 @@
         <v>13</v>
       </c>
       <c r="F91" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="92">
@@ -2617,7 +2623,7 @@
         <v>41</v>
       </c>
       <c r="B92" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C92" t="s">
         <v>20</v>
@@ -2629,7 +2635,7 @@
         <v>10</v>
       </c>
       <c r="F92" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="93">
@@ -2637,7 +2643,7 @@
         <v>41</v>
       </c>
       <c r="B93" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C93" t="s">
         <v>20</v>
@@ -2649,7 +2655,7 @@
         <v>12</v>
       </c>
       <c r="F93" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="94">
@@ -2657,7 +2663,7 @@
         <v>41</v>
       </c>
       <c r="B94" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C94" t="s">
         <v>20</v>
@@ -2669,7 +2675,7 @@
         <v>13</v>
       </c>
       <c r="F94" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="95">
@@ -2677,10 +2683,10 @@
         <v>41</v>
       </c>
       <c r="B95" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C95" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D95" t="s">
         <v>9</v>
@@ -2689,7 +2695,7 @@
         <v>10</v>
       </c>
       <c r="F95" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="96">
@@ -2697,10 +2703,10 @@
         <v>41</v>
       </c>
       <c r="B96" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C96" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D96" t="s">
         <v>14</v>
@@ -2709,7 +2715,7 @@
         <v>10</v>
       </c>
       <c r="F96" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="97">
@@ -2717,10 +2723,10 @@
         <v>41</v>
       </c>
       <c r="B97" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C97" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D97" t="s">
         <v>9</v>
@@ -2729,7 +2735,7 @@
         <v>10</v>
       </c>
       <c r="F97" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="98">
@@ -2737,19 +2743,19 @@
         <v>41</v>
       </c>
       <c r="B98" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C98" t="s">
         <v>20</v>
       </c>
       <c r="D98" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E98" t="s">
         <v>10</v>
       </c>
       <c r="F98" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="99">
@@ -2757,19 +2763,19 @@
         <v>41</v>
       </c>
       <c r="B99" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C99" t="s">
         <v>20</v>
       </c>
       <c r="D99" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E99" t="s">
         <v>12</v>
       </c>
       <c r="F99" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="100">
@@ -2777,19 +2783,19 @@
         <v>41</v>
       </c>
       <c r="B100" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C100" t="s">
         <v>20</v>
       </c>
       <c r="D100" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E100" t="s">
         <v>13</v>
       </c>
       <c r="F100" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="101">
@@ -2797,19 +2803,19 @@
         <v>41</v>
       </c>
       <c r="B101" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C101" t="s">
         <v>20</v>
       </c>
       <c r="D101" t="s">
+        <v>66</v>
+      </c>
+      <c r="E101" t="s">
+        <v>10</v>
+      </c>
+      <c r="F101" t="s">
         <v>65</v>
-      </c>
-      <c r="E101" t="s">
-        <v>10</v>
-      </c>
-      <c r="F101" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="102">
@@ -2817,19 +2823,19 @@
         <v>41</v>
       </c>
       <c r="B102" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C102" t="s">
         <v>20</v>
       </c>
       <c r="D102" t="s">
+        <v>66</v>
+      </c>
+      <c r="E102" t="s">
+        <v>12</v>
+      </c>
+      <c r="F102" t="s">
         <v>65</v>
-      </c>
-      <c r="E102" t="s">
-        <v>12</v>
-      </c>
-      <c r="F102" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="103">
@@ -2837,19 +2843,19 @@
         <v>41</v>
       </c>
       <c r="B103" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C103" t="s">
         <v>20</v>
       </c>
       <c r="D103" t="s">
+        <v>66</v>
+      </c>
+      <c r="E103" t="s">
+        <v>13</v>
+      </c>
+      <c r="F103" t="s">
         <v>65</v>
-      </c>
-      <c r="E103" t="s">
-        <v>13</v>
-      </c>
-      <c r="F103" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="104">
@@ -2857,7 +2863,7 @@
         <v>41</v>
       </c>
       <c r="B104" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C104" t="s">
         <v>20</v>
@@ -2869,7 +2875,7 @@
         <v>10</v>
       </c>
       <c r="F104" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="105">
@@ -2877,7 +2883,7 @@
         <v>41</v>
       </c>
       <c r="B105" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C105" t="s">
         <v>20</v>
@@ -2889,7 +2895,7 @@
         <v>12</v>
       </c>
       <c r="F105" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="106">
@@ -2897,7 +2903,7 @@
         <v>41</v>
       </c>
       <c r="B106" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C106" t="s">
         <v>20</v>
@@ -2909,7 +2915,7 @@
         <v>13</v>
       </c>
       <c r="F106" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="107">
@@ -2917,7 +2923,7 @@
         <v>41</v>
       </c>
       <c r="B107" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C107" t="s">
         <v>20</v>
@@ -2929,7 +2935,7 @@
         <v>10</v>
       </c>
       <c r="F107" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="108">
@@ -2937,7 +2943,7 @@
         <v>41</v>
       </c>
       <c r="B108" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C108" t="s">
         <v>20</v>
@@ -2949,7 +2955,7 @@
         <v>12</v>
       </c>
       <c r="F108" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="109">
@@ -2957,7 +2963,7 @@
         <v>41</v>
       </c>
       <c r="B109" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C109" t="s">
         <v>20</v>
@@ -2969,7 +2975,7 @@
         <v>13</v>
       </c>
       <c r="F109" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="110">
@@ -2977,19 +2983,19 @@
         <v>41</v>
       </c>
       <c r="B110" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C110" t="s">
         <v>20</v>
       </c>
       <c r="D110" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E110" t="s">
         <v>10</v>
       </c>
       <c r="F110" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="111">
@@ -2997,7 +3003,7 @@
         <v>41</v>
       </c>
       <c r="B111" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C111" t="s">
         <v>20</v>
@@ -3009,7 +3015,7 @@
         <v>10</v>
       </c>
       <c r="F111" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="112">
@@ -3017,7 +3023,7 @@
         <v>41</v>
       </c>
       <c r="B112" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C112" t="s">
         <v>20</v>
@@ -3029,7 +3035,7 @@
         <v>10</v>
       </c>
       <c r="F112" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="113">
@@ -3037,19 +3043,19 @@
         <v>41</v>
       </c>
       <c r="B113" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C113" t="s">
         <v>20</v>
       </c>
       <c r="D113" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E113" t="s">
         <v>10</v>
       </c>
       <c r="F113" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="114">
@@ -3057,19 +3063,19 @@
         <v>41</v>
       </c>
       <c r="B114" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C114" t="s">
         <v>20</v>
       </c>
       <c r="D114" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E114" t="s">
         <v>12</v>
       </c>
       <c r="F114" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="115">
@@ -3077,19 +3083,19 @@
         <v>41</v>
       </c>
       <c r="B115" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C115" t="s">
         <v>20</v>
       </c>
       <c r="D115" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E115" t="s">
         <v>13</v>
       </c>
       <c r="F115" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="116">
@@ -3097,7 +3103,7 @@
         <v>41</v>
       </c>
       <c r="B116" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C116" t="s">
         <v>20</v>
@@ -3109,7 +3115,7 @@
         <v>10</v>
       </c>
       <c r="F116" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="117">
@@ -3117,7 +3123,7 @@
         <v>41</v>
       </c>
       <c r="B117" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C117" t="s">
         <v>20</v>
@@ -3129,7 +3135,7 @@
         <v>12</v>
       </c>
       <c r="F117" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="118">
@@ -3137,7 +3143,7 @@
         <v>41</v>
       </c>
       <c r="B118" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C118" t="s">
         <v>20</v>
@@ -3149,7 +3155,7 @@
         <v>13</v>
       </c>
       <c r="F118" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="119">
@@ -3157,7 +3163,7 @@
         <v>41</v>
       </c>
       <c r="B119" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C119" t="s">
         <v>20</v>
@@ -3169,7 +3175,7 @@
         <v>10</v>
       </c>
       <c r="F119" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="120">
@@ -3177,7 +3183,7 @@
         <v>41</v>
       </c>
       <c r="B120" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C120" t="s">
         <v>20</v>
@@ -3189,7 +3195,7 @@
         <v>12</v>
       </c>
       <c r="F120" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="121">
@@ -3197,7 +3203,7 @@
         <v>41</v>
       </c>
       <c r="B121" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C121" t="s">
         <v>20</v>
@@ -3209,18 +3215,18 @@
         <v>13</v>
       </c>
       <c r="F121" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B122" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C122" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D122" t="s">
         <v>9</v>
@@ -3229,18 +3235,18 @@
         <v>10</v>
       </c>
       <c r="F122" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B123" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C123" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D123" t="s">
         <v>9</v>
@@ -3249,18 +3255,18 @@
         <v>12</v>
       </c>
       <c r="F123" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B124" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C124" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D124" t="s">
         <v>9</v>
@@ -3269,18 +3275,18 @@
         <v>13</v>
       </c>
       <c r="F124" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B125" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C125" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D125" t="s">
         <v>9</v>
@@ -3289,18 +3295,18 @@
         <v>10</v>
       </c>
       <c r="F125" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B126" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C126" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D126" t="s">
         <v>9</v>
@@ -3309,18 +3315,18 @@
         <v>12</v>
       </c>
       <c r="F126" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B127" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C127" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D127" t="s">
         <v>9</v>
@@ -3329,18 +3335,18 @@
         <v>13</v>
       </c>
       <c r="F127" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B128" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C128" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D128" t="s">
         <v>9</v>
@@ -3349,18 +3355,18 @@
         <v>10</v>
       </c>
       <c r="F128" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B129" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C129" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D129" t="s">
         <v>9</v>
@@ -3369,18 +3375,18 @@
         <v>12</v>
       </c>
       <c r="F129" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B130" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C130" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D130" t="s">
         <v>9</v>
@@ -3389,18 +3395,18 @@
         <v>13</v>
       </c>
       <c r="F130" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B131" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C131" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D131" t="s">
         <v>14</v>
@@ -3409,18 +3415,18 @@
         <v>10</v>
       </c>
       <c r="F131" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B132" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C132" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D132" t="s">
         <v>14</v>
@@ -3429,18 +3435,18 @@
         <v>12</v>
       </c>
       <c r="F132" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B133" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C133" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D133" t="s">
         <v>14</v>
@@ -3449,75 +3455,75 @@
         <v>13</v>
       </c>
       <c r="F133" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B134" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C134" t="s">
         <v>20</v>
       </c>
       <c r="D134" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E134" t="s">
         <v>10</v>
       </c>
       <c r="F134" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B135" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C135" t="s">
         <v>20</v>
       </c>
       <c r="D135" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E135" t="s">
         <v>12</v>
       </c>
       <c r="F135" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B136" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C136" t="s">
         <v>20</v>
       </c>
       <c r="D136" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E136" t="s">
         <v>13</v>
       </c>
       <c r="F136" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B137" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C137" t="s">
         <v>20</v>
@@ -3529,15 +3535,15 @@
         <v>10</v>
       </c>
       <c r="F137" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B138" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C138" t="s">
         <v>20</v>
@@ -3549,15 +3555,15 @@
         <v>12</v>
       </c>
       <c r="F138" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B139" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C139" t="s">
         <v>20</v>
@@ -3569,15 +3575,15 @@
         <v>13</v>
       </c>
       <c r="F139" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B140" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C140" t="s">
         <v>20</v>
@@ -3589,15 +3595,15 @@
         <v>10</v>
       </c>
       <c r="F140" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B141" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C141" t="s">
         <v>20</v>
@@ -3609,15 +3615,15 @@
         <v>12</v>
       </c>
       <c r="F141" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B142" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C142" t="s">
         <v>20</v>
@@ -3629,15 +3635,15 @@
         <v>13</v>
       </c>
       <c r="F142" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B143" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C143" t="s">
         <v>17</v>
@@ -3649,15 +3655,15 @@
         <v>10</v>
       </c>
       <c r="F143" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B144" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C144" t="s">
         <v>17</v>
@@ -3669,15 +3675,15 @@
         <v>12</v>
       </c>
       <c r="F144" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B145" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C145" t="s">
         <v>17</v>
@@ -3689,15 +3695,15 @@
         <v>13</v>
       </c>
       <c r="F145" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B146" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C146" t="s">
         <v>17</v>
@@ -3709,15 +3715,15 @@
         <v>10</v>
       </c>
       <c r="F146" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B147" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C147" t="s">
         <v>17</v>
@@ -3729,15 +3735,15 @@
         <v>12</v>
       </c>
       <c r="F147" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B148" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C148" t="s">
         <v>17</v>
@@ -3749,18 +3755,18 @@
         <v>13</v>
       </c>
       <c r="F148" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B149" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C149" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D149" t="s">
         <v>9</v>
@@ -3769,18 +3775,18 @@
         <v>10</v>
       </c>
       <c r="F149" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B150" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C150" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D150" t="s">
         <v>9</v>
@@ -3789,18 +3795,18 @@
         <v>12</v>
       </c>
       <c r="F150" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B151" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C151" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D151" t="s">
         <v>9</v>
@@ -3809,18 +3815,18 @@
         <v>13</v>
       </c>
       <c r="F151" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B152" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C152" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D152" t="s">
         <v>14</v>
@@ -3829,18 +3835,18 @@
         <v>10</v>
       </c>
       <c r="F152" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B153" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C153" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D153" t="s">
         <v>14</v>
@@ -3849,18 +3855,18 @@
         <v>12</v>
       </c>
       <c r="F153" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B154" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C154" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D154" t="s">
         <v>14</v>
@@ -3869,18 +3875,18 @@
         <v>13</v>
       </c>
       <c r="F154" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B155" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C155" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D155" t="s">
         <v>9</v>
@@ -3889,18 +3895,18 @@
         <v>10</v>
       </c>
       <c r="F155" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B156" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C156" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D156" t="s">
         <v>9</v>
@@ -3909,18 +3915,18 @@
         <v>12</v>
       </c>
       <c r="F156" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B157" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C157" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D157" t="s">
         <v>9</v>
@@ -3929,18 +3935,18 @@
         <v>13</v>
       </c>
       <c r="F157" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B158" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C158" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D158" t="s">
         <v>14</v>
@@ -3949,18 +3955,18 @@
         <v>10</v>
       </c>
       <c r="F158" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B159" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C159" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D159" t="s">
         <v>14</v>
@@ -3969,18 +3975,18 @@
         <v>12</v>
       </c>
       <c r="F159" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B160" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C160" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D160" t="s">
         <v>14</v>
@@ -3989,135 +3995,135 @@
         <v>13</v>
       </c>
       <c r="F160" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B161" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C161" t="s">
         <v>20</v>
       </c>
       <c r="D161" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E161" t="s">
         <v>10</v>
       </c>
       <c r="F161" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B162" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C162" t="s">
         <v>20</v>
       </c>
       <c r="D162" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E162" t="s">
         <v>12</v>
       </c>
       <c r="F162" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B163" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C163" t="s">
         <v>20</v>
       </c>
       <c r="D163" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E163" t="s">
         <v>13</v>
       </c>
       <c r="F163" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B164" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C164" t="s">
         <v>20</v>
       </c>
       <c r="D164" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E164" t="s">
         <v>10</v>
       </c>
       <c r="F164" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B165" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C165" t="s">
         <v>20</v>
       </c>
       <c r="D165" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E165" t="s">
         <v>12</v>
       </c>
       <c r="F165" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B166" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C166" t="s">
         <v>20</v>
       </c>
       <c r="D166" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E166" t="s">
         <v>13</v>
       </c>
       <c r="F166" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B167" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C167" t="s">
         <v>20</v>
@@ -4129,15 +4135,15 @@
         <v>10</v>
       </c>
       <c r="F167" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B168" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C168" t="s">
         <v>20</v>
@@ -4149,15 +4155,15 @@
         <v>12</v>
       </c>
       <c r="F168" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B169" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C169" t="s">
         <v>20</v>
@@ -4169,15 +4175,15 @@
         <v>13</v>
       </c>
       <c r="F169" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B170" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C170" t="s">
         <v>20</v>
@@ -4189,15 +4195,15 @@
         <v>10</v>
       </c>
       <c r="F170" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B171" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C171" t="s">
         <v>20</v>
@@ -4209,15 +4215,15 @@
         <v>12</v>
       </c>
       <c r="F171" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B172" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C172" t="s">
         <v>20</v>
@@ -4229,18 +4235,18 @@
         <v>13</v>
       </c>
       <c r="F172" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B173" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C173" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D173" t="s">
         <v>9</v>
@@ -4249,18 +4255,18 @@
         <v>10</v>
       </c>
       <c r="F173" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B174" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C174" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D174" t="s">
         <v>9</v>
@@ -4269,18 +4275,18 @@
         <v>12</v>
       </c>
       <c r="F174" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B175" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C175" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D175" t="s">
         <v>9</v>
@@ -4289,18 +4295,18 @@
         <v>13</v>
       </c>
       <c r="F175" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B176" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C176" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D176" t="s">
         <v>14</v>
@@ -4309,18 +4315,18 @@
         <v>10</v>
       </c>
       <c r="F176" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B177" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C177" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D177" t="s">
         <v>14</v>
@@ -4329,18 +4335,18 @@
         <v>12</v>
       </c>
       <c r="F177" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B178" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C178" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D178" t="s">
         <v>14</v>
@@ -4349,18 +4355,18 @@
         <v>13</v>
       </c>
       <c r="F178" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B179" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C179" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D179" t="s">
         <v>9</v>
@@ -4369,18 +4375,18 @@
         <v>10</v>
       </c>
       <c r="F179" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B180" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C180" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D180" t="s">
         <v>9</v>
@@ -4389,18 +4395,18 @@
         <v>12</v>
       </c>
       <c r="F180" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B181" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C181" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D181" t="s">
         <v>9</v>
@@ -4409,18 +4415,18 @@
         <v>13</v>
       </c>
       <c r="F181" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B182" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C182" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D182" t="s">
         <v>14</v>
@@ -4429,18 +4435,18 @@
         <v>10</v>
       </c>
       <c r="F182" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B183" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C183" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D183" t="s">
         <v>14</v>
@@ -4449,18 +4455,18 @@
         <v>12</v>
       </c>
       <c r="F183" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B184" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C184" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D184" t="s">
         <v>14</v>
@@ -4469,75 +4475,75 @@
         <v>13</v>
       </c>
       <c r="F184" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B185" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C185" t="s">
         <v>20</v>
       </c>
       <c r="D185" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E185" t="s">
         <v>10</v>
       </c>
       <c r="F185" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B186" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C186" t="s">
         <v>20</v>
       </c>
       <c r="D186" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E186" t="s">
         <v>12</v>
       </c>
       <c r="F186" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B187" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C187" t="s">
         <v>20</v>
       </c>
       <c r="D187" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E187" t="s">
         <v>13</v>
       </c>
       <c r="F187" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B188" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C188" t="s">
         <v>20</v>
@@ -4549,15 +4555,15 @@
         <v>10</v>
       </c>
       <c r="F188" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B189" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C189" t="s">
         <v>20</v>
@@ -4569,15 +4575,15 @@
         <v>12</v>
       </c>
       <c r="F189" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B190" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C190" t="s">
         <v>20</v>
@@ -4589,15 +4595,15 @@
         <v>13</v>
       </c>
       <c r="F190" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B191" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C191" t="s">
         <v>20</v>
@@ -4609,15 +4615,15 @@
         <v>10</v>
       </c>
       <c r="F191" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B192" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C192" t="s">
         <v>20</v>
@@ -4629,15 +4635,15 @@
         <v>12</v>
       </c>
       <c r="F192" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B193" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C193" t="s">
         <v>20</v>
@@ -4649,18 +4655,18 @@
         <v>13</v>
       </c>
       <c r="F193" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B194" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C194" t="s">
-        <v>17</v>
+        <v>93</v>
       </c>
       <c r="D194" t="s">
         <v>9</v>
@@ -4669,18 +4675,18 @@
         <v>10</v>
       </c>
       <c r="F194" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B195" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C195" t="s">
-        <v>17</v>
+        <v>93</v>
       </c>
       <c r="D195" t="s">
         <v>9</v>
@@ -4689,18 +4695,18 @@
         <v>12</v>
       </c>
       <c r="F195" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B196" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C196" t="s">
-        <v>17</v>
+        <v>93</v>
       </c>
       <c r="D196" t="s">
         <v>9</v>
@@ -4709,18 +4715,18 @@
         <v>13</v>
       </c>
       <c r="F196" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B197" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C197" t="s">
-        <v>17</v>
+        <v>93</v>
       </c>
       <c r="D197" t="s">
         <v>14</v>
@@ -4729,18 +4735,18 @@
         <v>10</v>
       </c>
       <c r="F197" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B198" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C198" t="s">
-        <v>17</v>
+        <v>93</v>
       </c>
       <c r="D198" t="s">
         <v>14</v>
@@ -4749,18 +4755,18 @@
         <v>12</v>
       </c>
       <c r="F198" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B199" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C199" t="s">
-        <v>17</v>
+        <v>93</v>
       </c>
       <c r="D199" t="s">
         <v>14</v>
@@ -4769,18 +4775,18 @@
         <v>13</v>
       </c>
       <c r="F199" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B200" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C200" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D200" t="s">
         <v>9</v>
@@ -4789,18 +4795,18 @@
         <v>10</v>
       </c>
       <c r="F200" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B201" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C201" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D201" t="s">
         <v>9</v>
@@ -4809,18 +4815,18 @@
         <v>12</v>
       </c>
       <c r="F201" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B202" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C202" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D202" t="s">
         <v>9</v>
@@ -4829,18 +4835,18 @@
         <v>13</v>
       </c>
       <c r="F202" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B203" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C203" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D203" t="s">
         <v>14</v>
@@ -4849,18 +4855,18 @@
         <v>10</v>
       </c>
       <c r="F203" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B204" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C204" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D204" t="s">
         <v>14</v>
@@ -4869,18 +4875,18 @@
         <v>12</v>
       </c>
       <c r="F204" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B205" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C205" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D205" t="s">
         <v>14</v>
@@ -4889,18 +4895,18 @@
         <v>13</v>
       </c>
       <c r="F205" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B206" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C206" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D206" t="s">
         <v>9</v>
@@ -4909,18 +4915,18 @@
         <v>10</v>
       </c>
       <c r="F206" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B207" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C207" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D207" t="s">
         <v>9</v>
@@ -4929,18 +4935,18 @@
         <v>12</v>
       </c>
       <c r="F207" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B208" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C208" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D208" t="s">
         <v>9</v>
@@ -4949,18 +4955,18 @@
         <v>13</v>
       </c>
       <c r="F208" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B209" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C209" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D209" t="s">
         <v>9</v>
@@ -4969,18 +4975,18 @@
         <v>10</v>
       </c>
       <c r="F209" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B210" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C210" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D210" t="s">
         <v>9</v>
@@ -4989,18 +4995,18 @@
         <v>12</v>
       </c>
       <c r="F210" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B211" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C211" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D211" t="s">
         <v>9</v>
@@ -5009,18 +5015,18 @@
         <v>13</v>
       </c>
       <c r="F211" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B212" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C212" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D212" t="s">
         <v>9</v>
@@ -5029,18 +5035,18 @@
         <v>10</v>
       </c>
       <c r="F212" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B213" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C213" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D213" t="s">
         <v>9</v>
@@ -5049,18 +5055,18 @@
         <v>12</v>
       </c>
       <c r="F213" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B214" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C214" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D214" t="s">
         <v>9</v>
@@ -5069,18 +5075,18 @@
         <v>13</v>
       </c>
       <c r="F214" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B215" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C215" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D215" t="s">
         <v>14</v>
@@ -5089,18 +5095,18 @@
         <v>10</v>
       </c>
       <c r="F215" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B216" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C216" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D216" t="s">
         <v>14</v>
@@ -5109,18 +5115,18 @@
         <v>12</v>
       </c>
       <c r="F216" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B217" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C217" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D217" t="s">
         <v>14</v>
@@ -5129,75 +5135,75 @@
         <v>13</v>
       </c>
       <c r="F217" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B218" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C218" t="s">
         <v>20</v>
       </c>
       <c r="D218" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E218" t="s">
         <v>10</v>
       </c>
       <c r="F218" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B219" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C219" t="s">
         <v>20</v>
       </c>
       <c r="D219" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E219" t="s">
         <v>12</v>
       </c>
       <c r="F219" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B220" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C220" t="s">
         <v>20</v>
       </c>
       <c r="D220" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E220" t="s">
         <v>13</v>
       </c>
       <c r="F220" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B221" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C221" t="s">
         <v>20</v>
@@ -5209,15 +5215,15 @@
         <v>10</v>
       </c>
       <c r="F221" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B222" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C222" t="s">
         <v>20</v>
@@ -5229,15 +5235,15 @@
         <v>12</v>
       </c>
       <c r="F222" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B223" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C223" t="s">
         <v>20</v>
@@ -5249,15 +5255,15 @@
         <v>13</v>
       </c>
       <c r="F223" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B224" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C224" t="s">
         <v>20</v>
@@ -5269,15 +5275,15 @@
         <v>10</v>
       </c>
       <c r="F224" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B225" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C225" t="s">
         <v>20</v>
@@ -5289,15 +5295,15 @@
         <v>12</v>
       </c>
       <c r="F225" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B226" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C226" t="s">
         <v>20</v>
@@ -5309,15 +5315,15 @@
         <v>13</v>
       </c>
       <c r="F226" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B227" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C227" t="s">
         <v>17</v>
@@ -5329,15 +5335,15 @@
         <v>10</v>
       </c>
       <c r="F227" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B228" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C228" t="s">
         <v>17</v>
@@ -5349,15 +5355,15 @@
         <v>12</v>
       </c>
       <c r="F228" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B229" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C229" t="s">
         <v>17</v>
@@ -5369,15 +5375,15 @@
         <v>13</v>
       </c>
       <c r="F229" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B230" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C230" t="s">
         <v>17</v>
@@ -5389,15 +5395,15 @@
         <v>10</v>
       </c>
       <c r="F230" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B231" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C231" t="s">
         <v>17</v>
@@ -5409,15 +5415,15 @@
         <v>12</v>
       </c>
       <c r="F231" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B232" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C232" t="s">
         <v>17</v>
@@ -5429,18 +5435,18 @@
         <v>13</v>
       </c>
       <c r="F232" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B233" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C233" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D233" t="s">
         <v>9</v>
@@ -5449,18 +5455,18 @@
         <v>10</v>
       </c>
       <c r="F233" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B234" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C234" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D234" t="s">
         <v>9</v>
@@ -5469,18 +5475,18 @@
         <v>10</v>
       </c>
       <c r="F234" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B235" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C235" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D235" t="s">
         <v>9</v>
@@ -5489,18 +5495,18 @@
         <v>12</v>
       </c>
       <c r="F235" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B236" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C236" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D236" t="s">
         <v>9</v>
@@ -5509,18 +5515,18 @@
         <v>12</v>
       </c>
       <c r="F236" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B237" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C237" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D237" t="s">
         <v>9</v>
@@ -5529,18 +5535,18 @@
         <v>13</v>
       </c>
       <c r="F237" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B238" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C238" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D238" t="s">
         <v>9</v>
@@ -5549,18 +5555,18 @@
         <v>13</v>
       </c>
       <c r="F238" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B239" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C239" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D239" t="s">
         <v>14</v>
@@ -5569,18 +5575,18 @@
         <v>10</v>
       </c>
       <c r="F239" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B240" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C240" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D240" t="s">
         <v>14</v>
@@ -5589,18 +5595,18 @@
         <v>10</v>
       </c>
       <c r="F240" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B241" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C241" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D241" t="s">
         <v>14</v>
@@ -5609,18 +5615,18 @@
         <v>12</v>
       </c>
       <c r="F241" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B242" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C242" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D242" t="s">
         <v>14</v>
@@ -5629,18 +5635,18 @@
         <v>12</v>
       </c>
       <c r="F242" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B243" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C243" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D243" t="s">
         <v>14</v>
@@ -5649,18 +5655,18 @@
         <v>13</v>
       </c>
       <c r="F243" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B244" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C244" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D244" t="s">
         <v>14</v>
@@ -5669,18 +5675,18 @@
         <v>13</v>
       </c>
       <c r="F244" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B245" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C245" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D245" t="s">
         <v>9</v>
@@ -5689,18 +5695,18 @@
         <v>10</v>
       </c>
       <c r="F245" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B246" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C246" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D246" t="s">
         <v>9</v>
@@ -5709,18 +5715,18 @@
         <v>12</v>
       </c>
       <c r="F246" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B247" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C247" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D247" t="s">
         <v>9</v>
@@ -5729,18 +5735,18 @@
         <v>13</v>
       </c>
       <c r="F247" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B248" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C248" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D248" t="s">
         <v>9</v>
@@ -5749,19 +5755,19 @@
         <v>10</v>
       </c>
       <c r="F248" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B249" t="s">
+        <v>107</v>
+      </c>
+      <c r="C249" t="s">
         <v>105</v>
       </c>
-      <c r="C249" t="s">
-        <v>103</v>
-      </c>
       <c r="D249" t="s">
         <v>9</v>
       </c>
@@ -5769,19 +5775,19 @@
         <v>10</v>
       </c>
       <c r="F249" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B250" t="s">
+        <v>107</v>
+      </c>
+      <c r="C250" t="s">
         <v>105</v>
       </c>
-      <c r="C250" t="s">
-        <v>103</v>
-      </c>
       <c r="D250" t="s">
         <v>14</v>
       </c>
@@ -5789,18 +5795,18 @@
         <v>10</v>
       </c>
       <c r="F250" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B251" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C251" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D251" t="s">
         <v>9</v>
@@ -5809,12 +5815,12 @@
         <v>10</v>
       </c>
       <c r="F251" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B252" t="s">
         <v>42</v>
@@ -5823,18 +5829,18 @@
         <v>20</v>
       </c>
       <c r="D252" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E252" t="s">
         <v>10</v>
       </c>
       <c r="F252" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B253" t="s">
         <v>42</v>
@@ -5843,18 +5849,18 @@
         <v>20</v>
       </c>
       <c r="D253" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E253" t="s">
         <v>12</v>
       </c>
       <c r="F253" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B254" t="s">
         <v>42</v>
@@ -5863,18 +5869,18 @@
         <v>20</v>
       </c>
       <c r="D254" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E254" t="s">
         <v>13</v>
       </c>
       <c r="F254" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B255" t="s">
         <v>42</v>
@@ -5889,12 +5895,12 @@
         <v>10</v>
       </c>
       <c r="F255" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B256" t="s">
         <v>42</v>
@@ -5909,12 +5915,12 @@
         <v>12</v>
       </c>
       <c r="F256" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B257" t="s">
         <v>42</v>
@@ -5929,12 +5935,12 @@
         <v>13</v>
       </c>
       <c r="F257" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B258" t="s">
         <v>42</v>
@@ -5949,12 +5955,12 @@
         <v>10</v>
       </c>
       <c r="F258" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B259" t="s">
         <v>42</v>
@@ -5969,12 +5975,12 @@
         <v>12</v>
       </c>
       <c r="F259" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B260" t="s">
         <v>42</v>
@@ -5989,18 +5995,18 @@
         <v>13</v>
       </c>
       <c r="F260" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B261" t="s">
         <v>42</v>
       </c>
       <c r="C261" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D261" t="s">
         <v>9</v>
@@ -6009,18 +6015,18 @@
         <v>10</v>
       </c>
       <c r="F261" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B262" t="s">
         <v>42</v>
       </c>
       <c r="C262" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D262" t="s">
         <v>9</v>
@@ -6029,18 +6035,18 @@
         <v>12</v>
       </c>
       <c r="F262" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B263" t="s">
         <v>42</v>
       </c>
       <c r="C263" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D263" t="s">
         <v>9</v>
@@ -6049,18 +6055,18 @@
         <v>13</v>
       </c>
       <c r="F263" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B264" t="s">
         <v>42</v>
       </c>
       <c r="C264" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D264" t="s">
         <v>14</v>
@@ -6069,18 +6075,18 @@
         <v>10</v>
       </c>
       <c r="F264" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B265" t="s">
         <v>42</v>
       </c>
       <c r="C265" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D265" t="s">
         <v>14</v>
@@ -6089,18 +6095,18 @@
         <v>12</v>
       </c>
       <c r="F265" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B266" t="s">
         <v>42</v>
       </c>
       <c r="C266" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D266" t="s">
         <v>14</v>
@@ -6109,18 +6115,18 @@
         <v>13</v>
       </c>
       <c r="F266" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B267" t="s">
         <v>42</v>
       </c>
       <c r="C267" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D267" t="s">
         <v>9</v>
@@ -6129,18 +6135,18 @@
         <v>10</v>
       </c>
       <c r="F267" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B268" t="s">
         <v>42</v>
       </c>
       <c r="C268" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D268" t="s">
         <v>9</v>
@@ -6149,18 +6155,18 @@
         <v>10</v>
       </c>
       <c r="F268" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B269" t="s">
         <v>42</v>
       </c>
       <c r="C269" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D269" t="s">
         <v>14</v>
@@ -6169,18 +6175,18 @@
         <v>10</v>
       </c>
       <c r="F269" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B270" t="s">
         <v>42</v>
       </c>
       <c r="C270" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D270" t="s">
         <v>9</v>
@@ -6189,18 +6195,18 @@
         <v>10</v>
       </c>
       <c r="F270" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B271" t="s">
         <v>42</v>
       </c>
       <c r="C271" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D271" t="s">
         <v>9</v>
@@ -6209,18 +6215,18 @@
         <v>12</v>
       </c>
       <c r="F271" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B272" t="s">
         <v>42</v>
       </c>
       <c r="C272" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D272" t="s">
         <v>9</v>
@@ -6229,18 +6235,18 @@
         <v>13</v>
       </c>
       <c r="F272" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B273" t="s">
         <v>42</v>
       </c>
       <c r="C273" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D273" t="s">
         <v>14</v>
@@ -6249,18 +6255,18 @@
         <v>10</v>
       </c>
       <c r="F273" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B274" t="s">
         <v>42</v>
       </c>
       <c r="C274" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D274" t="s">
         <v>14</v>
@@ -6269,18 +6275,18 @@
         <v>12</v>
       </c>
       <c r="F274" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B275" t="s">
         <v>42</v>
       </c>
       <c r="C275" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D275" t="s">
         <v>14</v>
@@ -6289,18 +6295,18 @@
         <v>13</v>
       </c>
       <c r="F275" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B276" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C276" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D276" t="s">
         <v>9</v>
@@ -6309,18 +6315,18 @@
         <v>10</v>
       </c>
       <c r="F276" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B277" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C277" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D277" t="s">
         <v>9</v>
@@ -6329,18 +6335,18 @@
         <v>12</v>
       </c>
       <c r="F277" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B278" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C278" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D278" t="s">
         <v>9</v>
@@ -6349,15 +6355,15 @@
         <v>13</v>
       </c>
       <c r="F278" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B279" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C279" t="s">
         <v>17</v>
@@ -6369,15 +6375,15 @@
         <v>10</v>
       </c>
       <c r="F279" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B280" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C280" t="s">
         <v>17</v>
@@ -6389,15 +6395,15 @@
         <v>12</v>
       </c>
       <c r="F280" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B281" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C281" t="s">
         <v>17</v>
@@ -6409,15 +6415,15 @@
         <v>13</v>
       </c>
       <c r="F281" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B282" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C282" t="s">
         <v>17</v>
@@ -6429,15 +6435,15 @@
         <v>10</v>
       </c>
       <c r="F282" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B283" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C283" t="s">
         <v>17</v>
@@ -6449,15 +6455,15 @@
         <v>12</v>
       </c>
       <c r="F283" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B284" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C284" t="s">
         <v>17</v>
@@ -6469,18 +6475,18 @@
         <v>13</v>
       </c>
       <c r="F284" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B285" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C285" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D285" t="s">
         <v>9</v>
@@ -6489,18 +6495,18 @@
         <v>10</v>
       </c>
       <c r="F285" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B286" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C286" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D286" t="s">
         <v>9</v>
@@ -6509,18 +6515,18 @@
         <v>12</v>
       </c>
       <c r="F286" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B287" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C287" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D287" t="s">
         <v>9</v>
@@ -6529,18 +6535,18 @@
         <v>13</v>
       </c>
       <c r="F287" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B288" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C288" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D288" t="s">
         <v>14</v>
@@ -6549,18 +6555,18 @@
         <v>10</v>
       </c>
       <c r="F288" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B289" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C289" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D289" t="s">
         <v>14</v>
@@ -6569,18 +6575,18 @@
         <v>12</v>
       </c>
       <c r="F289" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B290" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C290" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D290" t="s">
         <v>14</v>
@@ -6589,18 +6595,18 @@
         <v>13</v>
       </c>
       <c r="F290" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B291" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C291" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D291" t="s">
         <v>9</v>
@@ -6609,18 +6615,18 @@
         <v>10</v>
       </c>
       <c r="F291" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B292" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C292" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D292" t="s">
         <v>9</v>
@@ -6629,18 +6635,18 @@
         <v>12</v>
       </c>
       <c r="F292" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B293" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C293" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D293" t="s">
         <v>9</v>
@@ -6649,18 +6655,18 @@
         <v>13</v>
       </c>
       <c r="F293" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B294" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C294" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D294" t="s">
         <v>14</v>
@@ -6669,18 +6675,18 @@
         <v>10</v>
       </c>
       <c r="F294" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B295" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C295" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D295" t="s">
         <v>14</v>
@@ -6689,18 +6695,18 @@
         <v>12</v>
       </c>
       <c r="F295" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B296" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C296" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D296" t="s">
         <v>14</v>
@@ -6709,18 +6715,18 @@
         <v>13</v>
       </c>
       <c r="F296" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B297" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C297" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D297" t="s">
         <v>9</v>
@@ -6729,18 +6735,18 @@
         <v>10</v>
       </c>
       <c r="F297" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B298" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C298" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D298" t="s">
         <v>9</v>
@@ -6749,18 +6755,18 @@
         <v>12</v>
       </c>
       <c r="F298" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B299" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C299" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D299" t="s">
         <v>9</v>
@@ -6769,18 +6775,18 @@
         <v>13</v>
       </c>
       <c r="F299" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B300" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C300" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D300" t="s">
         <v>14</v>
@@ -6789,18 +6795,18 @@
         <v>10</v>
       </c>
       <c r="F300" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B301" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C301" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D301" t="s">
         <v>14</v>
@@ -6809,18 +6815,18 @@
         <v>12</v>
       </c>
       <c r="F301" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B302" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C302" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D302" t="s">
         <v>14</v>
@@ -6829,18 +6835,18 @@
         <v>13</v>
       </c>
       <c r="F302" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B303" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C303" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D303" t="s">
         <v>9</v>
@@ -6849,18 +6855,18 @@
         <v>10</v>
       </c>
       <c r="F303" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B304" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C304" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D304" t="s">
         <v>9</v>
@@ -6869,18 +6875,18 @@
         <v>12</v>
       </c>
       <c r="F304" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B305" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C305" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D305" t="s">
         <v>9</v>
@@ -6889,18 +6895,18 @@
         <v>13</v>
       </c>
       <c r="F305" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B306" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C306" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D306" t="s">
         <v>14</v>
@@ -6909,18 +6915,18 @@
         <v>10</v>
       </c>
       <c r="F306" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B307" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C307" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D307" t="s">
         <v>14</v>
@@ -6929,18 +6935,18 @@
         <v>12</v>
       </c>
       <c r="F307" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B308" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C308" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D308" t="s">
         <v>14</v>
@@ -6949,18 +6955,18 @@
         <v>13</v>
       </c>
       <c r="F308" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B309" t="s">
         <v>42</v>
       </c>
       <c r="C309" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D309" t="s">
         <v>9</v>
@@ -6969,18 +6975,18 @@
         <v>10</v>
       </c>
       <c r="F309" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B310" t="s">
         <v>42</v>
       </c>
       <c r="C310" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D310" t="s">
         <v>14</v>
@@ -6989,18 +6995,18 @@
         <v>10</v>
       </c>
       <c r="F310" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B311" t="s">
         <v>42</v>
       </c>
       <c r="C311" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D311" t="s">
         <v>9</v>
@@ -7009,18 +7015,18 @@
         <v>10</v>
       </c>
       <c r="F311" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B312" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C312" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D312" t="s">
         <v>9</v>
@@ -7029,18 +7035,18 @@
         <v>10</v>
       </c>
       <c r="F312" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B313" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C313" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D313" t="s">
         <v>9</v>
@@ -7049,18 +7055,18 @@
         <v>12</v>
       </c>
       <c r="F313" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B314" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C314" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D314" t="s">
         <v>9</v>
@@ -7069,18 +7075,18 @@
         <v>13</v>
       </c>
       <c r="F314" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B315" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C315" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D315" t="s">
         <v>9</v>
@@ -7089,18 +7095,18 @@
         <v>10</v>
       </c>
       <c r="F315" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B316" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C316" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D316" t="s">
         <v>9</v>
@@ -7109,18 +7115,18 @@
         <v>12</v>
       </c>
       <c r="F316" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B317" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C317" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D317" t="s">
         <v>9</v>
@@ -7129,18 +7135,18 @@
         <v>13</v>
       </c>
       <c r="F317" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B318" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C318" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D318" t="s">
         <v>14</v>
@@ -7149,18 +7155,18 @@
         <v>10</v>
       </c>
       <c r="F318" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B319" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C319" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D319" t="s">
         <v>14</v>
@@ -7169,18 +7175,18 @@
         <v>12</v>
       </c>
       <c r="F319" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B320" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C320" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D320" t="s">
         <v>14</v>
@@ -7189,18 +7195,18 @@
         <v>13</v>
       </c>
       <c r="F320" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B321" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C321" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D321" t="s">
         <v>9</v>
@@ -7209,18 +7215,18 @@
         <v>10</v>
       </c>
       <c r="F321" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B322" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C322" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D322" t="s">
         <v>9</v>
@@ -7229,18 +7235,18 @@
         <v>12</v>
       </c>
       <c r="F322" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B323" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C323" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D323" t="s">
         <v>9</v>
@@ -7249,18 +7255,18 @@
         <v>13</v>
       </c>
       <c r="F323" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B324" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C324" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D324" t="s">
         <v>14</v>
@@ -7269,18 +7275,18 @@
         <v>10</v>
       </c>
       <c r="F324" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B325" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C325" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D325" t="s">
         <v>14</v>
@@ -7289,18 +7295,18 @@
         <v>12</v>
       </c>
       <c r="F325" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B326" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C326" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D326" t="s">
         <v>14</v>
@@ -7309,18 +7315,18 @@
         <v>13</v>
       </c>
       <c r="F326" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B327" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C327" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D327" t="s">
         <v>9</v>
@@ -7329,18 +7335,18 @@
         <v>10</v>
       </c>
       <c r="F327" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B328" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C328" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D328" t="s">
         <v>9</v>
@@ -7349,18 +7355,18 @@
         <v>12</v>
       </c>
       <c r="F328" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B329" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C329" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="D329" t="s">
         <v>9</v>
@@ -7369,18 +7375,18 @@
         <v>13</v>
       </c>
       <c r="F329" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B330" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C330" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D330" t="s">
         <v>9</v>
@@ -7389,18 +7395,18 @@
         <v>10</v>
       </c>
       <c r="F330" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B331" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C331" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D331" t="s">
         <v>9</v>
@@ -7409,18 +7415,18 @@
         <v>12</v>
       </c>
       <c r="F331" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B332" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C332" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D332" t="s">
         <v>9</v>
@@ -7429,18 +7435,18 @@
         <v>13</v>
       </c>
       <c r="F332" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B333" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C333" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D333" t="s">
         <v>14</v>
@@ -7449,18 +7455,18 @@
         <v>10</v>
       </c>
       <c r="F333" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B334" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C334" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D334" t="s">
         <v>14</v>
@@ -7469,18 +7475,18 @@
         <v>12</v>
       </c>
       <c r="F334" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B335" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C335" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D335" t="s">
         <v>14</v>
@@ -7489,18 +7495,18 @@
         <v>13</v>
       </c>
       <c r="F335" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B336" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C336" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D336" t="s">
         <v>9</v>
@@ -7509,18 +7515,18 @@
         <v>10</v>
       </c>
       <c r="F336" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B337" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C337" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D337" t="s">
         <v>9</v>
@@ -7529,18 +7535,18 @@
         <v>12</v>
       </c>
       <c r="F337" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B338" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C338" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D338" t="s">
         <v>9</v>
@@ -7549,18 +7555,18 @@
         <v>13</v>
       </c>
       <c r="F338" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B339" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C339" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D339" t="s">
         <v>14</v>
@@ -7569,18 +7575,18 @@
         <v>10</v>
       </c>
       <c r="F339" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B340" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C340" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D340" t="s">
         <v>14</v>
@@ -7589,18 +7595,18 @@
         <v>12</v>
       </c>
       <c r="F340" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B341" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C341" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D341" t="s">
         <v>14</v>
@@ -7609,18 +7615,18 @@
         <v>13</v>
       </c>
       <c r="F341" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B342" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C342" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D342" t="s">
         <v>9</v>
@@ -7629,18 +7635,18 @@
         <v>10</v>
       </c>
       <c r="F342" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B343" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C343" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D343" t="s">
         <v>9</v>
@@ -7649,18 +7655,18 @@
         <v>12</v>
       </c>
       <c r="F343" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B344" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C344" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D344" t="s">
         <v>9</v>
@@ -7669,18 +7675,18 @@
         <v>13</v>
       </c>
       <c r="F344" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B345" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C345" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D345" t="s">
         <v>14</v>
@@ -7689,18 +7695,18 @@
         <v>10</v>
       </c>
       <c r="F345" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B346" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C346" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D346" t="s">
         <v>14</v>
@@ -7709,18 +7715,18 @@
         <v>12</v>
       </c>
       <c r="F346" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B347" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C347" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D347" t="s">
         <v>14</v>
@@ -7729,18 +7735,18 @@
         <v>13</v>
       </c>
       <c r="F347" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B348" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C348" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D348" t="s">
         <v>9</v>
@@ -7749,18 +7755,18 @@
         <v>10</v>
       </c>
       <c r="F348" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B349" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C349" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D349" t="s">
         <v>9</v>
@@ -7769,18 +7775,18 @@
         <v>12</v>
       </c>
       <c r="F349" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B350" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C350" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D350" t="s">
         <v>9</v>
@@ -7789,18 +7795,18 @@
         <v>13</v>
       </c>
       <c r="F350" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B351" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C351" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D351" t="s">
         <v>14</v>
@@ -7809,18 +7815,18 @@
         <v>10</v>
       </c>
       <c r="F351" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B352" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C352" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D352" t="s">
         <v>14</v>
@@ -7829,18 +7835,18 @@
         <v>12</v>
       </c>
       <c r="F352" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B353" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C353" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D353" t="s">
         <v>14</v>
@@ -7849,7 +7855,7 @@
         <v>13</v>
       </c>
       <c r="F353" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/reports/series_reference.xlsx
+++ b/reports/series_reference.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="143">
   <si>
     <t xml:space="preserve">Theme</t>
   </si>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">Top 25 ranking by citizenship (annual)</t>
   </si>
   <si>
-    <t xml:space="preserve">Country of Citizenship, Country Rank  Fr Label</t>
+    <t xml:space="preserve">Country of Citizenship</t>
   </si>
   <si>
     <t xml:space="preserve">Canada - Asylum Claimants by Top 25 Countries of Citizenship (annual ranking), Province/Territory of Claim and Claim Month/Year</t>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">Top 25 ranking by citizenship (claim year)</t>
   </si>
   <si>
-    <t xml:space="preserve">Claim Office Type, Country of Citizenship, Country of Citizenship  Fr Label, Country Rank  Fr Label</t>
+    <t xml:space="preserve">Claim Office Type, Country of Citizenship</t>
   </si>
   <si>
     <t xml:space="preserve">Canada - Asylum Claimants by Top 25 Countries of Citizenship, Claim Office Type and Claim Year</t>
@@ -143,9 +143,6 @@
     <t xml:space="preserve">All permits (at December 31)</t>
   </si>
   <si>
-    <t xml:space="preserve">Country of Citizenship</t>
-  </si>
-  <si>
     <t xml:space="preserve">Canada – All International Mobility Program (IMP) work permit holders on December 31st by country of citizenship and year</t>
   </si>
   <si>
@@ -293,9 +290,6 @@
     <t xml:space="preserve">Canada ex-QC - Admissions of French-Speaking Permanent Residents within Canada (excluding Quebec) by Province/Territory and Census Metropolitan Area of Intended Destination</t>
   </si>
   <si>
-    <t xml:space="preserve">Gender, Gender  Fr Label</t>
-  </si>
-  <si>
     <t xml:space="preserve">Canada ex-QC - Admissions of French-Speaking Permanent Residents within Canada (excluding Quebec) by Province/Territory of Intended Destination and Gender</t>
   </si>
   <si>
@@ -383,7 +377,7 @@
     <t xml:space="preserve">Post-Secondary (Year became effective)</t>
   </si>
   <si>
-    <t xml:space="preserve">Citizenship, Year in which Permit(s) Became Effective</t>
+    <t xml:space="preserve">Citizenship, Institution Type and Citizenship</t>
   </si>
   <si>
     <t xml:space="preserve">Canada - Post-Secondary by P/T of Designated Learning Institution Type, Citizenship and Year in which permit(s) became effective</t>
@@ -1946,16 +1940,16 @@
         <v>42</v>
       </c>
       <c r="C58" t="s">
+        <v>23</v>
+      </c>
+      <c r="D58" t="s">
+        <v>9</v>
+      </c>
+      <c r="E58" t="s">
+        <v>10</v>
+      </c>
+      <c r="F58" t="s">
         <v>43</v>
-      </c>
-      <c r="D58" t="s">
-        <v>9</v>
-      </c>
-      <c r="E58" t="s">
-        <v>10</v>
-      </c>
-      <c r="F58" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="59">
@@ -1963,19 +1957,19 @@
         <v>41</v>
       </c>
       <c r="B59" t="s">
+        <v>44</v>
+      </c>
+      <c r="C59" t="s">
         <v>45</v>
       </c>
-      <c r="C59" t="s">
+      <c r="D59" t="s">
+        <v>9</v>
+      </c>
+      <c r="E59" t="s">
+        <v>10</v>
+      </c>
+      <c r="F59" t="s">
         <v>46</v>
-      </c>
-      <c r="D59" t="s">
-        <v>9</v>
-      </c>
-      <c r="E59" t="s">
-        <v>10</v>
-      </c>
-      <c r="F59" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="60">
@@ -1983,19 +1977,19 @@
         <v>41</v>
       </c>
       <c r="B60" t="s">
+        <v>44</v>
+      </c>
+      <c r="C60" t="s">
         <v>45</v>
       </c>
-      <c r="C60" t="s">
+      <c r="D60" t="s">
+        <v>9</v>
+      </c>
+      <c r="E60" t="s">
+        <v>12</v>
+      </c>
+      <c r="F60" t="s">
         <v>46</v>
-      </c>
-      <c r="D60" t="s">
-        <v>9</v>
-      </c>
-      <c r="E60" t="s">
-        <v>12</v>
-      </c>
-      <c r="F60" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="61">
@@ -2003,19 +1997,19 @@
         <v>41</v>
       </c>
       <c r="B61" t="s">
+        <v>44</v>
+      </c>
+      <c r="C61" t="s">
         <v>45</v>
       </c>
-      <c r="C61" t="s">
+      <c r="D61" t="s">
+        <v>9</v>
+      </c>
+      <c r="E61" t="s">
+        <v>13</v>
+      </c>
+      <c r="F61" t="s">
         <v>46</v>
-      </c>
-      <c r="D61" t="s">
-        <v>9</v>
-      </c>
-      <c r="E61" t="s">
-        <v>13</v>
-      </c>
-      <c r="F61" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="62">
@@ -2023,19 +2017,19 @@
         <v>41</v>
       </c>
       <c r="B62" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C62" t="s">
+        <v>47</v>
+      </c>
+      <c r="D62" t="s">
+        <v>9</v>
+      </c>
+      <c r="E62" t="s">
+        <v>10</v>
+      </c>
+      <c r="F62" t="s">
         <v>48</v>
-      </c>
-      <c r="D62" t="s">
-        <v>9</v>
-      </c>
-      <c r="E62" t="s">
-        <v>10</v>
-      </c>
-      <c r="F62" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="63">
@@ -2043,19 +2037,19 @@
         <v>41</v>
       </c>
       <c r="B63" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C63" t="s">
+        <v>47</v>
+      </c>
+      <c r="D63" t="s">
+        <v>9</v>
+      </c>
+      <c r="E63" t="s">
+        <v>12</v>
+      </c>
+      <c r="F63" t="s">
         <v>48</v>
-      </c>
-      <c r="D63" t="s">
-        <v>9</v>
-      </c>
-      <c r="E63" t="s">
-        <v>12</v>
-      </c>
-      <c r="F63" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="64">
@@ -2063,19 +2057,19 @@
         <v>41</v>
       </c>
       <c r="B64" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C64" t="s">
+        <v>47</v>
+      </c>
+      <c r="D64" t="s">
+        <v>9</v>
+      </c>
+      <c r="E64" t="s">
+        <v>13</v>
+      </c>
+      <c r="F64" t="s">
         <v>48</v>
-      </c>
-      <c r="D64" t="s">
-        <v>9</v>
-      </c>
-      <c r="E64" t="s">
-        <v>13</v>
-      </c>
-      <c r="F64" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="65">
@@ -2083,19 +2077,19 @@
         <v>41</v>
       </c>
       <c r="B65" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C65" t="s">
+        <v>47</v>
+      </c>
+      <c r="D65" t="s">
+        <v>14</v>
+      </c>
+      <c r="E65" t="s">
+        <v>10</v>
+      </c>
+      <c r="F65" t="s">
         <v>48</v>
-      </c>
-      <c r="D65" t="s">
-        <v>14</v>
-      </c>
-      <c r="E65" t="s">
-        <v>10</v>
-      </c>
-      <c r="F65" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="66">
@@ -2103,19 +2097,19 @@
         <v>41</v>
       </c>
       <c r="B66" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C66" t="s">
+        <v>47</v>
+      </c>
+      <c r="D66" t="s">
+        <v>14</v>
+      </c>
+      <c r="E66" t="s">
+        <v>12</v>
+      </c>
+      <c r="F66" t="s">
         <v>48</v>
-      </c>
-      <c r="D66" t="s">
-        <v>14</v>
-      </c>
-      <c r="E66" t="s">
-        <v>12</v>
-      </c>
-      <c r="F66" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="67">
@@ -2123,19 +2117,19 @@
         <v>41</v>
       </c>
       <c r="B67" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C67" t="s">
+        <v>47</v>
+      </c>
+      <c r="D67" t="s">
+        <v>14</v>
+      </c>
+      <c r="E67" t="s">
+        <v>13</v>
+      </c>
+      <c r="F67" t="s">
         <v>48</v>
-      </c>
-      <c r="D67" t="s">
-        <v>14</v>
-      </c>
-      <c r="E67" t="s">
-        <v>13</v>
-      </c>
-      <c r="F67" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="68">
@@ -2143,19 +2137,19 @@
         <v>41</v>
       </c>
       <c r="B68" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C68" t="s">
+        <v>49</v>
+      </c>
+      <c r="D68" t="s">
+        <v>9</v>
+      </c>
+      <c r="E68" t="s">
+        <v>10</v>
+      </c>
+      <c r="F68" t="s">
         <v>50</v>
-      </c>
-      <c r="D68" t="s">
-        <v>9</v>
-      </c>
-      <c r="E68" t="s">
-        <v>10</v>
-      </c>
-      <c r="F68" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="69">
@@ -2163,19 +2157,19 @@
         <v>41</v>
       </c>
       <c r="B69" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C69" t="s">
+        <v>49</v>
+      </c>
+      <c r="D69" t="s">
+        <v>9</v>
+      </c>
+      <c r="E69" t="s">
+        <v>12</v>
+      </c>
+      <c r="F69" t="s">
         <v>50</v>
-      </c>
-      <c r="D69" t="s">
-        <v>9</v>
-      </c>
-      <c r="E69" t="s">
-        <v>12</v>
-      </c>
-      <c r="F69" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="70">
@@ -2183,19 +2177,19 @@
         <v>41</v>
       </c>
       <c r="B70" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C70" t="s">
+        <v>49</v>
+      </c>
+      <c r="D70" t="s">
+        <v>9</v>
+      </c>
+      <c r="E70" t="s">
+        <v>13</v>
+      </c>
+      <c r="F70" t="s">
         <v>50</v>
-      </c>
-      <c r="D70" t="s">
-        <v>9</v>
-      </c>
-      <c r="E70" t="s">
-        <v>13</v>
-      </c>
-      <c r="F70" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="71">
@@ -2203,19 +2197,19 @@
         <v>41</v>
       </c>
       <c r="B71" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C71" t="s">
+        <v>49</v>
+      </c>
+      <c r="D71" t="s">
+        <v>14</v>
+      </c>
+      <c r="E71" t="s">
+        <v>10</v>
+      </c>
+      <c r="F71" t="s">
         <v>50</v>
-      </c>
-      <c r="D71" t="s">
-        <v>14</v>
-      </c>
-      <c r="E71" t="s">
-        <v>10</v>
-      </c>
-      <c r="F71" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="72">
@@ -2223,19 +2217,19 @@
         <v>41</v>
       </c>
       <c r="B72" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C72" t="s">
+        <v>49</v>
+      </c>
+      <c r="D72" t="s">
+        <v>14</v>
+      </c>
+      <c r="E72" t="s">
+        <v>12</v>
+      </c>
+      <c r="F72" t="s">
         <v>50</v>
-      </c>
-      <c r="D72" t="s">
-        <v>14</v>
-      </c>
-      <c r="E72" t="s">
-        <v>12</v>
-      </c>
-      <c r="F72" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="73">
@@ -2243,19 +2237,19 @@
         <v>41</v>
       </c>
       <c r="B73" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C73" t="s">
+        <v>49</v>
+      </c>
+      <c r="D73" t="s">
+        <v>14</v>
+      </c>
+      <c r="E73" t="s">
+        <v>13</v>
+      </c>
+      <c r="F73" t="s">
         <v>50</v>
-      </c>
-      <c r="D73" t="s">
-        <v>14</v>
-      </c>
-      <c r="E73" t="s">
-        <v>13</v>
-      </c>
-      <c r="F73" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="74">
@@ -2263,19 +2257,19 @@
         <v>41</v>
       </c>
       <c r="B74" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C74" t="s">
+        <v>51</v>
+      </c>
+      <c r="D74" t="s">
+        <v>9</v>
+      </c>
+      <c r="E74" t="s">
+        <v>10</v>
+      </c>
+      <c r="F74" t="s">
         <v>52</v>
-      </c>
-      <c r="D74" t="s">
-        <v>9</v>
-      </c>
-      <c r="E74" t="s">
-        <v>10</v>
-      </c>
-      <c r="F74" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="75">
@@ -2283,19 +2277,19 @@
         <v>41</v>
       </c>
       <c r="B75" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C75" t="s">
+        <v>51</v>
+      </c>
+      <c r="D75" t="s">
+        <v>9</v>
+      </c>
+      <c r="E75" t="s">
+        <v>12</v>
+      </c>
+      <c r="F75" t="s">
         <v>52</v>
-      </c>
-      <c r="D75" t="s">
-        <v>9</v>
-      </c>
-      <c r="E75" t="s">
-        <v>12</v>
-      </c>
-      <c r="F75" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="76">
@@ -2303,19 +2297,19 @@
         <v>41</v>
       </c>
       <c r="B76" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C76" t="s">
+        <v>51</v>
+      </c>
+      <c r="D76" t="s">
+        <v>9</v>
+      </c>
+      <c r="E76" t="s">
+        <v>13</v>
+      </c>
+      <c r="F76" t="s">
         <v>52</v>
-      </c>
-      <c r="D76" t="s">
-        <v>9</v>
-      </c>
-      <c r="E76" t="s">
-        <v>13</v>
-      </c>
-      <c r="F76" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="77">
@@ -2323,19 +2317,19 @@
         <v>41</v>
       </c>
       <c r="B77" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C77" t="s">
+        <v>51</v>
+      </c>
+      <c r="D77" t="s">
+        <v>14</v>
+      </c>
+      <c r="E77" t="s">
+        <v>10</v>
+      </c>
+      <c r="F77" t="s">
         <v>52</v>
-      </c>
-      <c r="D77" t="s">
-        <v>14</v>
-      </c>
-      <c r="E77" t="s">
-        <v>10</v>
-      </c>
-      <c r="F77" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="78">
@@ -2343,19 +2337,19 @@
         <v>41</v>
       </c>
       <c r="B78" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C78" t="s">
+        <v>51</v>
+      </c>
+      <c r="D78" t="s">
+        <v>14</v>
+      </c>
+      <c r="E78" t="s">
+        <v>12</v>
+      </c>
+      <c r="F78" t="s">
         <v>52</v>
-      </c>
-      <c r="D78" t="s">
-        <v>14</v>
-      </c>
-      <c r="E78" t="s">
-        <v>12</v>
-      </c>
-      <c r="F78" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="79">
@@ -2363,19 +2357,19 @@
         <v>41</v>
       </c>
       <c r="B79" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C79" t="s">
+        <v>51</v>
+      </c>
+      <c r="D79" t="s">
+        <v>14</v>
+      </c>
+      <c r="E79" t="s">
+        <v>13</v>
+      </c>
+      <c r="F79" t="s">
         <v>52</v>
-      </c>
-      <c r="D79" t="s">
-        <v>14</v>
-      </c>
-      <c r="E79" t="s">
-        <v>13</v>
-      </c>
-      <c r="F79" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="80">
@@ -2383,10 +2377,10 @@
         <v>41</v>
       </c>
       <c r="B80" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C80" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D80" t="s">
         <v>9</v>
@@ -2395,7 +2389,7 @@
         <v>10</v>
       </c>
       <c r="F80" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="81">
@@ -2403,10 +2397,10 @@
         <v>41</v>
       </c>
       <c r="B81" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C81" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D81" t="s">
         <v>9</v>
@@ -2415,7 +2409,7 @@
         <v>12</v>
       </c>
       <c r="F81" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="82">
@@ -2423,10 +2417,10 @@
         <v>41</v>
       </c>
       <c r="B82" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C82" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D82" t="s">
         <v>9</v>
@@ -2435,7 +2429,7 @@
         <v>13</v>
       </c>
       <c r="F82" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="83">
@@ -2443,19 +2437,19 @@
         <v>41</v>
       </c>
       <c r="B83" t="s">
+        <v>54</v>
+      </c>
+      <c r="C83" t="s">
+        <v>23</v>
+      </c>
+      <c r="D83" t="s">
+        <v>9</v>
+      </c>
+      <c r="E83" t="s">
+        <v>10</v>
+      </c>
+      <c r="F83" t="s">
         <v>55</v>
-      </c>
-      <c r="C83" t="s">
-        <v>43</v>
-      </c>
-      <c r="D83" t="s">
-        <v>9</v>
-      </c>
-      <c r="E83" t="s">
-        <v>10</v>
-      </c>
-      <c r="F83" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="84">
@@ -2463,19 +2457,19 @@
         <v>41</v>
       </c>
       <c r="B84" t="s">
+        <v>54</v>
+      </c>
+      <c r="C84" t="s">
+        <v>23</v>
+      </c>
+      <c r="D84" t="s">
+        <v>9</v>
+      </c>
+      <c r="E84" t="s">
+        <v>12</v>
+      </c>
+      <c r="F84" t="s">
         <v>55</v>
-      </c>
-      <c r="C84" t="s">
-        <v>43</v>
-      </c>
-      <c r="D84" t="s">
-        <v>9</v>
-      </c>
-      <c r="E84" t="s">
-        <v>12</v>
-      </c>
-      <c r="F84" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="85">
@@ -2483,19 +2477,19 @@
         <v>41</v>
       </c>
       <c r="B85" t="s">
+        <v>54</v>
+      </c>
+      <c r="C85" t="s">
+        <v>23</v>
+      </c>
+      <c r="D85" t="s">
+        <v>9</v>
+      </c>
+      <c r="E85" t="s">
+        <v>13</v>
+      </c>
+      <c r="F85" t="s">
         <v>55</v>
-      </c>
-      <c r="C85" t="s">
-        <v>43</v>
-      </c>
-      <c r="D85" t="s">
-        <v>9</v>
-      </c>
-      <c r="E85" t="s">
-        <v>13</v>
-      </c>
-      <c r="F85" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="86">
@@ -2503,19 +2497,19 @@
         <v>41</v>
       </c>
       <c r="B86" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C86" t="s">
+        <v>56</v>
+      </c>
+      <c r="D86" t="s">
+        <v>9</v>
+      </c>
+      <c r="E86" t="s">
+        <v>10</v>
+      </c>
+      <c r="F86" t="s">
         <v>57</v>
-      </c>
-      <c r="D86" t="s">
-        <v>9</v>
-      </c>
-      <c r="E86" t="s">
-        <v>10</v>
-      </c>
-      <c r="F86" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="87">
@@ -2523,19 +2517,19 @@
         <v>41</v>
       </c>
       <c r="B87" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C87" t="s">
+        <v>56</v>
+      </c>
+      <c r="D87" t="s">
+        <v>9</v>
+      </c>
+      <c r="E87" t="s">
+        <v>12</v>
+      </c>
+      <c r="F87" t="s">
         <v>57</v>
-      </c>
-      <c r="D87" t="s">
-        <v>9</v>
-      </c>
-      <c r="E87" t="s">
-        <v>12</v>
-      </c>
-      <c r="F87" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="88">
@@ -2543,19 +2537,19 @@
         <v>41</v>
       </c>
       <c r="B88" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C88" t="s">
+        <v>56</v>
+      </c>
+      <c r="D88" t="s">
+        <v>9</v>
+      </c>
+      <c r="E88" t="s">
+        <v>13</v>
+      </c>
+      <c r="F88" t="s">
         <v>57</v>
-      </c>
-      <c r="D88" t="s">
-        <v>9</v>
-      </c>
-      <c r="E88" t="s">
-        <v>13</v>
-      </c>
-      <c r="F88" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="89">
@@ -2563,7 +2557,7 @@
         <v>41</v>
       </c>
       <c r="B89" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C89" t="s">
         <v>20</v>
@@ -2575,7 +2569,7 @@
         <v>10</v>
       </c>
       <c r="F89" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="90">
@@ -2583,7 +2577,7 @@
         <v>41</v>
       </c>
       <c r="B90" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C90" t="s">
         <v>20</v>
@@ -2595,7 +2589,7 @@
         <v>12</v>
       </c>
       <c r="F90" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="91">
@@ -2603,7 +2597,7 @@
         <v>41</v>
       </c>
       <c r="B91" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C91" t="s">
         <v>20</v>
@@ -2615,7 +2609,7 @@
         <v>13</v>
       </c>
       <c r="F91" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="92">
@@ -2623,7 +2617,7 @@
         <v>41</v>
       </c>
       <c r="B92" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C92" t="s">
         <v>20</v>
@@ -2635,7 +2629,7 @@
         <v>10</v>
       </c>
       <c r="F92" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="93">
@@ -2643,7 +2637,7 @@
         <v>41</v>
       </c>
       <c r="B93" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C93" t="s">
         <v>20</v>
@@ -2655,7 +2649,7 @@
         <v>12</v>
       </c>
       <c r="F93" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="94">
@@ -2663,7 +2657,7 @@
         <v>41</v>
       </c>
       <c r="B94" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C94" t="s">
         <v>20</v>
@@ -2675,7 +2669,7 @@
         <v>13</v>
       </c>
       <c r="F94" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="95">
@@ -2683,19 +2677,19 @@
         <v>41</v>
       </c>
       <c r="B95" t="s">
+        <v>59</v>
+      </c>
+      <c r="C95" t="s">
+        <v>49</v>
+      </c>
+      <c r="D95" t="s">
+        <v>9</v>
+      </c>
+      <c r="E95" t="s">
+        <v>10</v>
+      </c>
+      <c r="F95" t="s">
         <v>60</v>
-      </c>
-      <c r="C95" t="s">
-        <v>50</v>
-      </c>
-      <c r="D95" t="s">
-        <v>9</v>
-      </c>
-      <c r="E95" t="s">
-        <v>10</v>
-      </c>
-      <c r="F95" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="96">
@@ -2703,19 +2697,19 @@
         <v>41</v>
       </c>
       <c r="B96" t="s">
+        <v>59</v>
+      </c>
+      <c r="C96" t="s">
+        <v>49</v>
+      </c>
+      <c r="D96" t="s">
+        <v>14</v>
+      </c>
+      <c r="E96" t="s">
+        <v>10</v>
+      </c>
+      <c r="F96" t="s">
         <v>60</v>
-      </c>
-      <c r="C96" t="s">
-        <v>50</v>
-      </c>
-      <c r="D96" t="s">
-        <v>14</v>
-      </c>
-      <c r="E96" t="s">
-        <v>10</v>
-      </c>
-      <c r="F96" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="97">
@@ -2723,10 +2717,10 @@
         <v>41</v>
       </c>
       <c r="B97" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C97" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D97" t="s">
         <v>9</v>
@@ -2735,7 +2729,7 @@
         <v>10</v>
       </c>
       <c r="F97" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="98">
@@ -2743,19 +2737,19 @@
         <v>41</v>
       </c>
       <c r="B98" t="s">
+        <v>62</v>
+      </c>
+      <c r="C98" t="s">
+        <v>20</v>
+      </c>
+      <c r="D98" t="s">
         <v>63</v>
       </c>
-      <c r="C98" t="s">
-        <v>20</v>
-      </c>
-      <c r="D98" t="s">
+      <c r="E98" t="s">
+        <v>10</v>
+      </c>
+      <c r="F98" t="s">
         <v>64</v>
-      </c>
-      <c r="E98" t="s">
-        <v>10</v>
-      </c>
-      <c r="F98" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="99">
@@ -2763,19 +2757,19 @@
         <v>41</v>
       </c>
       <c r="B99" t="s">
+        <v>62</v>
+      </c>
+      <c r="C99" t="s">
+        <v>20</v>
+      </c>
+      <c r="D99" t="s">
         <v>63</v>
       </c>
-      <c r="C99" t="s">
-        <v>20</v>
-      </c>
-      <c r="D99" t="s">
+      <c r="E99" t="s">
+        <v>12</v>
+      </c>
+      <c r="F99" t="s">
         <v>64</v>
-      </c>
-      <c r="E99" t="s">
-        <v>12</v>
-      </c>
-      <c r="F99" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="100">
@@ -2783,19 +2777,19 @@
         <v>41</v>
       </c>
       <c r="B100" t="s">
+        <v>62</v>
+      </c>
+      <c r="C100" t="s">
+        <v>20</v>
+      </c>
+      <c r="D100" t="s">
         <v>63</v>
       </c>
-      <c r="C100" t="s">
-        <v>20</v>
-      </c>
-      <c r="D100" t="s">
+      <c r="E100" t="s">
+        <v>13</v>
+      </c>
+      <c r="F100" t="s">
         <v>64</v>
-      </c>
-      <c r="E100" t="s">
-        <v>13</v>
-      </c>
-      <c r="F100" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="101">
@@ -2803,19 +2797,19 @@
         <v>41</v>
       </c>
       <c r="B101" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C101" t="s">
         <v>20</v>
       </c>
       <c r="D101" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E101" t="s">
         <v>10</v>
       </c>
       <c r="F101" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="102">
@@ -2823,19 +2817,19 @@
         <v>41</v>
       </c>
       <c r="B102" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C102" t="s">
         <v>20</v>
       </c>
       <c r="D102" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E102" t="s">
         <v>12</v>
       </c>
       <c r="F102" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="103">
@@ -2843,19 +2837,19 @@
         <v>41</v>
       </c>
       <c r="B103" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C103" t="s">
         <v>20</v>
       </c>
       <c r="D103" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E103" t="s">
         <v>13</v>
       </c>
       <c r="F103" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="104">
@@ -2863,7 +2857,7 @@
         <v>41</v>
       </c>
       <c r="B104" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C104" t="s">
         <v>20</v>
@@ -2875,7 +2869,7 @@
         <v>10</v>
       </c>
       <c r="F104" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="105">
@@ -2883,7 +2877,7 @@
         <v>41</v>
       </c>
       <c r="B105" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C105" t="s">
         <v>20</v>
@@ -2895,7 +2889,7 @@
         <v>12</v>
       </c>
       <c r="F105" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="106">
@@ -2903,7 +2897,7 @@
         <v>41</v>
       </c>
       <c r="B106" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C106" t="s">
         <v>20</v>
@@ -2915,7 +2909,7 @@
         <v>13</v>
       </c>
       <c r="F106" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="107">
@@ -2923,7 +2917,7 @@
         <v>41</v>
       </c>
       <c r="B107" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C107" t="s">
         <v>20</v>
@@ -2935,7 +2929,7 @@
         <v>10</v>
       </c>
       <c r="F107" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="108">
@@ -2943,7 +2937,7 @@
         <v>41</v>
       </c>
       <c r="B108" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C108" t="s">
         <v>20</v>
@@ -2955,7 +2949,7 @@
         <v>12</v>
       </c>
       <c r="F108" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="109">
@@ -2963,7 +2957,7 @@
         <v>41</v>
       </c>
       <c r="B109" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C109" t="s">
         <v>20</v>
@@ -2975,7 +2969,7 @@
         <v>13</v>
       </c>
       <c r="F109" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="110">
@@ -2983,19 +2977,19 @@
         <v>41</v>
       </c>
       <c r="B110" t="s">
+        <v>66</v>
+      </c>
+      <c r="C110" t="s">
+        <v>20</v>
+      </c>
+      <c r="D110" t="s">
         <v>67</v>
       </c>
-      <c r="C110" t="s">
-        <v>20</v>
-      </c>
-      <c r="D110" t="s">
+      <c r="E110" t="s">
+        <v>10</v>
+      </c>
+      <c r="F110" t="s">
         <v>68</v>
-      </c>
-      <c r="E110" t="s">
-        <v>10</v>
-      </c>
-      <c r="F110" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="111">
@@ -3003,7 +2997,7 @@
         <v>41</v>
       </c>
       <c r="B111" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C111" t="s">
         <v>20</v>
@@ -3015,7 +3009,7 @@
         <v>10</v>
       </c>
       <c r="F111" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="112">
@@ -3023,7 +3017,7 @@
         <v>41</v>
       </c>
       <c r="B112" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C112" t="s">
         <v>20</v>
@@ -3035,7 +3029,7 @@
         <v>10</v>
       </c>
       <c r="F112" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="113">
@@ -3043,19 +3037,19 @@
         <v>41</v>
       </c>
       <c r="B113" t="s">
+        <v>69</v>
+      </c>
+      <c r="C113" t="s">
+        <v>20</v>
+      </c>
+      <c r="D113" t="s">
+        <v>67</v>
+      </c>
+      <c r="E113" t="s">
+        <v>10</v>
+      </c>
+      <c r="F113" t="s">
         <v>70</v>
-      </c>
-      <c r="C113" t="s">
-        <v>20</v>
-      </c>
-      <c r="D113" t="s">
-        <v>68</v>
-      </c>
-      <c r="E113" t="s">
-        <v>10</v>
-      </c>
-      <c r="F113" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="114">
@@ -3063,19 +3057,19 @@
         <v>41</v>
       </c>
       <c r="B114" t="s">
+        <v>69</v>
+      </c>
+      <c r="C114" t="s">
+        <v>20</v>
+      </c>
+      <c r="D114" t="s">
+        <v>67</v>
+      </c>
+      <c r="E114" t="s">
+        <v>12</v>
+      </c>
+      <c r="F114" t="s">
         <v>70</v>
-      </c>
-      <c r="C114" t="s">
-        <v>20</v>
-      </c>
-      <c r="D114" t="s">
-        <v>68</v>
-      </c>
-      <c r="E114" t="s">
-        <v>12</v>
-      </c>
-      <c r="F114" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="115">
@@ -3083,19 +3077,19 @@
         <v>41</v>
       </c>
       <c r="B115" t="s">
+        <v>69</v>
+      </c>
+      <c r="C115" t="s">
+        <v>20</v>
+      </c>
+      <c r="D115" t="s">
+        <v>67</v>
+      </c>
+      <c r="E115" t="s">
+        <v>13</v>
+      </c>
+      <c r="F115" t="s">
         <v>70</v>
-      </c>
-      <c r="C115" t="s">
-        <v>20</v>
-      </c>
-      <c r="D115" t="s">
-        <v>68</v>
-      </c>
-      <c r="E115" t="s">
-        <v>13</v>
-      </c>
-      <c r="F115" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="116">
@@ -3103,19 +3097,19 @@
         <v>41</v>
       </c>
       <c r="B116" t="s">
+        <v>69</v>
+      </c>
+      <c r="C116" t="s">
+        <v>20</v>
+      </c>
+      <c r="D116" t="s">
+        <v>9</v>
+      </c>
+      <c r="E116" t="s">
+        <v>10</v>
+      </c>
+      <c r="F116" t="s">
         <v>70</v>
-      </c>
-      <c r="C116" t="s">
-        <v>20</v>
-      </c>
-      <c r="D116" t="s">
-        <v>9</v>
-      </c>
-      <c r="E116" t="s">
-        <v>10</v>
-      </c>
-      <c r="F116" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="117">
@@ -3123,19 +3117,19 @@
         <v>41</v>
       </c>
       <c r="B117" t="s">
+        <v>69</v>
+      </c>
+      <c r="C117" t="s">
+        <v>20</v>
+      </c>
+      <c r="D117" t="s">
+        <v>9</v>
+      </c>
+      <c r="E117" t="s">
+        <v>12</v>
+      </c>
+      <c r="F117" t="s">
         <v>70</v>
-      </c>
-      <c r="C117" t="s">
-        <v>20</v>
-      </c>
-      <c r="D117" t="s">
-        <v>9</v>
-      </c>
-      <c r="E117" t="s">
-        <v>12</v>
-      </c>
-      <c r="F117" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="118">
@@ -3143,19 +3137,19 @@
         <v>41</v>
       </c>
       <c r="B118" t="s">
+        <v>69</v>
+      </c>
+      <c r="C118" t="s">
+        <v>20</v>
+      </c>
+      <c r="D118" t="s">
+        <v>9</v>
+      </c>
+      <c r="E118" t="s">
+        <v>13</v>
+      </c>
+      <c r="F118" t="s">
         <v>70</v>
-      </c>
-      <c r="C118" t="s">
-        <v>20</v>
-      </c>
-      <c r="D118" t="s">
-        <v>9</v>
-      </c>
-      <c r="E118" t="s">
-        <v>13</v>
-      </c>
-      <c r="F118" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="119">
@@ -3163,19 +3157,19 @@
         <v>41</v>
       </c>
       <c r="B119" t="s">
+        <v>69</v>
+      </c>
+      <c r="C119" t="s">
+        <v>20</v>
+      </c>
+      <c r="D119" t="s">
+        <v>14</v>
+      </c>
+      <c r="E119" t="s">
+        <v>10</v>
+      </c>
+      <c r="F119" t="s">
         <v>70</v>
-      </c>
-      <c r="C119" t="s">
-        <v>20</v>
-      </c>
-      <c r="D119" t="s">
-        <v>14</v>
-      </c>
-      <c r="E119" t="s">
-        <v>10</v>
-      </c>
-      <c r="F119" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="120">
@@ -3183,19 +3177,19 @@
         <v>41</v>
       </c>
       <c r="B120" t="s">
+        <v>69</v>
+      </c>
+      <c r="C120" t="s">
+        <v>20</v>
+      </c>
+      <c r="D120" t="s">
+        <v>14</v>
+      </c>
+      <c r="E120" t="s">
+        <v>12</v>
+      </c>
+      <c r="F120" t="s">
         <v>70</v>
-      </c>
-      <c r="C120" t="s">
-        <v>20</v>
-      </c>
-      <c r="D120" t="s">
-        <v>14</v>
-      </c>
-      <c r="E120" t="s">
-        <v>12</v>
-      </c>
-      <c r="F120" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="121">
@@ -3203,327 +3197,327 @@
         <v>41</v>
       </c>
       <c r="B121" t="s">
+        <v>69</v>
+      </c>
+      <c r="C121" t="s">
+        <v>20</v>
+      </c>
+      <c r="D121" t="s">
+        <v>14</v>
+      </c>
+      <c r="E121" t="s">
+        <v>13</v>
+      </c>
+      <c r="F121" t="s">
         <v>70</v>
-      </c>
-      <c r="C121" t="s">
-        <v>20</v>
-      </c>
-      <c r="D121" t="s">
-        <v>14</v>
-      </c>
-      <c r="E121" t="s">
-        <v>13</v>
-      </c>
-      <c r="F121" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
+        <v>71</v>
+      </c>
+      <c r="B122" t="s">
         <v>72</v>
       </c>
-      <c r="B122" t="s">
+      <c r="C122" t="s">
         <v>73</v>
       </c>
-      <c r="C122" t="s">
+      <c r="D122" t="s">
+        <v>9</v>
+      </c>
+      <c r="E122" t="s">
+        <v>10</v>
+      </c>
+      <c r="F122" t="s">
         <v>74</v>
-      </c>
-      <c r="D122" t="s">
-        <v>9</v>
-      </c>
-      <c r="E122" t="s">
-        <v>10</v>
-      </c>
-      <c r="F122" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
+        <v>71</v>
+      </c>
+      <c r="B123" t="s">
         <v>72</v>
       </c>
-      <c r="B123" t="s">
+      <c r="C123" t="s">
         <v>73</v>
       </c>
-      <c r="C123" t="s">
+      <c r="D123" t="s">
+        <v>9</v>
+      </c>
+      <c r="E123" t="s">
+        <v>12</v>
+      </c>
+      <c r="F123" t="s">
         <v>74</v>
-      </c>
-      <c r="D123" t="s">
-        <v>9</v>
-      </c>
-      <c r="E123" t="s">
-        <v>12</v>
-      </c>
-      <c r="F123" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
+        <v>71</v>
+      </c>
+      <c r="B124" t="s">
         <v>72</v>
       </c>
-      <c r="B124" t="s">
+      <c r="C124" t="s">
         <v>73</v>
       </c>
-      <c r="C124" t="s">
+      <c r="D124" t="s">
+        <v>9</v>
+      </c>
+      <c r="E124" t="s">
+        <v>13</v>
+      </c>
+      <c r="F124" t="s">
         <v>74</v>
-      </c>
-      <c r="D124" t="s">
-        <v>9</v>
-      </c>
-      <c r="E124" t="s">
-        <v>13</v>
-      </c>
-      <c r="F124" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B125" t="s">
+        <v>75</v>
+      </c>
+      <c r="C125" t="s">
         <v>76</v>
       </c>
-      <c r="C125" t="s">
+      <c r="D125" t="s">
+        <v>9</v>
+      </c>
+      <c r="E125" t="s">
+        <v>10</v>
+      </c>
+      <c r="F125" t="s">
         <v>77</v>
-      </c>
-      <c r="D125" t="s">
-        <v>9</v>
-      </c>
-      <c r="E125" t="s">
-        <v>10</v>
-      </c>
-      <c r="F125" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B126" t="s">
+        <v>75</v>
+      </c>
+      <c r="C126" t="s">
         <v>76</v>
       </c>
-      <c r="C126" t="s">
+      <c r="D126" t="s">
+        <v>9</v>
+      </c>
+      <c r="E126" t="s">
+        <v>12</v>
+      </c>
+      <c r="F126" t="s">
         <v>77</v>
-      </c>
-      <c r="D126" t="s">
-        <v>9</v>
-      </c>
-      <c r="E126" t="s">
-        <v>12</v>
-      </c>
-      <c r="F126" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B127" t="s">
+        <v>75</v>
+      </c>
+      <c r="C127" t="s">
         <v>76</v>
       </c>
-      <c r="C127" t="s">
+      <c r="D127" t="s">
+        <v>9</v>
+      </c>
+      <c r="E127" t="s">
+        <v>13</v>
+      </c>
+      <c r="F127" t="s">
         <v>77</v>
-      </c>
-      <c r="D127" t="s">
-        <v>9</v>
-      </c>
-      <c r="E127" t="s">
-        <v>13</v>
-      </c>
-      <c r="F127" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B128" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C128" t="s">
+        <v>78</v>
+      </c>
+      <c r="D128" t="s">
+        <v>9</v>
+      </c>
+      <c r="E128" t="s">
+        <v>10</v>
+      </c>
+      <c r="F128" t="s">
         <v>79</v>
-      </c>
-      <c r="D128" t="s">
-        <v>9</v>
-      </c>
-      <c r="E128" t="s">
-        <v>10</v>
-      </c>
-      <c r="F128" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B129" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C129" t="s">
+        <v>78</v>
+      </c>
+      <c r="D129" t="s">
+        <v>9</v>
+      </c>
+      <c r="E129" t="s">
+        <v>12</v>
+      </c>
+      <c r="F129" t="s">
         <v>79</v>
-      </c>
-      <c r="D129" t="s">
-        <v>9</v>
-      </c>
-      <c r="E129" t="s">
-        <v>12</v>
-      </c>
-      <c r="F129" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B130" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C130" t="s">
+        <v>78</v>
+      </c>
+      <c r="D130" t="s">
+        <v>9</v>
+      </c>
+      <c r="E130" t="s">
+        <v>13</v>
+      </c>
+      <c r="F130" t="s">
         <v>79</v>
-      </c>
-      <c r="D130" t="s">
-        <v>9</v>
-      </c>
-      <c r="E130" t="s">
-        <v>13</v>
-      </c>
-      <c r="F130" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B131" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C131" t="s">
+        <v>78</v>
+      </c>
+      <c r="D131" t="s">
+        <v>14</v>
+      </c>
+      <c r="E131" t="s">
+        <v>10</v>
+      </c>
+      <c r="F131" t="s">
         <v>79</v>
-      </c>
-      <c r="D131" t="s">
-        <v>14</v>
-      </c>
-      <c r="E131" t="s">
-        <v>10</v>
-      </c>
-      <c r="F131" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B132" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C132" t="s">
+        <v>78</v>
+      </c>
+      <c r="D132" t="s">
+        <v>14</v>
+      </c>
+      <c r="E132" t="s">
+        <v>12</v>
+      </c>
+      <c r="F132" t="s">
         <v>79</v>
-      </c>
-      <c r="D132" t="s">
-        <v>14</v>
-      </c>
-      <c r="E132" t="s">
-        <v>12</v>
-      </c>
-      <c r="F132" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B133" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C133" t="s">
+        <v>78</v>
+      </c>
+      <c r="D133" t="s">
+        <v>14</v>
+      </c>
+      <c r="E133" t="s">
+        <v>13</v>
+      </c>
+      <c r="F133" t="s">
         <v>79</v>
-      </c>
-      <c r="D133" t="s">
-        <v>14</v>
-      </c>
-      <c r="E133" t="s">
-        <v>13</v>
-      </c>
-      <c r="F133" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B134" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C134" t="s">
         <v>20</v>
       </c>
       <c r="D134" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E134" t="s">
         <v>10</v>
       </c>
       <c r="F134" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B135" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C135" t="s">
         <v>20</v>
       </c>
       <c r="D135" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E135" t="s">
         <v>12</v>
       </c>
       <c r="F135" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B136" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C136" t="s">
         <v>20</v>
       </c>
       <c r="D136" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E136" t="s">
         <v>13</v>
       </c>
       <c r="F136" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B137" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C137" t="s">
         <v>20</v>
@@ -3535,15 +3529,15 @@
         <v>10</v>
       </c>
       <c r="F137" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B138" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C138" t="s">
         <v>20</v>
@@ -3555,15 +3549,15 @@
         <v>12</v>
       </c>
       <c r="F138" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B139" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C139" t="s">
         <v>20</v>
@@ -3575,15 +3569,15 @@
         <v>13</v>
       </c>
       <c r="F139" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B140" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C140" t="s">
         <v>20</v>
@@ -3595,15 +3589,15 @@
         <v>10</v>
       </c>
       <c r="F140" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B141" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C141" t="s">
         <v>20</v>
@@ -3615,15 +3609,15 @@
         <v>12</v>
       </c>
       <c r="F141" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B142" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C142" t="s">
         <v>20</v>
@@ -3635,15 +3629,15 @@
         <v>13</v>
       </c>
       <c r="F142" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B143" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C143" t="s">
         <v>17</v>
@@ -3655,15 +3649,15 @@
         <v>10</v>
       </c>
       <c r="F143" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B144" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C144" t="s">
         <v>17</v>
@@ -3675,15 +3669,15 @@
         <v>12</v>
       </c>
       <c r="F144" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B145" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C145" t="s">
         <v>17</v>
@@ -3695,15 +3689,15 @@
         <v>13</v>
       </c>
       <c r="F145" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B146" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C146" t="s">
         <v>17</v>
@@ -3715,15 +3709,15 @@
         <v>10</v>
       </c>
       <c r="F146" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B147" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C147" t="s">
         <v>17</v>
@@ -3735,15 +3729,15 @@
         <v>12</v>
       </c>
       <c r="F147" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B148" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C148" t="s">
         <v>17</v>
@@ -3755,375 +3749,375 @@
         <v>13</v>
       </c>
       <c r="F148" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B149" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C149" t="s">
+        <v>82</v>
+      </c>
+      <c r="D149" t="s">
+        <v>9</v>
+      </c>
+      <c r="E149" t="s">
+        <v>10</v>
+      </c>
+      <c r="F149" t="s">
         <v>83</v>
-      </c>
-      <c r="D149" t="s">
-        <v>9</v>
-      </c>
-      <c r="E149" t="s">
-        <v>10</v>
-      </c>
-      <c r="F149" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B150" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C150" t="s">
+        <v>82</v>
+      </c>
+      <c r="D150" t="s">
+        <v>9</v>
+      </c>
+      <c r="E150" t="s">
+        <v>12</v>
+      </c>
+      <c r="F150" t="s">
         <v>83</v>
-      </c>
-      <c r="D150" t="s">
-        <v>9</v>
-      </c>
-      <c r="E150" t="s">
-        <v>12</v>
-      </c>
-      <c r="F150" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B151" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C151" t="s">
+        <v>82</v>
+      </c>
+      <c r="D151" t="s">
+        <v>9</v>
+      </c>
+      <c r="E151" t="s">
+        <v>13</v>
+      </c>
+      <c r="F151" t="s">
         <v>83</v>
-      </c>
-      <c r="D151" t="s">
-        <v>9</v>
-      </c>
-      <c r="E151" t="s">
-        <v>13</v>
-      </c>
-      <c r="F151" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B152" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C152" t="s">
+        <v>82</v>
+      </c>
+      <c r="D152" t="s">
+        <v>14</v>
+      </c>
+      <c r="E152" t="s">
+        <v>10</v>
+      </c>
+      <c r="F152" t="s">
         <v>83</v>
-      </c>
-      <c r="D152" t="s">
-        <v>14</v>
-      </c>
-      <c r="E152" t="s">
-        <v>10</v>
-      </c>
-      <c r="F152" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B153" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C153" t="s">
+        <v>82</v>
+      </c>
+      <c r="D153" t="s">
+        <v>14</v>
+      </c>
+      <c r="E153" t="s">
+        <v>12</v>
+      </c>
+      <c r="F153" t="s">
         <v>83</v>
-      </c>
-      <c r="D153" t="s">
-        <v>14</v>
-      </c>
-      <c r="E153" t="s">
-        <v>12</v>
-      </c>
-      <c r="F153" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B154" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C154" t="s">
+        <v>82</v>
+      </c>
+      <c r="D154" t="s">
+        <v>14</v>
+      </c>
+      <c r="E154" t="s">
+        <v>13</v>
+      </c>
+      <c r="F154" t="s">
         <v>83</v>
-      </c>
-      <c r="D154" t="s">
-        <v>14</v>
-      </c>
-      <c r="E154" t="s">
-        <v>13</v>
-      </c>
-      <c r="F154" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B155" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C155" t="s">
+        <v>84</v>
+      </c>
+      <c r="D155" t="s">
+        <v>9</v>
+      </c>
+      <c r="E155" t="s">
+        <v>10</v>
+      </c>
+      <c r="F155" t="s">
         <v>85</v>
-      </c>
-      <c r="D155" t="s">
-        <v>9</v>
-      </c>
-      <c r="E155" t="s">
-        <v>10</v>
-      </c>
-      <c r="F155" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B156" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C156" t="s">
+        <v>84</v>
+      </c>
+      <c r="D156" t="s">
+        <v>9</v>
+      </c>
+      <c r="E156" t="s">
+        <v>12</v>
+      </c>
+      <c r="F156" t="s">
         <v>85</v>
-      </c>
-      <c r="D156" t="s">
-        <v>9</v>
-      </c>
-      <c r="E156" t="s">
-        <v>12</v>
-      </c>
-      <c r="F156" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B157" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C157" t="s">
+        <v>84</v>
+      </c>
+      <c r="D157" t="s">
+        <v>9</v>
+      </c>
+      <c r="E157" t="s">
+        <v>13</v>
+      </c>
+      <c r="F157" t="s">
         <v>85</v>
-      </c>
-      <c r="D157" t="s">
-        <v>9</v>
-      </c>
-      <c r="E157" t="s">
-        <v>13</v>
-      </c>
-      <c r="F157" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B158" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C158" t="s">
+        <v>84</v>
+      </c>
+      <c r="D158" t="s">
+        <v>14</v>
+      </c>
+      <c r="E158" t="s">
+        <v>10</v>
+      </c>
+      <c r="F158" t="s">
         <v>85</v>
-      </c>
-      <c r="D158" t="s">
-        <v>14</v>
-      </c>
-      <c r="E158" t="s">
-        <v>10</v>
-      </c>
-      <c r="F158" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B159" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C159" t="s">
+        <v>84</v>
+      </c>
+      <c r="D159" t="s">
+        <v>14</v>
+      </c>
+      <c r="E159" t="s">
+        <v>12</v>
+      </c>
+      <c r="F159" t="s">
         <v>85</v>
-      </c>
-      <c r="D159" t="s">
-        <v>14</v>
-      </c>
-      <c r="E159" t="s">
-        <v>12</v>
-      </c>
-      <c r="F159" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B160" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C160" t="s">
+        <v>84</v>
+      </c>
+      <c r="D160" t="s">
+        <v>14</v>
+      </c>
+      <c r="E160" t="s">
+        <v>13</v>
+      </c>
+      <c r="F160" t="s">
         <v>85</v>
-      </c>
-      <c r="D160" t="s">
-        <v>14</v>
-      </c>
-      <c r="E160" t="s">
-        <v>13</v>
-      </c>
-      <c r="F160" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B161" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C161" t="s">
         <v>20</v>
       </c>
       <c r="D161" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E161" t="s">
         <v>10</v>
       </c>
       <c r="F161" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B162" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C162" t="s">
         <v>20</v>
       </c>
       <c r="D162" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E162" t="s">
         <v>12</v>
       </c>
       <c r="F162" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B163" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C163" t="s">
         <v>20</v>
       </c>
       <c r="D163" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E163" t="s">
         <v>13</v>
       </c>
       <c r="F163" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B164" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C164" t="s">
         <v>20</v>
       </c>
       <c r="D164" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E164" t="s">
         <v>10</v>
       </c>
       <c r="F164" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B165" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C165" t="s">
         <v>20</v>
       </c>
       <c r="D165" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E165" t="s">
         <v>12</v>
       </c>
       <c r="F165" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B166" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C166" t="s">
         <v>20</v>
       </c>
       <c r="D166" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E166" t="s">
         <v>13</v>
       </c>
       <c r="F166" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B167" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C167" t="s">
         <v>20</v>
@@ -4135,15 +4129,15 @@
         <v>10</v>
       </c>
       <c r="F167" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B168" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C168" t="s">
         <v>20</v>
@@ -4155,15 +4149,15 @@
         <v>12</v>
       </c>
       <c r="F168" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B169" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C169" t="s">
         <v>20</v>
@@ -4175,15 +4169,15 @@
         <v>13</v>
       </c>
       <c r="F169" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B170" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C170" t="s">
         <v>20</v>
@@ -4195,15 +4189,15 @@
         <v>10</v>
       </c>
       <c r="F170" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B171" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C171" t="s">
         <v>20</v>
@@ -4215,15 +4209,15 @@
         <v>12</v>
       </c>
       <c r="F171" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B172" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C172" t="s">
         <v>20</v>
@@ -4235,138 +4229,138 @@
         <v>13</v>
       </c>
       <c r="F172" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B173" t="s">
+        <v>87</v>
+      </c>
+      <c r="C173" t="s">
+        <v>82</v>
+      </c>
+      <c r="D173" t="s">
+        <v>9</v>
+      </c>
+      <c r="E173" t="s">
+        <v>10</v>
+      </c>
+      <c r="F173" t="s">
         <v>88</v>
-      </c>
-      <c r="C173" t="s">
-        <v>83</v>
-      </c>
-      <c r="D173" t="s">
-        <v>9</v>
-      </c>
-      <c r="E173" t="s">
-        <v>10</v>
-      </c>
-      <c r="F173" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B174" t="s">
+        <v>87</v>
+      </c>
+      <c r="C174" t="s">
+        <v>82</v>
+      </c>
+      <c r="D174" t="s">
+        <v>9</v>
+      </c>
+      <c r="E174" t="s">
+        <v>12</v>
+      </c>
+      <c r="F174" t="s">
         <v>88</v>
-      </c>
-      <c r="C174" t="s">
-        <v>83</v>
-      </c>
-      <c r="D174" t="s">
-        <v>9</v>
-      </c>
-      <c r="E174" t="s">
-        <v>12</v>
-      </c>
-      <c r="F174" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B175" t="s">
+        <v>87</v>
+      </c>
+      <c r="C175" t="s">
+        <v>82</v>
+      </c>
+      <c r="D175" t="s">
+        <v>9</v>
+      </c>
+      <c r="E175" t="s">
+        <v>13</v>
+      </c>
+      <c r="F175" t="s">
         <v>88</v>
-      </c>
-      <c r="C175" t="s">
-        <v>83</v>
-      </c>
-      <c r="D175" t="s">
-        <v>9</v>
-      </c>
-      <c r="E175" t="s">
-        <v>13</v>
-      </c>
-      <c r="F175" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B176" t="s">
+        <v>87</v>
+      </c>
+      <c r="C176" t="s">
+        <v>82</v>
+      </c>
+      <c r="D176" t="s">
+        <v>14</v>
+      </c>
+      <c r="E176" t="s">
+        <v>10</v>
+      </c>
+      <c r="F176" t="s">
         <v>88</v>
-      </c>
-      <c r="C176" t="s">
-        <v>83</v>
-      </c>
-      <c r="D176" t="s">
-        <v>14</v>
-      </c>
-      <c r="E176" t="s">
-        <v>10</v>
-      </c>
-      <c r="F176" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B177" t="s">
+        <v>87</v>
+      </c>
+      <c r="C177" t="s">
+        <v>82</v>
+      </c>
+      <c r="D177" t="s">
+        <v>14</v>
+      </c>
+      <c r="E177" t="s">
+        <v>12</v>
+      </c>
+      <c r="F177" t="s">
         <v>88</v>
-      </c>
-      <c r="C177" t="s">
-        <v>83</v>
-      </c>
-      <c r="D177" t="s">
-        <v>14</v>
-      </c>
-      <c r="E177" t="s">
-        <v>12</v>
-      </c>
-      <c r="F177" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B178" t="s">
+        <v>87</v>
+      </c>
+      <c r="C178" t="s">
+        <v>82</v>
+      </c>
+      <c r="D178" t="s">
+        <v>14</v>
+      </c>
+      <c r="E178" t="s">
+        <v>13</v>
+      </c>
+      <c r="F178" t="s">
         <v>88</v>
-      </c>
-      <c r="C178" t="s">
-        <v>83</v>
-      </c>
-      <c r="D178" t="s">
-        <v>14</v>
-      </c>
-      <c r="E178" t="s">
-        <v>13</v>
-      </c>
-      <c r="F178" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B179" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C179" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D179" t="s">
         <v>9</v>
@@ -4375,18 +4369,18 @@
         <v>10</v>
       </c>
       <c r="F179" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B180" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C180" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D180" t="s">
         <v>9</v>
@@ -4395,18 +4389,18 @@
         <v>12</v>
       </c>
       <c r="F180" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B181" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C181" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D181" t="s">
         <v>9</v>
@@ -4415,18 +4409,18 @@
         <v>13</v>
       </c>
       <c r="F181" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B182" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C182" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D182" t="s">
         <v>14</v>
@@ -4435,18 +4429,18 @@
         <v>10</v>
       </c>
       <c r="F182" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B183" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C183" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D183" t="s">
         <v>14</v>
@@ -4455,18 +4449,18 @@
         <v>12</v>
       </c>
       <c r="F183" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B184" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C184" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D184" t="s">
         <v>14</v>
@@ -4475,198 +4469,198 @@
         <v>13</v>
       </c>
       <c r="F184" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B185" t="s">
+        <v>90</v>
+      </c>
+      <c r="C185" t="s">
+        <v>20</v>
+      </c>
+      <c r="D185" t="s">
+        <v>67</v>
+      </c>
+      <c r="E185" t="s">
+        <v>10</v>
+      </c>
+      <c r="F185" t="s">
         <v>91</v>
-      </c>
-      <c r="C185" t="s">
-        <v>20</v>
-      </c>
-      <c r="D185" t="s">
-        <v>68</v>
-      </c>
-      <c r="E185" t="s">
-        <v>10</v>
-      </c>
-      <c r="F185" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B186" t="s">
+        <v>90</v>
+      </c>
+      <c r="C186" t="s">
+        <v>20</v>
+      </c>
+      <c r="D186" t="s">
+        <v>67</v>
+      </c>
+      <c r="E186" t="s">
+        <v>12</v>
+      </c>
+      <c r="F186" t="s">
         <v>91</v>
-      </c>
-      <c r="C186" t="s">
-        <v>20</v>
-      </c>
-      <c r="D186" t="s">
-        <v>68</v>
-      </c>
-      <c r="E186" t="s">
-        <v>12</v>
-      </c>
-      <c r="F186" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B187" t="s">
+        <v>90</v>
+      </c>
+      <c r="C187" t="s">
+        <v>20</v>
+      </c>
+      <c r="D187" t="s">
+        <v>67</v>
+      </c>
+      <c r="E187" t="s">
+        <v>13</v>
+      </c>
+      <c r="F187" t="s">
         <v>91</v>
-      </c>
-      <c r="C187" t="s">
-        <v>20</v>
-      </c>
-      <c r="D187" t="s">
-        <v>68</v>
-      </c>
-      <c r="E187" t="s">
-        <v>13</v>
-      </c>
-      <c r="F187" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B188" t="s">
+        <v>90</v>
+      </c>
+      <c r="C188" t="s">
+        <v>20</v>
+      </c>
+      <c r="D188" t="s">
+        <v>9</v>
+      </c>
+      <c r="E188" t="s">
+        <v>10</v>
+      </c>
+      <c r="F188" t="s">
         <v>91</v>
-      </c>
-      <c r="C188" t="s">
-        <v>20</v>
-      </c>
-      <c r="D188" t="s">
-        <v>9</v>
-      </c>
-      <c r="E188" t="s">
-        <v>10</v>
-      </c>
-      <c r="F188" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B189" t="s">
+        <v>90</v>
+      </c>
+      <c r="C189" t="s">
+        <v>20</v>
+      </c>
+      <c r="D189" t="s">
+        <v>9</v>
+      </c>
+      <c r="E189" t="s">
+        <v>12</v>
+      </c>
+      <c r="F189" t="s">
         <v>91</v>
-      </c>
-      <c r="C189" t="s">
-        <v>20</v>
-      </c>
-      <c r="D189" t="s">
-        <v>9</v>
-      </c>
-      <c r="E189" t="s">
-        <v>12</v>
-      </c>
-      <c r="F189" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B190" t="s">
+        <v>90</v>
+      </c>
+      <c r="C190" t="s">
+        <v>20</v>
+      </c>
+      <c r="D190" t="s">
+        <v>9</v>
+      </c>
+      <c r="E190" t="s">
+        <v>13</v>
+      </c>
+      <c r="F190" t="s">
         <v>91</v>
-      </c>
-      <c r="C190" t="s">
-        <v>20</v>
-      </c>
-      <c r="D190" t="s">
-        <v>9</v>
-      </c>
-      <c r="E190" t="s">
-        <v>13</v>
-      </c>
-      <c r="F190" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B191" t="s">
+        <v>90</v>
+      </c>
+      <c r="C191" t="s">
+        <v>20</v>
+      </c>
+      <c r="D191" t="s">
+        <v>14</v>
+      </c>
+      <c r="E191" t="s">
+        <v>10</v>
+      </c>
+      <c r="F191" t="s">
         <v>91</v>
-      </c>
-      <c r="C191" t="s">
-        <v>20</v>
-      </c>
-      <c r="D191" t="s">
-        <v>14</v>
-      </c>
-      <c r="E191" t="s">
-        <v>10</v>
-      </c>
-      <c r="F191" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B192" t="s">
+        <v>90</v>
+      </c>
+      <c r="C192" t="s">
+        <v>20</v>
+      </c>
+      <c r="D192" t="s">
+        <v>14</v>
+      </c>
+      <c r="E192" t="s">
+        <v>12</v>
+      </c>
+      <c r="F192" t="s">
         <v>91</v>
-      </c>
-      <c r="C192" t="s">
-        <v>20</v>
-      </c>
-      <c r="D192" t="s">
-        <v>14</v>
-      </c>
-      <c r="E192" t="s">
-        <v>12</v>
-      </c>
-      <c r="F192" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B193" t="s">
+        <v>90</v>
+      </c>
+      <c r="C193" t="s">
+        <v>20</v>
+      </c>
+      <c r="D193" t="s">
+        <v>14</v>
+      </c>
+      <c r="E193" t="s">
+        <v>13</v>
+      </c>
+      <c r="F193" t="s">
         <v>91</v>
-      </c>
-      <c r="C193" t="s">
-        <v>20</v>
-      </c>
-      <c r="D193" t="s">
-        <v>14</v>
-      </c>
-      <c r="E193" t="s">
-        <v>13</v>
-      </c>
-      <c r="F193" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B194" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C194" t="s">
-        <v>93</v>
+        <v>17</v>
       </c>
       <c r="D194" t="s">
         <v>9</v>
@@ -4675,18 +4669,18 @@
         <v>10</v>
       </c>
       <c r="F194" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B195" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C195" t="s">
-        <v>93</v>
+        <v>17</v>
       </c>
       <c r="D195" t="s">
         <v>9</v>
@@ -4695,18 +4689,18 @@
         <v>12</v>
       </c>
       <c r="F195" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B196" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C196" t="s">
-        <v>93</v>
+        <v>17</v>
       </c>
       <c r="D196" t="s">
         <v>9</v>
@@ -4715,18 +4709,18 @@
         <v>13</v>
       </c>
       <c r="F196" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B197" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C197" t="s">
-        <v>93</v>
+        <v>17</v>
       </c>
       <c r="D197" t="s">
         <v>14</v>
@@ -4735,18 +4729,18 @@
         <v>10</v>
       </c>
       <c r="F197" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B198" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C198" t="s">
-        <v>93</v>
+        <v>17</v>
       </c>
       <c r="D198" t="s">
         <v>14</v>
@@ -4755,18 +4749,18 @@
         <v>12</v>
       </c>
       <c r="F198" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B199" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C199" t="s">
-        <v>93</v>
+        <v>17</v>
       </c>
       <c r="D199" t="s">
         <v>14</v>
@@ -4775,18 +4769,18 @@
         <v>13</v>
       </c>
       <c r="F199" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B200" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C200" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D200" t="s">
         <v>9</v>
@@ -4795,18 +4789,18 @@
         <v>10</v>
       </c>
       <c r="F200" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B201" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C201" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D201" t="s">
         <v>9</v>
@@ -4815,18 +4809,18 @@
         <v>12</v>
       </c>
       <c r="F201" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B202" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C202" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D202" t="s">
         <v>9</v>
@@ -4835,18 +4829,18 @@
         <v>13</v>
       </c>
       <c r="F202" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B203" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C203" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D203" t="s">
         <v>14</v>
@@ -4855,18 +4849,18 @@
         <v>10</v>
       </c>
       <c r="F203" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B204" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C204" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D204" t="s">
         <v>14</v>
@@ -4875,18 +4869,18 @@
         <v>12</v>
       </c>
       <c r="F204" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B205" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C205" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D205" t="s">
         <v>14</v>
@@ -4895,18 +4889,18 @@
         <v>13</v>
       </c>
       <c r="F205" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B206" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C206" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D206" t="s">
         <v>9</v>
@@ -4915,18 +4909,18 @@
         <v>10</v>
       </c>
       <c r="F206" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B207" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C207" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D207" t="s">
         <v>9</v>
@@ -4935,18 +4929,18 @@
         <v>12</v>
       </c>
       <c r="F207" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B208" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C208" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D208" t="s">
         <v>9</v>
@@ -4955,18 +4949,18 @@
         <v>13</v>
       </c>
       <c r="F208" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B209" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C209" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D209" t="s">
         <v>9</v>
@@ -4975,18 +4969,18 @@
         <v>10</v>
       </c>
       <c r="F209" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B210" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C210" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D210" t="s">
         <v>9</v>
@@ -4995,18 +4989,18 @@
         <v>12</v>
       </c>
       <c r="F210" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B211" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C211" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D211" t="s">
         <v>9</v>
@@ -5015,18 +5009,18 @@
         <v>13</v>
       </c>
       <c r="F211" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B212" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C212" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D212" t="s">
         <v>9</v>
@@ -5035,18 +5029,18 @@
         <v>10</v>
       </c>
       <c r="F212" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B213" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C213" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D213" t="s">
         <v>9</v>
@@ -5055,18 +5049,18 @@
         <v>12</v>
       </c>
       <c r="F213" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B214" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C214" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D214" t="s">
         <v>9</v>
@@ -5075,18 +5069,18 @@
         <v>13</v>
       </c>
       <c r="F214" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B215" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C215" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D215" t="s">
         <v>14</v>
@@ -5095,18 +5089,18 @@
         <v>10</v>
       </c>
       <c r="F215" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B216" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C216" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D216" t="s">
         <v>14</v>
@@ -5115,18 +5109,18 @@
         <v>12</v>
       </c>
       <c r="F216" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B217" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C217" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D217" t="s">
         <v>14</v>
@@ -5135,75 +5129,75 @@
         <v>13</v>
       </c>
       <c r="F217" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B218" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C218" t="s">
         <v>20</v>
       </c>
       <c r="D218" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E218" t="s">
         <v>10</v>
       </c>
       <c r="F218" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B219" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C219" t="s">
         <v>20</v>
       </c>
       <c r="D219" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E219" t="s">
         <v>12</v>
       </c>
       <c r="F219" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B220" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C220" t="s">
         <v>20</v>
       </c>
       <c r="D220" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E220" t="s">
         <v>13</v>
       </c>
       <c r="F220" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B221" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C221" t="s">
         <v>20</v>
@@ -5215,15 +5209,15 @@
         <v>10</v>
       </c>
       <c r="F221" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B222" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C222" t="s">
         <v>20</v>
@@ -5235,15 +5229,15 @@
         <v>12</v>
       </c>
       <c r="F222" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B223" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C223" t="s">
         <v>20</v>
@@ -5255,15 +5249,15 @@
         <v>13</v>
       </c>
       <c r="F223" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B224" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C224" t="s">
         <v>20</v>
@@ -5275,15 +5269,15 @@
         <v>10</v>
       </c>
       <c r="F224" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B225" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C225" t="s">
         <v>20</v>
@@ -5295,15 +5289,15 @@
         <v>12</v>
       </c>
       <c r="F225" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B226" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C226" t="s">
         <v>20</v>
@@ -5315,15 +5309,15 @@
         <v>13</v>
       </c>
       <c r="F226" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B227" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C227" t="s">
         <v>17</v>
@@ -5335,15 +5329,15 @@
         <v>10</v>
       </c>
       <c r="F227" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B228" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C228" t="s">
         <v>17</v>
@@ -5355,15 +5349,15 @@
         <v>12</v>
       </c>
       <c r="F228" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B229" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C229" t="s">
         <v>17</v>
@@ -5375,15 +5369,15 @@
         <v>13</v>
       </c>
       <c r="F229" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B230" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C230" t="s">
         <v>17</v>
@@ -5395,15 +5389,15 @@
         <v>10</v>
       </c>
       <c r="F230" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B231" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C231" t="s">
         <v>17</v>
@@ -5415,15 +5409,15 @@
         <v>12</v>
       </c>
       <c r="F231" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B232" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C232" t="s">
         <v>17</v>
@@ -5435,18 +5429,18 @@
         <v>13</v>
       </c>
       <c r="F232" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B233" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C233" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D233" t="s">
         <v>9</v>
@@ -5455,18 +5449,18 @@
         <v>10</v>
       </c>
       <c r="F233" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B234" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C234" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D234" t="s">
         <v>9</v>
@@ -5475,18 +5469,18 @@
         <v>10</v>
       </c>
       <c r="F234" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B235" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C235" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D235" t="s">
         <v>9</v>
@@ -5495,18 +5489,18 @@
         <v>12</v>
       </c>
       <c r="F235" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B236" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C236" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D236" t="s">
         <v>9</v>
@@ -5515,18 +5509,18 @@
         <v>12</v>
       </c>
       <c r="F236" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B237" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C237" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D237" t="s">
         <v>9</v>
@@ -5535,18 +5529,18 @@
         <v>13</v>
       </c>
       <c r="F237" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B238" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C238" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D238" t="s">
         <v>9</v>
@@ -5555,18 +5549,18 @@
         <v>13</v>
       </c>
       <c r="F238" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B239" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C239" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D239" t="s">
         <v>14</v>
@@ -5575,18 +5569,18 @@
         <v>10</v>
       </c>
       <c r="F239" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B240" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C240" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D240" t="s">
         <v>14</v>
@@ -5595,18 +5589,18 @@
         <v>10</v>
       </c>
       <c r="F240" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B241" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C241" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D241" t="s">
         <v>14</v>
@@ -5615,18 +5609,18 @@
         <v>12</v>
       </c>
       <c r="F241" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B242" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C242" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D242" t="s">
         <v>14</v>
@@ -5635,18 +5629,18 @@
         <v>12</v>
       </c>
       <c r="F242" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B243" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C243" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D243" t="s">
         <v>14</v>
@@ -5655,18 +5649,18 @@
         <v>13</v>
       </c>
       <c r="F243" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B244" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C244" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D244" t="s">
         <v>14</v>
@@ -5675,18 +5669,18 @@
         <v>13</v>
       </c>
       <c r="F244" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B245" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C245" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D245" t="s">
         <v>9</v>
@@ -5695,18 +5689,18 @@
         <v>10</v>
       </c>
       <c r="F245" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B246" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C246" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D246" t="s">
         <v>9</v>
@@ -5715,18 +5709,18 @@
         <v>12</v>
       </c>
       <c r="F246" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B247" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C247" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D247" t="s">
         <v>9</v>
@@ -5735,38 +5729,38 @@
         <v>13</v>
       </c>
       <c r="F247" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="s">
+        <v>102</v>
+      </c>
+      <c r="B248" t="s">
+        <v>103</v>
+      </c>
+      <c r="C248" t="s">
+        <v>103</v>
+      </c>
+      <c r="D248" t="s">
+        <v>9</v>
+      </c>
+      <c r="E248" t="s">
+        <v>10</v>
+      </c>
+      <c r="F248" t="s">
         <v>104</v>
-      </c>
-      <c r="B248" t="s">
-        <v>105</v>
-      </c>
-      <c r="C248" t="s">
-        <v>105</v>
-      </c>
-      <c r="D248" t="s">
-        <v>9</v>
-      </c>
-      <c r="E248" t="s">
-        <v>10</v>
-      </c>
-      <c r="F248" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B249" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C249" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D249" t="s">
         <v>9</v>
@@ -5775,18 +5769,18 @@
         <v>10</v>
       </c>
       <c r="F249" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B250" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C250" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D250" t="s">
         <v>14</v>
@@ -5795,32 +5789,32 @@
         <v>10</v>
       </c>
       <c r="F250" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B251" t="s">
+        <v>107</v>
+      </c>
+      <c r="C251" t="s">
+        <v>108</v>
+      </c>
+      <c r="D251" t="s">
+        <v>9</v>
+      </c>
+      <c r="E251" t="s">
+        <v>10</v>
+      </c>
+      <c r="F251" t="s">
         <v>109</v>
-      </c>
-      <c r="C251" t="s">
-        <v>110</v>
-      </c>
-      <c r="D251" t="s">
-        <v>9</v>
-      </c>
-      <c r="E251" t="s">
-        <v>10</v>
-      </c>
-      <c r="F251" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B252" t="s">
         <v>42</v>
@@ -5829,18 +5823,18 @@
         <v>20</v>
       </c>
       <c r="D252" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E252" t="s">
         <v>10</v>
       </c>
       <c r="F252" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B253" t="s">
         <v>42</v>
@@ -5849,18 +5843,18 @@
         <v>20</v>
       </c>
       <c r="D253" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E253" t="s">
         <v>12</v>
       </c>
       <c r="F253" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B254" t="s">
         <v>42</v>
@@ -5869,18 +5863,18 @@
         <v>20</v>
       </c>
       <c r="D254" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E254" t="s">
         <v>13</v>
       </c>
       <c r="F254" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B255" t="s">
         <v>42</v>
@@ -5895,12 +5889,12 @@
         <v>10</v>
       </c>
       <c r="F255" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B256" t="s">
         <v>42</v>
@@ -5915,12 +5909,12 @@
         <v>12</v>
       </c>
       <c r="F256" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B257" t="s">
         <v>42</v>
@@ -5935,12 +5929,12 @@
         <v>13</v>
       </c>
       <c r="F257" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B258" t="s">
         <v>42</v>
@@ -5955,12 +5949,12 @@
         <v>10</v>
       </c>
       <c r="F258" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B259" t="s">
         <v>42</v>
@@ -5975,12 +5969,12 @@
         <v>12</v>
       </c>
       <c r="F259" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B260" t="s">
         <v>42</v>
@@ -5995,18 +5989,18 @@
         <v>13</v>
       </c>
       <c r="F260" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B261" t="s">
         <v>42</v>
       </c>
       <c r="C261" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D261" t="s">
         <v>9</v>
@@ -6015,18 +6009,18 @@
         <v>10</v>
       </c>
       <c r="F261" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B262" t="s">
         <v>42</v>
       </c>
       <c r="C262" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D262" t="s">
         <v>9</v>
@@ -6035,18 +6029,18 @@
         <v>12</v>
       </c>
       <c r="F262" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B263" t="s">
         <v>42</v>
       </c>
       <c r="C263" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D263" t="s">
         <v>9</v>
@@ -6055,18 +6049,18 @@
         <v>13</v>
       </c>
       <c r="F263" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B264" t="s">
         <v>42</v>
       </c>
       <c r="C264" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D264" t="s">
         <v>14</v>
@@ -6075,18 +6069,18 @@
         <v>10</v>
       </c>
       <c r="F264" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B265" t="s">
         <v>42</v>
       </c>
       <c r="C265" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D265" t="s">
         <v>14</v>
@@ -6095,18 +6089,18 @@
         <v>12</v>
       </c>
       <c r="F265" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B266" t="s">
         <v>42</v>
       </c>
       <c r="C266" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D266" t="s">
         <v>14</v>
@@ -6115,18 +6109,18 @@
         <v>13</v>
       </c>
       <c r="F266" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B267" t="s">
         <v>42</v>
       </c>
       <c r="C267" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D267" t="s">
         <v>9</v>
@@ -6135,18 +6129,18 @@
         <v>10</v>
       </c>
       <c r="F267" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B268" t="s">
         <v>42</v>
       </c>
       <c r="C268" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D268" t="s">
         <v>9</v>
@@ -6155,18 +6149,18 @@
         <v>10</v>
       </c>
       <c r="F268" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B269" t="s">
         <v>42</v>
       </c>
       <c r="C269" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D269" t="s">
         <v>14</v>
@@ -6175,18 +6169,18 @@
         <v>10</v>
       </c>
       <c r="F269" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B270" t="s">
         <v>42</v>
       </c>
       <c r="C270" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D270" t="s">
         <v>9</v>
@@ -6195,18 +6189,18 @@
         <v>10</v>
       </c>
       <c r="F270" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B271" t="s">
         <v>42</v>
       </c>
       <c r="C271" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D271" t="s">
         <v>9</v>
@@ -6215,18 +6209,18 @@
         <v>12</v>
       </c>
       <c r="F271" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B272" t="s">
         <v>42</v>
       </c>
       <c r="C272" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D272" t="s">
         <v>9</v>
@@ -6235,18 +6229,18 @@
         <v>13</v>
       </c>
       <c r="F272" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B273" t="s">
         <v>42</v>
       </c>
       <c r="C273" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D273" t="s">
         <v>14</v>
@@ -6255,18 +6249,18 @@
         <v>10</v>
       </c>
       <c r="F273" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B274" t="s">
         <v>42</v>
       </c>
       <c r="C274" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D274" t="s">
         <v>14</v>
@@ -6275,18 +6269,18 @@
         <v>12</v>
       </c>
       <c r="F274" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B275" t="s">
         <v>42</v>
       </c>
       <c r="C275" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D275" t="s">
         <v>14</v>
@@ -6295,18 +6289,18 @@
         <v>13</v>
       </c>
       <c r="F275" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B276" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C276" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D276" t="s">
         <v>9</v>
@@ -6315,18 +6309,18 @@
         <v>10</v>
       </c>
       <c r="F276" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B277" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C277" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D277" t="s">
         <v>9</v>
@@ -6335,18 +6329,18 @@
         <v>12</v>
       </c>
       <c r="F277" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B278" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C278" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D278" t="s">
         <v>9</v>
@@ -6355,15 +6349,15 @@
         <v>13</v>
       </c>
       <c r="F278" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B279" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C279" t="s">
         <v>17</v>
@@ -6375,15 +6369,15 @@
         <v>10</v>
       </c>
       <c r="F279" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B280" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C280" t="s">
         <v>17</v>
@@ -6395,15 +6389,15 @@
         <v>12</v>
       </c>
       <c r="F280" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B281" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C281" t="s">
         <v>17</v>
@@ -6415,15 +6409,15 @@
         <v>13</v>
       </c>
       <c r="F281" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B282" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C282" t="s">
         <v>17</v>
@@ -6435,15 +6429,15 @@
         <v>10</v>
       </c>
       <c r="F282" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B283" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C283" t="s">
         <v>17</v>
@@ -6455,15 +6449,15 @@
         <v>12</v>
       </c>
       <c r="F283" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B284" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C284" t="s">
         <v>17</v>
@@ -6475,19 +6469,19 @@
         <v>13</v>
       </c>
       <c r="F284" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="s">
+        <v>110</v>
+      </c>
+      <c r="B285" t="s">
+        <v>44</v>
+      </c>
+      <c r="C285" t="s">
         <v>112</v>
       </c>
-      <c r="B285" t="s">
-        <v>45</v>
-      </c>
-      <c r="C285" t="s">
-        <v>114</v>
-      </c>
       <c r="D285" t="s">
         <v>9</v>
       </c>
@@ -6495,19 +6489,19 @@
         <v>10</v>
       </c>
       <c r="F285" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="s">
+        <v>110</v>
+      </c>
+      <c r="B286" t="s">
+        <v>44</v>
+      </c>
+      <c r="C286" t="s">
         <v>112</v>
       </c>
-      <c r="B286" t="s">
-        <v>45</v>
-      </c>
-      <c r="C286" t="s">
-        <v>114</v>
-      </c>
       <c r="D286" t="s">
         <v>9</v>
       </c>
@@ -6515,19 +6509,19 @@
         <v>12</v>
       </c>
       <c r="F286" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="s">
+        <v>110</v>
+      </c>
+      <c r="B287" t="s">
+        <v>44</v>
+      </c>
+      <c r="C287" t="s">
         <v>112</v>
       </c>
-      <c r="B287" t="s">
-        <v>45</v>
-      </c>
-      <c r="C287" t="s">
-        <v>114</v>
-      </c>
       <c r="D287" t="s">
         <v>9</v>
       </c>
@@ -6535,19 +6529,19 @@
         <v>13</v>
       </c>
       <c r="F287" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="s">
+        <v>110</v>
+      </c>
+      <c r="B288" t="s">
+        <v>44</v>
+      </c>
+      <c r="C288" t="s">
         <v>112</v>
       </c>
-      <c r="B288" t="s">
-        <v>45</v>
-      </c>
-      <c r="C288" t="s">
-        <v>114</v>
-      </c>
       <c r="D288" t="s">
         <v>14</v>
       </c>
@@ -6555,19 +6549,19 @@
         <v>10</v>
       </c>
       <c r="F288" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="s">
+        <v>110</v>
+      </c>
+      <c r="B289" t="s">
+        <v>44</v>
+      </c>
+      <c r="C289" t="s">
         <v>112</v>
       </c>
-      <c r="B289" t="s">
-        <v>45</v>
-      </c>
-      <c r="C289" t="s">
-        <v>114</v>
-      </c>
       <c r="D289" t="s">
         <v>14</v>
       </c>
@@ -6575,19 +6569,19 @@
         <v>12</v>
       </c>
       <c r="F289" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="s">
+        <v>110</v>
+      </c>
+      <c r="B290" t="s">
+        <v>44</v>
+      </c>
+      <c r="C290" t="s">
         <v>112</v>
       </c>
-      <c r="B290" t="s">
-        <v>45</v>
-      </c>
-      <c r="C290" t="s">
-        <v>114</v>
-      </c>
       <c r="D290" t="s">
         <v>14</v>
       </c>
@@ -6595,138 +6589,138 @@
         <v>13</v>
       </c>
       <c r="F290" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B291" t="s">
+        <v>120</v>
+      </c>
+      <c r="C291" t="s">
+        <v>121</v>
+      </c>
+      <c r="D291" t="s">
+        <v>9</v>
+      </c>
+      <c r="E291" t="s">
+        <v>10</v>
+      </c>
+      <c r="F291" t="s">
         <v>122</v>
-      </c>
-      <c r="C291" t="s">
-        <v>123</v>
-      </c>
-      <c r="D291" t="s">
-        <v>9</v>
-      </c>
-      <c r="E291" t="s">
-        <v>10</v>
-      </c>
-      <c r="F291" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B292" t="s">
+        <v>120</v>
+      </c>
+      <c r="C292" t="s">
+        <v>121</v>
+      </c>
+      <c r="D292" t="s">
+        <v>9</v>
+      </c>
+      <c r="E292" t="s">
+        <v>12</v>
+      </c>
+      <c r="F292" t="s">
         <v>122</v>
-      </c>
-      <c r="C292" t="s">
-        <v>123</v>
-      </c>
-      <c r="D292" t="s">
-        <v>9</v>
-      </c>
-      <c r="E292" t="s">
-        <v>12</v>
-      </c>
-      <c r="F292" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B293" t="s">
+        <v>120</v>
+      </c>
+      <c r="C293" t="s">
+        <v>121</v>
+      </c>
+      <c r="D293" t="s">
+        <v>9</v>
+      </c>
+      <c r="E293" t="s">
+        <v>13</v>
+      </c>
+      <c r="F293" t="s">
         <v>122</v>
-      </c>
-      <c r="C293" t="s">
-        <v>123</v>
-      </c>
-      <c r="D293" t="s">
-        <v>9</v>
-      </c>
-      <c r="E293" t="s">
-        <v>13</v>
-      </c>
-      <c r="F293" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B294" t="s">
+        <v>120</v>
+      </c>
+      <c r="C294" t="s">
+        <v>121</v>
+      </c>
+      <c r="D294" t="s">
+        <v>14</v>
+      </c>
+      <c r="E294" t="s">
+        <v>10</v>
+      </c>
+      <c r="F294" t="s">
         <v>122</v>
-      </c>
-      <c r="C294" t="s">
-        <v>123</v>
-      </c>
-      <c r="D294" t="s">
-        <v>14</v>
-      </c>
-      <c r="E294" t="s">
-        <v>10</v>
-      </c>
-      <c r="F294" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B295" t="s">
+        <v>120</v>
+      </c>
+      <c r="C295" t="s">
+        <v>121</v>
+      </c>
+      <c r="D295" t="s">
+        <v>14</v>
+      </c>
+      <c r="E295" t="s">
+        <v>12</v>
+      </c>
+      <c r="F295" t="s">
         <v>122</v>
-      </c>
-      <c r="C295" t="s">
-        <v>123</v>
-      </c>
-      <c r="D295" t="s">
-        <v>14</v>
-      </c>
-      <c r="E295" t="s">
-        <v>12</v>
-      </c>
-      <c r="F295" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B296" t="s">
+        <v>120</v>
+      </c>
+      <c r="C296" t="s">
+        <v>121</v>
+      </c>
+      <c r="D296" t="s">
+        <v>14</v>
+      </c>
+      <c r="E296" t="s">
+        <v>13</v>
+      </c>
+      <c r="F296" t="s">
         <v>122</v>
-      </c>
-      <c r="C296" t="s">
-        <v>123</v>
-      </c>
-      <c r="D296" t="s">
-        <v>14</v>
-      </c>
-      <c r="E296" t="s">
-        <v>13</v>
-      </c>
-      <c r="F296" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B297" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C297" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D297" t="s">
         <v>9</v>
@@ -6735,18 +6729,18 @@
         <v>10</v>
       </c>
       <c r="F297" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B298" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C298" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D298" t="s">
         <v>9</v>
@@ -6755,18 +6749,18 @@
         <v>12</v>
       </c>
       <c r="F298" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B299" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C299" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D299" t="s">
         <v>9</v>
@@ -6775,18 +6769,18 @@
         <v>13</v>
       </c>
       <c r="F299" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B300" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C300" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D300" t="s">
         <v>14</v>
@@ -6795,18 +6789,18 @@
         <v>10</v>
       </c>
       <c r="F300" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B301" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C301" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D301" t="s">
         <v>14</v>
@@ -6815,18 +6809,18 @@
         <v>12</v>
       </c>
       <c r="F301" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B302" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C302" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D302" t="s">
         <v>14</v>
@@ -6835,18 +6829,18 @@
         <v>13</v>
       </c>
       <c r="F302" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B303" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C303" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D303" t="s">
         <v>9</v>
@@ -6855,18 +6849,18 @@
         <v>10</v>
       </c>
       <c r="F303" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B304" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C304" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D304" t="s">
         <v>9</v>
@@ -6875,18 +6869,18 @@
         <v>12</v>
       </c>
       <c r="F304" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B305" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C305" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D305" t="s">
         <v>9</v>
@@ -6895,18 +6889,18 @@
         <v>13</v>
       </c>
       <c r="F305" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B306" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C306" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D306" t="s">
         <v>14</v>
@@ -6915,18 +6909,18 @@
         <v>10</v>
       </c>
       <c r="F306" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B307" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C307" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D307" t="s">
         <v>14</v>
@@ -6935,18 +6929,18 @@
         <v>12</v>
       </c>
       <c r="F307" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B308" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C308" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D308" t="s">
         <v>14</v>
@@ -6955,18 +6949,18 @@
         <v>13</v>
       </c>
       <c r="F308" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B309" t="s">
         <v>42</v>
       </c>
       <c r="C309" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D309" t="s">
         <v>9</v>
@@ -6975,18 +6969,18 @@
         <v>10</v>
       </c>
       <c r="F309" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B310" t="s">
         <v>42</v>
       </c>
       <c r="C310" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D310" t="s">
         <v>14</v>
@@ -6995,18 +6989,18 @@
         <v>10</v>
       </c>
       <c r="F310" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B311" t="s">
         <v>42</v>
       </c>
       <c r="C311" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D311" t="s">
         <v>9</v>
@@ -7015,19 +7009,19 @@
         <v>10</v>
       </c>
       <c r="F311" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B312" t="s">
+        <v>44</v>
+      </c>
+      <c r="C312" t="s">
         <v>45</v>
       </c>
-      <c r="C312" t="s">
-        <v>46</v>
-      </c>
       <c r="D312" t="s">
         <v>9</v>
       </c>
@@ -7035,19 +7029,19 @@
         <v>10</v>
       </c>
       <c r="F312" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B313" t="s">
+        <v>44</v>
+      </c>
+      <c r="C313" t="s">
         <v>45</v>
       </c>
-      <c r="C313" t="s">
-        <v>46</v>
-      </c>
       <c r="D313" t="s">
         <v>9</v>
       </c>
@@ -7055,19 +7049,19 @@
         <v>12</v>
       </c>
       <c r="F313" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B314" t="s">
+        <v>44</v>
+      </c>
+      <c r="C314" t="s">
         <v>45</v>
       </c>
-      <c r="C314" t="s">
-        <v>46</v>
-      </c>
       <c r="D314" t="s">
         <v>9</v>
       </c>
@@ -7075,18 +7069,18 @@
         <v>13</v>
       </c>
       <c r="F314" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B315" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C315" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D315" t="s">
         <v>9</v>
@@ -7095,18 +7089,18 @@
         <v>10</v>
       </c>
       <c r="F315" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B316" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C316" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D316" t="s">
         <v>9</v>
@@ -7115,18 +7109,18 @@
         <v>12</v>
       </c>
       <c r="F316" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B317" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C317" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D317" t="s">
         <v>9</v>
@@ -7135,18 +7129,18 @@
         <v>13</v>
       </c>
       <c r="F317" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B318" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C318" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D318" t="s">
         <v>14</v>
@@ -7155,18 +7149,18 @@
         <v>10</v>
       </c>
       <c r="F318" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B319" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C319" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D319" t="s">
         <v>14</v>
@@ -7175,18 +7169,18 @@
         <v>12</v>
       </c>
       <c r="F319" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B320" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C320" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D320" t="s">
         <v>14</v>
@@ -7195,18 +7189,18 @@
         <v>13</v>
       </c>
       <c r="F320" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B321" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C321" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D321" t="s">
         <v>9</v>
@@ -7215,18 +7209,18 @@
         <v>10</v>
       </c>
       <c r="F321" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B322" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C322" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D322" t="s">
         <v>9</v>
@@ -7235,18 +7229,18 @@
         <v>12</v>
       </c>
       <c r="F322" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B323" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C323" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D323" t="s">
         <v>9</v>
@@ -7255,18 +7249,18 @@
         <v>13</v>
       </c>
       <c r="F323" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B324" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C324" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D324" t="s">
         <v>14</v>
@@ -7275,18 +7269,18 @@
         <v>10</v>
       </c>
       <c r="F324" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B325" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C325" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D325" t="s">
         <v>14</v>
@@ -7295,18 +7289,18 @@
         <v>12</v>
       </c>
       <c r="F325" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B326" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C326" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D326" t="s">
         <v>14</v>
@@ -7315,18 +7309,18 @@
         <v>13</v>
       </c>
       <c r="F326" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B327" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C327" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D327" t="s">
         <v>9</v>
@@ -7335,18 +7329,18 @@
         <v>10</v>
       </c>
       <c r="F327" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B328" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C328" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D328" t="s">
         <v>9</v>
@@ -7355,18 +7349,18 @@
         <v>12</v>
       </c>
       <c r="F328" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B329" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C329" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D329" t="s">
         <v>9</v>
@@ -7375,138 +7369,138 @@
         <v>13</v>
       </c>
       <c r="F329" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="s">
+        <v>134</v>
+      </c>
+      <c r="B330" t="s">
+        <v>135</v>
+      </c>
+      <c r="C330" t="s">
+        <v>82</v>
+      </c>
+      <c r="D330" t="s">
+        <v>9</v>
+      </c>
+      <c r="E330" t="s">
+        <v>10</v>
+      </c>
+      <c r="F330" t="s">
         <v>136</v>
-      </c>
-      <c r="B330" t="s">
-        <v>137</v>
-      </c>
-      <c r="C330" t="s">
-        <v>83</v>
-      </c>
-      <c r="D330" t="s">
-        <v>9</v>
-      </c>
-      <c r="E330" t="s">
-        <v>10</v>
-      </c>
-      <c r="F330" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="s">
+        <v>134</v>
+      </c>
+      <c r="B331" t="s">
+        <v>135</v>
+      </c>
+      <c r="C331" t="s">
+        <v>82</v>
+      </c>
+      <c r="D331" t="s">
+        <v>9</v>
+      </c>
+      <c r="E331" t="s">
+        <v>12</v>
+      </c>
+      <c r="F331" t="s">
         <v>136</v>
-      </c>
-      <c r="B331" t="s">
-        <v>137</v>
-      </c>
-      <c r="C331" t="s">
-        <v>83</v>
-      </c>
-      <c r="D331" t="s">
-        <v>9</v>
-      </c>
-      <c r="E331" t="s">
-        <v>12</v>
-      </c>
-      <c r="F331" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="s">
+        <v>134</v>
+      </c>
+      <c r="B332" t="s">
+        <v>135</v>
+      </c>
+      <c r="C332" t="s">
+        <v>82</v>
+      </c>
+      <c r="D332" t="s">
+        <v>9</v>
+      </c>
+      <c r="E332" t="s">
+        <v>13</v>
+      </c>
+      <c r="F332" t="s">
         <v>136</v>
-      </c>
-      <c r="B332" t="s">
-        <v>137</v>
-      </c>
-      <c r="C332" t="s">
-        <v>83</v>
-      </c>
-      <c r="D332" t="s">
-        <v>9</v>
-      </c>
-      <c r="E332" t="s">
-        <v>13</v>
-      </c>
-      <c r="F332" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="s">
+        <v>134</v>
+      </c>
+      <c r="B333" t="s">
+        <v>135</v>
+      </c>
+      <c r="C333" t="s">
+        <v>82</v>
+      </c>
+      <c r="D333" t="s">
+        <v>14</v>
+      </c>
+      <c r="E333" t="s">
+        <v>10</v>
+      </c>
+      <c r="F333" t="s">
         <v>136</v>
-      </c>
-      <c r="B333" t="s">
-        <v>137</v>
-      </c>
-      <c r="C333" t="s">
-        <v>83</v>
-      </c>
-      <c r="D333" t="s">
-        <v>14</v>
-      </c>
-      <c r="E333" t="s">
-        <v>10</v>
-      </c>
-      <c r="F333" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="s">
+        <v>134</v>
+      </c>
+      <c r="B334" t="s">
+        <v>135</v>
+      </c>
+      <c r="C334" t="s">
+        <v>82</v>
+      </c>
+      <c r="D334" t="s">
+        <v>14</v>
+      </c>
+      <c r="E334" t="s">
+        <v>12</v>
+      </c>
+      <c r="F334" t="s">
         <v>136</v>
-      </c>
-      <c r="B334" t="s">
-        <v>137</v>
-      </c>
-      <c r="C334" t="s">
-        <v>83</v>
-      </c>
-      <c r="D334" t="s">
-        <v>14</v>
-      </c>
-      <c r="E334" t="s">
-        <v>12</v>
-      </c>
-      <c r="F334" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="s">
+        <v>134</v>
+      </c>
+      <c r="B335" t="s">
+        <v>135</v>
+      </c>
+      <c r="C335" t="s">
+        <v>82</v>
+      </c>
+      <c r="D335" t="s">
+        <v>14</v>
+      </c>
+      <c r="E335" t="s">
+        <v>13</v>
+      </c>
+      <c r="F335" t="s">
         <v>136</v>
-      </c>
-      <c r="B335" t="s">
-        <v>137</v>
-      </c>
-      <c r="C335" t="s">
-        <v>83</v>
-      </c>
-      <c r="D335" t="s">
-        <v>14</v>
-      </c>
-      <c r="E335" t="s">
-        <v>13</v>
-      </c>
-      <c r="F335" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B336" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C336" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D336" t="s">
         <v>9</v>
@@ -7515,18 +7509,18 @@
         <v>10</v>
       </c>
       <c r="F336" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B337" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C337" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D337" t="s">
         <v>9</v>
@@ -7535,18 +7529,18 @@
         <v>12</v>
       </c>
       <c r="F337" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B338" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C338" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D338" t="s">
         <v>9</v>
@@ -7555,18 +7549,18 @@
         <v>13</v>
       </c>
       <c r="F338" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B339" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C339" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D339" t="s">
         <v>14</v>
@@ -7575,18 +7569,18 @@
         <v>10</v>
       </c>
       <c r="F339" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B340" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C340" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D340" t="s">
         <v>14</v>
@@ -7595,18 +7589,18 @@
         <v>12</v>
       </c>
       <c r="F340" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B341" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C341" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D341" t="s">
         <v>14</v>
@@ -7615,18 +7609,18 @@
         <v>13</v>
       </c>
       <c r="F341" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B342" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C342" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D342" t="s">
         <v>9</v>
@@ -7635,18 +7629,18 @@
         <v>10</v>
       </c>
       <c r="F342" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B343" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C343" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D343" t="s">
         <v>9</v>
@@ -7655,18 +7649,18 @@
         <v>12</v>
       </c>
       <c r="F343" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B344" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C344" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D344" t="s">
         <v>9</v>
@@ -7675,18 +7669,18 @@
         <v>13</v>
       </c>
       <c r="F344" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B345" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C345" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D345" t="s">
         <v>14</v>
@@ -7695,18 +7689,18 @@
         <v>10</v>
       </c>
       <c r="F345" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B346" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C346" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D346" t="s">
         <v>14</v>
@@ -7715,18 +7709,18 @@
         <v>12</v>
       </c>
       <c r="F346" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B347" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C347" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D347" t="s">
         <v>14</v>
@@ -7735,18 +7729,18 @@
         <v>13</v>
       </c>
       <c r="F347" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B348" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C348" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D348" t="s">
         <v>9</v>
@@ -7755,18 +7749,18 @@
         <v>10</v>
       </c>
       <c r="F348" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B349" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C349" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D349" t="s">
         <v>9</v>
@@ -7775,18 +7769,18 @@
         <v>12</v>
       </c>
       <c r="F349" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B350" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C350" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D350" t="s">
         <v>9</v>
@@ -7795,18 +7789,18 @@
         <v>13</v>
       </c>
       <c r="F350" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B351" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C351" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D351" t="s">
         <v>14</v>
@@ -7815,18 +7809,18 @@
         <v>10</v>
       </c>
       <c r="F351" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B352" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C352" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D352" t="s">
         <v>14</v>
@@ -7835,18 +7829,18 @@
         <v>12</v>
       </c>
       <c r="F352" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B353" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C353" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D353" t="s">
         <v>14</v>
@@ -7855,7 +7849,7 @@
         <v>13</v>
       </c>
       <c r="F353" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/reports/series_reference.xlsx
+++ b/reports/series_reference.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="144">
   <si>
     <t xml:space="preserve">Theme</t>
   </si>
@@ -300,6 +300,9 @@
   </si>
   <si>
     <t xml:space="preserve">Canada ex-QC - French-Speaking Permanent Residents by Country of Citizenship</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Express Entry, Immigration Category, Immigration Category and Express Entry</t>
   </si>
   <si>
     <t xml:space="preserve">Canada ex-QC - French-Speaking Permanent Residents by Immigration Category</t>
@@ -4960,7 +4963,7 @@
         <v>90</v>
       </c>
       <c r="C209" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="D209" t="s">
         <v>9</v>
@@ -4969,7 +4972,7 @@
         <v>10</v>
       </c>
       <c r="F209" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="210">
@@ -4980,7 +4983,7 @@
         <v>90</v>
       </c>
       <c r="C210" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="D210" t="s">
         <v>9</v>
@@ -4989,7 +4992,7 @@
         <v>12</v>
       </c>
       <c r="F210" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="211">
@@ -5000,7 +5003,7 @@
         <v>90</v>
       </c>
       <c r="C211" t="s">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="D211" t="s">
         <v>9</v>
@@ -5009,7 +5012,7 @@
         <v>13</v>
       </c>
       <c r="F211" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="212">
@@ -5029,7 +5032,7 @@
         <v>10</v>
       </c>
       <c r="F212" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="213">
@@ -5049,7 +5052,7 @@
         <v>12</v>
       </c>
       <c r="F213" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="214">
@@ -5069,7 +5072,7 @@
         <v>13</v>
       </c>
       <c r="F214" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="215">
@@ -5089,7 +5092,7 @@
         <v>10</v>
       </c>
       <c r="F215" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="216">
@@ -5109,7 +5112,7 @@
         <v>12</v>
       </c>
       <c r="F216" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="217">
@@ -5129,7 +5132,7 @@
         <v>13</v>
       </c>
       <c r="F217" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="218">
@@ -5149,7 +5152,7 @@
         <v>10</v>
       </c>
       <c r="F218" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="219">
@@ -5169,7 +5172,7 @@
         <v>12</v>
       </c>
       <c r="F219" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="220">
@@ -5189,7 +5192,7 @@
         <v>13</v>
       </c>
       <c r="F220" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="221">
@@ -5209,7 +5212,7 @@
         <v>10</v>
       </c>
       <c r="F221" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="222">
@@ -5229,7 +5232,7 @@
         <v>12</v>
       </c>
       <c r="F222" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="223">
@@ -5249,7 +5252,7 @@
         <v>13</v>
       </c>
       <c r="F223" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="224">
@@ -5269,7 +5272,7 @@
         <v>10</v>
       </c>
       <c r="F224" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="225">
@@ -5289,7 +5292,7 @@
         <v>12</v>
       </c>
       <c r="F225" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="226">
@@ -5309,7 +5312,7 @@
         <v>13</v>
       </c>
       <c r="F226" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="227">
@@ -5329,7 +5332,7 @@
         <v>10</v>
       </c>
       <c r="F227" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="228">
@@ -5349,7 +5352,7 @@
         <v>12</v>
       </c>
       <c r="F228" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="229">
@@ -5369,7 +5372,7 @@
         <v>13</v>
       </c>
       <c r="F229" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="230">
@@ -5389,7 +5392,7 @@
         <v>10</v>
       </c>
       <c r="F230" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="231">
@@ -5409,7 +5412,7 @@
         <v>12</v>
       </c>
       <c r="F231" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="232">
@@ -5429,7 +5432,7 @@
         <v>13</v>
       </c>
       <c r="F232" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="233">
@@ -5449,7 +5452,7 @@
         <v>10</v>
       </c>
       <c r="F233" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="234">
@@ -5469,7 +5472,7 @@
         <v>10</v>
       </c>
       <c r="F234" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="235">
@@ -5489,7 +5492,7 @@
         <v>12</v>
       </c>
       <c r="F235" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="236">
@@ -5509,7 +5512,7 @@
         <v>12</v>
       </c>
       <c r="F236" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="237">
@@ -5529,7 +5532,7 @@
         <v>13</v>
       </c>
       <c r="F237" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="238">
@@ -5549,7 +5552,7 @@
         <v>13</v>
       </c>
       <c r="F238" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="239">
@@ -5569,7 +5572,7 @@
         <v>10</v>
       </c>
       <c r="F239" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="240">
@@ -5589,7 +5592,7 @@
         <v>10</v>
       </c>
       <c r="F240" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="241">
@@ -5609,7 +5612,7 @@
         <v>12</v>
       </c>
       <c r="F241" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="242">
@@ -5629,7 +5632,7 @@
         <v>12</v>
       </c>
       <c r="F242" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="243">
@@ -5649,7 +5652,7 @@
         <v>13</v>
       </c>
       <c r="F243" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="244">
@@ -5669,7 +5672,7 @@
         <v>13</v>
       </c>
       <c r="F244" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="245">
@@ -5689,7 +5692,7 @@
         <v>10</v>
       </c>
       <c r="F245" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="246">
@@ -5709,7 +5712,7 @@
         <v>12</v>
       </c>
       <c r="F246" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="247">
@@ -5729,18 +5732,18 @@
         <v>13</v>
       </c>
       <c r="F247" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B248" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C248" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D248" t="s">
         <v>9</v>
@@ -5749,18 +5752,18 @@
         <v>10</v>
       </c>
       <c r="F248" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B249" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C249" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D249" t="s">
         <v>9</v>
@@ -5769,18 +5772,18 @@
         <v>10</v>
       </c>
       <c r="F249" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B250" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C250" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D250" t="s">
         <v>14</v>
@@ -5789,18 +5792,18 @@
         <v>10</v>
       </c>
       <c r="F250" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B251" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C251" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D251" t="s">
         <v>9</v>
@@ -5809,12 +5812,12 @@
         <v>10</v>
       </c>
       <c r="F251" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B252" t="s">
         <v>42</v>
@@ -5829,12 +5832,12 @@
         <v>10</v>
       </c>
       <c r="F252" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B253" t="s">
         <v>42</v>
@@ -5849,12 +5852,12 @@
         <v>12</v>
       </c>
       <c r="F253" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B254" t="s">
         <v>42</v>
@@ -5869,12 +5872,12 @@
         <v>13</v>
       </c>
       <c r="F254" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B255" t="s">
         <v>42</v>
@@ -5889,12 +5892,12 @@
         <v>10</v>
       </c>
       <c r="F255" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B256" t="s">
         <v>42</v>
@@ -5909,12 +5912,12 @@
         <v>12</v>
       </c>
       <c r="F256" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B257" t="s">
         <v>42</v>
@@ -5929,12 +5932,12 @@
         <v>13</v>
       </c>
       <c r="F257" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B258" t="s">
         <v>42</v>
@@ -5949,12 +5952,12 @@
         <v>10</v>
       </c>
       <c r="F258" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B259" t="s">
         <v>42</v>
@@ -5969,12 +5972,12 @@
         <v>12</v>
       </c>
       <c r="F259" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B260" t="s">
         <v>42</v>
@@ -5989,18 +5992,18 @@
         <v>13</v>
       </c>
       <c r="F260" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B261" t="s">
         <v>42</v>
       </c>
       <c r="C261" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D261" t="s">
         <v>9</v>
@@ -6009,18 +6012,18 @@
         <v>10</v>
       </c>
       <c r="F261" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B262" t="s">
         <v>42</v>
       </c>
       <c r="C262" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D262" t="s">
         <v>9</v>
@@ -6029,18 +6032,18 @@
         <v>12</v>
       </c>
       <c r="F262" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B263" t="s">
         <v>42</v>
       </c>
       <c r="C263" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D263" t="s">
         <v>9</v>
@@ -6049,18 +6052,18 @@
         <v>13</v>
       </c>
       <c r="F263" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B264" t="s">
         <v>42</v>
       </c>
       <c r="C264" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D264" t="s">
         <v>14</v>
@@ -6069,18 +6072,18 @@
         <v>10</v>
       </c>
       <c r="F264" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B265" t="s">
         <v>42</v>
       </c>
       <c r="C265" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D265" t="s">
         <v>14</v>
@@ -6089,18 +6092,18 @@
         <v>12</v>
       </c>
       <c r="F265" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B266" t="s">
         <v>42</v>
       </c>
       <c r="C266" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D266" t="s">
         <v>14</v>
@@ -6109,12 +6112,12 @@
         <v>13</v>
       </c>
       <c r="F266" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B267" t="s">
         <v>42</v>
@@ -6129,18 +6132,18 @@
         <v>10</v>
       </c>
       <c r="F267" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B268" t="s">
         <v>42</v>
       </c>
       <c r="C268" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D268" t="s">
         <v>9</v>
@@ -6149,18 +6152,18 @@
         <v>10</v>
       </c>
       <c r="F268" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B269" t="s">
         <v>42</v>
       </c>
       <c r="C269" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D269" t="s">
         <v>14</v>
@@ -6169,12 +6172,12 @@
         <v>10</v>
       </c>
       <c r="F269" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B270" t="s">
         <v>42</v>
@@ -6189,12 +6192,12 @@
         <v>10</v>
       </c>
       <c r="F270" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B271" t="s">
         <v>42</v>
@@ -6209,12 +6212,12 @@
         <v>12</v>
       </c>
       <c r="F271" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B272" t="s">
         <v>42</v>
@@ -6229,12 +6232,12 @@
         <v>13</v>
       </c>
       <c r="F272" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B273" t="s">
         <v>42</v>
@@ -6249,12 +6252,12 @@
         <v>10</v>
       </c>
       <c r="F273" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B274" t="s">
         <v>42</v>
@@ -6269,12 +6272,12 @@
         <v>12</v>
       </c>
       <c r="F274" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B275" t="s">
         <v>42</v>
@@ -6289,12 +6292,12 @@
         <v>13</v>
       </c>
       <c r="F275" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B276" t="s">
         <v>44</v>
@@ -6309,12 +6312,12 @@
         <v>10</v>
       </c>
       <c r="F276" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B277" t="s">
         <v>44</v>
@@ -6329,12 +6332,12 @@
         <v>12</v>
       </c>
       <c r="F277" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B278" t="s">
         <v>44</v>
@@ -6349,12 +6352,12 @@
         <v>13</v>
       </c>
       <c r="F278" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B279" t="s">
         <v>44</v>
@@ -6369,12 +6372,12 @@
         <v>10</v>
       </c>
       <c r="F279" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B280" t="s">
         <v>44</v>
@@ -6389,12 +6392,12 @@
         <v>12</v>
       </c>
       <c r="F280" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B281" t="s">
         <v>44</v>
@@ -6409,12 +6412,12 @@
         <v>13</v>
       </c>
       <c r="F281" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B282" t="s">
         <v>44</v>
@@ -6429,12 +6432,12 @@
         <v>10</v>
       </c>
       <c r="F282" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B283" t="s">
         <v>44</v>
@@ -6449,12 +6452,12 @@
         <v>12</v>
       </c>
       <c r="F283" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B284" t="s">
         <v>44</v>
@@ -6469,18 +6472,18 @@
         <v>13</v>
       </c>
       <c r="F284" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B285" t="s">
         <v>44</v>
       </c>
       <c r="C285" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D285" t="s">
         <v>9</v>
@@ -6489,18 +6492,18 @@
         <v>10</v>
       </c>
       <c r="F285" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B286" t="s">
         <v>44</v>
       </c>
       <c r="C286" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D286" t="s">
         <v>9</v>
@@ -6509,18 +6512,18 @@
         <v>12</v>
       </c>
       <c r="F286" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B287" t="s">
         <v>44</v>
       </c>
       <c r="C287" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D287" t="s">
         <v>9</v>
@@ -6529,18 +6532,18 @@
         <v>13</v>
       </c>
       <c r="F287" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B288" t="s">
         <v>44</v>
       </c>
       <c r="C288" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D288" t="s">
         <v>14</v>
@@ -6549,18 +6552,18 @@
         <v>10</v>
       </c>
       <c r="F288" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B289" t="s">
         <v>44</v>
       </c>
       <c r="C289" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D289" t="s">
         <v>14</v>
@@ -6569,18 +6572,18 @@
         <v>12</v>
       </c>
       <c r="F289" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B290" t="s">
         <v>44</v>
       </c>
       <c r="C290" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D290" t="s">
         <v>14</v>
@@ -6589,18 +6592,18 @@
         <v>13</v>
       </c>
       <c r="F290" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B291" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C291" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D291" t="s">
         <v>9</v>
@@ -6609,18 +6612,18 @@
         <v>10</v>
       </c>
       <c r="F291" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B292" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C292" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D292" t="s">
         <v>9</v>
@@ -6629,18 +6632,18 @@
         <v>12</v>
       </c>
       <c r="F292" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B293" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C293" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D293" t="s">
         <v>9</v>
@@ -6649,18 +6652,18 @@
         <v>13</v>
       </c>
       <c r="F293" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B294" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C294" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D294" t="s">
         <v>14</v>
@@ -6669,18 +6672,18 @@
         <v>10</v>
       </c>
       <c r="F294" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B295" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C295" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D295" t="s">
         <v>14</v>
@@ -6689,18 +6692,18 @@
         <v>12</v>
       </c>
       <c r="F295" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B296" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C296" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D296" t="s">
         <v>14</v>
@@ -6709,18 +6712,18 @@
         <v>13</v>
       </c>
       <c r="F296" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B297" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C297" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D297" t="s">
         <v>9</v>
@@ -6729,18 +6732,18 @@
         <v>10</v>
       </c>
       <c r="F297" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B298" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C298" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D298" t="s">
         <v>9</v>
@@ -6749,18 +6752,18 @@
         <v>12</v>
       </c>
       <c r="F298" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B299" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C299" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D299" t="s">
         <v>9</v>
@@ -6769,18 +6772,18 @@
         <v>13</v>
       </c>
       <c r="F299" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B300" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C300" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D300" t="s">
         <v>14</v>
@@ -6789,18 +6792,18 @@
         <v>10</v>
       </c>
       <c r="F300" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B301" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C301" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D301" t="s">
         <v>14</v>
@@ -6809,18 +6812,18 @@
         <v>12</v>
       </c>
       <c r="F301" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B302" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C302" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D302" t="s">
         <v>14</v>
@@ -6829,18 +6832,18 @@
         <v>13</v>
       </c>
       <c r="F302" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B303" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C303" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D303" t="s">
         <v>9</v>
@@ -6849,18 +6852,18 @@
         <v>10</v>
       </c>
       <c r="F303" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B304" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C304" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D304" t="s">
         <v>9</v>
@@ -6869,18 +6872,18 @@
         <v>12</v>
       </c>
       <c r="F304" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B305" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C305" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D305" t="s">
         <v>9</v>
@@ -6889,18 +6892,18 @@
         <v>13</v>
       </c>
       <c r="F305" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B306" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C306" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D306" t="s">
         <v>14</v>
@@ -6909,18 +6912,18 @@
         <v>10</v>
       </c>
       <c r="F306" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B307" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C307" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D307" t="s">
         <v>14</v>
@@ -6929,18 +6932,18 @@
         <v>12</v>
       </c>
       <c r="F307" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B308" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C308" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D308" t="s">
         <v>14</v>
@@ -6949,12 +6952,12 @@
         <v>13</v>
       </c>
       <c r="F308" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B309" t="s">
         <v>42</v>
@@ -6969,12 +6972,12 @@
         <v>10</v>
       </c>
       <c r="F309" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B310" t="s">
         <v>42</v>
@@ -6989,12 +6992,12 @@
         <v>10</v>
       </c>
       <c r="F310" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B311" t="s">
         <v>42</v>
@@ -7009,12 +7012,12 @@
         <v>10</v>
       </c>
       <c r="F311" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B312" t="s">
         <v>44</v>
@@ -7029,12 +7032,12 @@
         <v>10</v>
       </c>
       <c r="F312" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B313" t="s">
         <v>44</v>
@@ -7049,12 +7052,12 @@
         <v>12</v>
       </c>
       <c r="F313" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B314" t="s">
         <v>44</v>
@@ -7069,12 +7072,12 @@
         <v>13</v>
       </c>
       <c r="F314" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B315" t="s">
         <v>44</v>
@@ -7089,12 +7092,12 @@
         <v>10</v>
       </c>
       <c r="F315" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B316" t="s">
         <v>44</v>
@@ -7109,12 +7112,12 @@
         <v>12</v>
       </c>
       <c r="F316" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B317" t="s">
         <v>44</v>
@@ -7129,12 +7132,12 @@
         <v>13</v>
       </c>
       <c r="F317" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B318" t="s">
         <v>44</v>
@@ -7149,12 +7152,12 @@
         <v>10</v>
       </c>
       <c r="F318" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B319" t="s">
         <v>44</v>
@@ -7169,12 +7172,12 @@
         <v>12</v>
       </c>
       <c r="F319" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B320" t="s">
         <v>44</v>
@@ -7189,12 +7192,12 @@
         <v>13</v>
       </c>
       <c r="F320" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B321" t="s">
         <v>44</v>
@@ -7209,12 +7212,12 @@
         <v>10</v>
       </c>
       <c r="F321" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B322" t="s">
         <v>44</v>
@@ -7229,12 +7232,12 @@
         <v>12</v>
       </c>
       <c r="F322" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B323" t="s">
         <v>44</v>
@@ -7249,12 +7252,12 @@
         <v>13</v>
       </c>
       <c r="F323" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B324" t="s">
         <v>44</v>
@@ -7269,12 +7272,12 @@
         <v>10</v>
       </c>
       <c r="F324" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B325" t="s">
         <v>44</v>
@@ -7289,12 +7292,12 @@
         <v>12</v>
       </c>
       <c r="F325" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B326" t="s">
         <v>44</v>
@@ -7309,12 +7312,12 @@
         <v>13</v>
       </c>
       <c r="F326" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B327" t="s">
         <v>44</v>
@@ -7329,12 +7332,12 @@
         <v>10</v>
       </c>
       <c r="F327" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B328" t="s">
         <v>44</v>
@@ -7349,12 +7352,12 @@
         <v>12</v>
       </c>
       <c r="F328" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B329" t="s">
         <v>44</v>
@@ -7369,15 +7372,15 @@
         <v>13</v>
       </c>
       <c r="F329" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B330" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C330" t="s">
         <v>82</v>
@@ -7389,15 +7392,15 @@
         <v>10</v>
       </c>
       <c r="F330" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B331" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C331" t="s">
         <v>82</v>
@@ -7409,15 +7412,15 @@
         <v>12</v>
       </c>
       <c r="F331" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B332" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C332" t="s">
         <v>82</v>
@@ -7429,15 +7432,15 @@
         <v>13</v>
       </c>
       <c r="F332" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B333" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C333" t="s">
         <v>82</v>
@@ -7449,15 +7452,15 @@
         <v>10</v>
       </c>
       <c r="F333" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B334" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C334" t="s">
         <v>82</v>
@@ -7469,15 +7472,15 @@
         <v>12</v>
       </c>
       <c r="F334" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B335" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C335" t="s">
         <v>82</v>
@@ -7489,15 +7492,15 @@
         <v>13</v>
       </c>
       <c r="F335" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B336" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C336" t="s">
         <v>82</v>
@@ -7509,15 +7512,15 @@
         <v>10</v>
       </c>
       <c r="F336" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B337" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C337" t="s">
         <v>82</v>
@@ -7529,15 +7532,15 @@
         <v>12</v>
       </c>
       <c r="F337" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B338" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C338" t="s">
         <v>82</v>
@@ -7549,15 +7552,15 @@
         <v>13</v>
       </c>
       <c r="F338" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B339" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C339" t="s">
         <v>82</v>
@@ -7569,15 +7572,15 @@
         <v>10</v>
       </c>
       <c r="F339" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B340" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C340" t="s">
         <v>82</v>
@@ -7589,15 +7592,15 @@
         <v>12</v>
       </c>
       <c r="F340" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B341" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C341" t="s">
         <v>82</v>
@@ -7609,15 +7612,15 @@
         <v>13</v>
       </c>
       <c r="F341" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B342" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C342" t="s">
         <v>82</v>
@@ -7629,15 +7632,15 @@
         <v>10</v>
       </c>
       <c r="F342" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B343" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C343" t="s">
         <v>82</v>
@@ -7649,15 +7652,15 @@
         <v>12</v>
       </c>
       <c r="F343" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B344" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C344" t="s">
         <v>82</v>
@@ -7669,15 +7672,15 @@
         <v>13</v>
       </c>
       <c r="F344" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B345" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C345" t="s">
         <v>82</v>
@@ -7689,15 +7692,15 @@
         <v>10</v>
       </c>
       <c r="F345" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B346" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C346" t="s">
         <v>82</v>
@@ -7709,15 +7712,15 @@
         <v>12</v>
       </c>
       <c r="F346" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B347" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C347" t="s">
         <v>82</v>
@@ -7729,15 +7732,15 @@
         <v>13</v>
       </c>
       <c r="F347" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B348" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C348" t="s">
         <v>82</v>
@@ -7749,15 +7752,15 @@
         <v>10</v>
       </c>
       <c r="F348" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B349" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C349" t="s">
         <v>82</v>
@@ -7769,15 +7772,15 @@
         <v>12</v>
       </c>
       <c r="F349" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B350" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C350" t="s">
         <v>82</v>
@@ -7789,15 +7792,15 @@
         <v>13</v>
       </c>
       <c r="F350" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B351" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C351" t="s">
         <v>82</v>
@@ -7809,15 +7812,15 @@
         <v>10</v>
       </c>
       <c r="F351" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B352" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C352" t="s">
         <v>82</v>
@@ -7829,15 +7832,15 @@
         <v>12</v>
       </c>
       <c r="F352" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B353" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C353" t="s">
         <v>82</v>
@@ -7849,7 +7852,7 @@
         <v>13</v>
       </c>
       <c r="F353" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>

--- a/reports/series_reference.xlsx
+++ b/reports/series_reference.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="182">
   <si>
     <t xml:space="preserve">Theme</t>
   </si>
@@ -137,6 +137,135 @@
     <t xml:space="preserve">Canada - Asylum Claimants by Top 25 Countries of Citizenship in the Most Recent Complete Year, Province/Territory of Claim, Claim Month</t>
   </si>
   <si>
+    <t xml:space="preserve">Express Entry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admissions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Permanent Residents under Express Entry by Gender and Province/Territory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Permanent Residents under Express Entry by Intended Destination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Permanent Residents under Express Entry by Province/Territory and Age Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Country of Birth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Permanent Residents under Express Entry by Province/Territory and Country of Birth</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Permanent Residents under Express Entry by Province/Territory and Country of Citizenship</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Immigration Category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Permanent Residents under Express Entry by Province/Territory and Immigration Category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intended Occupation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Permanent Residents under Express Entry by Province/Territory and Intended Occupation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invited candidates who applied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invitation Category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Express Entry Candidates by Province/Territory and Invitation Category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age Group, Invitation Category and Age Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Express Entry Candidates by Province/Territory, Invitation Category and Age Group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Express Entry Candidates by Province/Territory, Invitation Category and Census Metropolitan Area of Intended Destination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Country of Citizenship, Invitation Category and Country of Citizenship</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Express Entry Candidates by Province/Territory, Invitation Category and Country of Citizenship (2025 ranking)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field of Study, Invitation Category and Field of Study</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Express Entry Candidates by Province/Territory, Invitation Category and Field of Study</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRS Score at Invitation, Invitation Category and CRS Score at Invitation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Express Entry Candidates by Province/Territory, Invitation Category and Invitation to Apply (ITA) Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invitation Category and Level of Canadian Education, Level of Canadian Education</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Express Entry Candidates by Province/Territory, Invitation Category and Level of Canadian Education</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invitation Category and Level of Foreign Education, Level of Foreign Education</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Express Entry Candidates by Province/Territory, Invitation Category and Level of Foreign Education</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invitation Category and First Official Language Tested, Tested for First Official Language</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Express Entry Candidates by Province/Territory, Invitation Category and Tested for First Official Language</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invited candidates who applied (Canadian Experience Class)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Occupation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Express Entry Candidates under Canadian Experience Class Invitation Category by Province/Territory and Occupation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invited candidates who applied (Federal Skilled Trades Program)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Express Entry Candidates under Federal Skilled Trades Invitation Category by Province/Territory and Occupation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invited candidates who applied (Federal Skilled Worker Program)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Express Entry Candidates under Federal Skilled Worker Invitation Category by Province/Territory and Occupation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invited candidates who applied (Provincial Nominee Program)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Canada - Express Entry Candidates under Provincial Nominee Program Invitation Category by Province/Territory and Occupation</t>
+  </si>
+  <si>
     <t xml:space="preserve">International Mobility Program</t>
   </si>
   <si>
@@ -203,21 +332,12 @@
     <t xml:space="preserve">Permits under post-grad employment</t>
   </si>
   <si>
-    <t xml:space="preserve">CD</t>
-  </si>
-  <si>
     <t xml:space="preserve">Canada - International Mobility Program (IMP) work permit holders under post-graduate employment by province/territory, Census Division and Census Subdivision of the Intended Destination and year in which permit(s) became effective</t>
   </si>
   <si>
-    <t xml:space="preserve">CSD</t>
-  </si>
-  <si>
     <t xml:space="preserve">Permits under post-grad employment (at December 31)</t>
   </si>
   <si>
-    <t xml:space="preserve">CMA</t>
-  </si>
-  <si>
     <t xml:space="preserve">Canada – International Mobility Program Work Permit Holders under Post-Graduate Employment on December 31st by Province/Territory and Census Metropolitan Area (CMA) of Intended Destination</t>
   </si>
   <si>
@@ -248,9 +368,6 @@
     <t xml:space="preserve">Canada - Permanent Residents by Country of Citizenship and Immigration Category</t>
   </si>
   <si>
-    <t xml:space="preserve">Age Group</t>
-  </si>
-  <si>
     <t xml:space="preserve">Canada - Permanent Residents by Province/Territory and Age Group</t>
   </si>
   <si>
@@ -258,9 +375,6 @@
   </si>
   <si>
     <t xml:space="preserve">Canada - Permanent Residents by Province/Territory and Gender</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Immigration Category</t>
   </si>
   <si>
     <t xml:space="preserve">Canada - Permanent Residents by Province/Territory and Immigration Category</t>
@@ -491,8 +605,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:F353" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:F353"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A1:F428" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:F428"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Theme"/>
     <tableColumn id="2" name="Series"/>
@@ -1943,7 +2057,7 @@
         <v>42</v>
       </c>
       <c r="C58" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D58" t="s">
         <v>9</v>
@@ -1960,19 +2074,19 @@
         <v>41</v>
       </c>
       <c r="B59" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C59" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="D59" t="s">
         <v>9</v>
       </c>
       <c r="E59" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F59" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="60">
@@ -1980,19 +2094,19 @@
         <v>41</v>
       </c>
       <c r="B60" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C60" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="D60" t="s">
         <v>9</v>
       </c>
       <c r="E60" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F60" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="61">
@@ -2000,19 +2114,19 @@
         <v>41</v>
       </c>
       <c r="B61" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C61" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="D61" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E61" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F61" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
     </row>
     <row r="62">
@@ -2020,19 +2134,19 @@
         <v>41</v>
       </c>
       <c r="B62" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C62" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="D62" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E62" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F62" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="63">
@@ -2040,19 +2154,19 @@
         <v>41</v>
       </c>
       <c r="B63" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C63" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="D63" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E63" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F63" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="64">
@@ -2060,19 +2174,19 @@
         <v>41</v>
       </c>
       <c r="B64" t="s">
+        <v>42</v>
+      </c>
+      <c r="C64" t="s">
+        <v>20</v>
+      </c>
+      <c r="D64" t="s">
         <v>44</v>
       </c>
-      <c r="C64" t="s">
-        <v>47</v>
-      </c>
-      <c r="D64" t="s">
-        <v>9</v>
-      </c>
       <c r="E64" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F64" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="65">
@@ -2080,19 +2194,19 @@
         <v>41</v>
       </c>
       <c r="B65" t="s">
+        <v>42</v>
+      </c>
+      <c r="C65" t="s">
+        <v>20</v>
+      </c>
+      <c r="D65" t="s">
         <v>44</v>
       </c>
-      <c r="C65" t="s">
-        <v>47</v>
-      </c>
-      <c r="D65" t="s">
-        <v>14</v>
-      </c>
       <c r="E65" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F65" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="66">
@@ -2100,19 +2214,19 @@
         <v>41</v>
       </c>
       <c r="B66" t="s">
+        <v>42</v>
+      </c>
+      <c r="C66" t="s">
+        <v>20</v>
+      </c>
+      <c r="D66" t="s">
         <v>44</v>
       </c>
-      <c r="C66" t="s">
-        <v>47</v>
-      </c>
-      <c r="D66" t="s">
-        <v>14</v>
-      </c>
       <c r="E66" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F66" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="67">
@@ -2120,19 +2234,19 @@
         <v>41</v>
       </c>
       <c r="B67" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C67" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="D67" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="E67" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F67" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="68">
@@ -2140,19 +2254,19 @@
         <v>41</v>
       </c>
       <c r="B68" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C68" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="D68" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="E68" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F68" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="69">
@@ -2160,19 +2274,19 @@
         <v>41</v>
       </c>
       <c r="B69" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C69" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="D69" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="E69" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F69" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="70">
@@ -2180,19 +2294,19 @@
         <v>41</v>
       </c>
       <c r="B70" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C70" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="D70" t="s">
         <v>9</v>
       </c>
       <c r="E70" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F70" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="71">
@@ -2200,19 +2314,19 @@
         <v>41</v>
       </c>
       <c r="B71" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C71" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="D71" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E71" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F71" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="72">
@@ -2220,19 +2334,19 @@
         <v>41</v>
       </c>
       <c r="B72" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C72" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="D72" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E72" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F72" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="73">
@@ -2240,19 +2354,19 @@
         <v>41</v>
       </c>
       <c r="B73" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C73" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="D73" t="s">
         <v>14</v>
       </c>
       <c r="E73" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F73" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="74">
@@ -2260,19 +2374,19 @@
         <v>41</v>
       </c>
       <c r="B74" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C74" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="D74" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E74" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F74" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
     </row>
     <row r="75">
@@ -2280,19 +2394,19 @@
         <v>41</v>
       </c>
       <c r="B75" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C75" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="D75" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E75" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F75" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
     </row>
     <row r="76">
@@ -2300,19 +2414,19 @@
         <v>41</v>
       </c>
       <c r="B76" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C76" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D76" t="s">
         <v>9</v>
       </c>
       <c r="E76" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F76" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="77">
@@ -2320,19 +2434,19 @@
         <v>41</v>
       </c>
       <c r="B77" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C77" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D77" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E77" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F77" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="78">
@@ -2340,19 +2454,19 @@
         <v>41</v>
       </c>
       <c r="B78" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C78" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D78" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E78" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F78" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="79">
@@ -2360,19 +2474,19 @@
         <v>41</v>
       </c>
       <c r="B79" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C79" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D79" t="s">
         <v>14</v>
       </c>
       <c r="E79" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F79" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="80">
@@ -2380,19 +2494,19 @@
         <v>41</v>
       </c>
       <c r="B80" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C80" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="D80" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E80" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F80" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="81">
@@ -2400,19 +2514,19 @@
         <v>41</v>
       </c>
       <c r="B81" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C81" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="D81" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E81" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F81" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="82">
@@ -2420,19 +2534,19 @@
         <v>41</v>
       </c>
       <c r="B82" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C82" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="D82" t="s">
         <v>9</v>
       </c>
       <c r="E82" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F82" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="83">
@@ -2440,19 +2554,19 @@
         <v>41</v>
       </c>
       <c r="B83" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C83" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="D83" t="s">
         <v>9</v>
       </c>
       <c r="E83" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F83" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="84">
@@ -2460,19 +2574,19 @@
         <v>41</v>
       </c>
       <c r="B84" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C84" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="D84" t="s">
         <v>9</v>
       </c>
       <c r="E84" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F84" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="85">
@@ -2480,19 +2594,19 @@
         <v>41</v>
       </c>
       <c r="B85" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C85" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
       <c r="D85" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E85" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F85" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="86">
@@ -2500,19 +2614,19 @@
         <v>41</v>
       </c>
       <c r="B86" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C86" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D86" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E86" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F86" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
     <row r="87">
@@ -2520,19 +2634,19 @@
         <v>41</v>
       </c>
       <c r="B87" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C87" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="D87" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E87" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F87" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
     </row>
     <row r="88">
@@ -2540,19 +2654,19 @@
         <v>41</v>
       </c>
       <c r="B88" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C88" t="s">
-        <v>56</v>
+        <v>23</v>
       </c>
       <c r="D88" t="s">
         <v>9</v>
       </c>
       <c r="E88" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F88" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="89">
@@ -2560,19 +2674,19 @@
         <v>41</v>
       </c>
       <c r="B89" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C89" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D89" t="s">
         <v>9</v>
       </c>
       <c r="E89" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F89" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="90">
@@ -2580,19 +2694,19 @@
         <v>41</v>
       </c>
       <c r="B90" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C90" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D90" t="s">
         <v>9</v>
       </c>
       <c r="E90" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F90" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="91">
@@ -2600,19 +2714,19 @@
         <v>41</v>
       </c>
       <c r="B91" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C91" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D91" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E91" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F91" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="92">
@@ -2620,19 +2734,19 @@
         <v>41</v>
       </c>
       <c r="B92" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C92" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D92" t="s">
         <v>14</v>
       </c>
       <c r="E92" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F92" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="93">
@@ -2640,19 +2754,19 @@
         <v>41</v>
       </c>
       <c r="B93" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C93" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D93" t="s">
         <v>14</v>
       </c>
       <c r="E93" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F93" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
     </row>
     <row r="94">
@@ -2660,19 +2774,19 @@
         <v>41</v>
       </c>
       <c r="B94" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C94" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="D94" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E94" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F94" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="95">
@@ -2680,19 +2794,19 @@
         <v>41</v>
       </c>
       <c r="B95" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="C95" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D95" t="s">
         <v>9</v>
       </c>
       <c r="E95" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F95" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="96">
@@ -2700,19 +2814,19 @@
         <v>41</v>
       </c>
       <c r="B96" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="C96" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D96" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E96" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F96" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
     </row>
     <row r="97">
@@ -2720,19 +2834,19 @@
         <v>41</v>
       </c>
       <c r="B97" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="C97" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="D97" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E97" t="s">
         <v>10</v>
       </c>
       <c r="F97" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="98">
@@ -2740,19 +2854,19 @@
         <v>41</v>
       </c>
       <c r="B98" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="C98" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="D98" t="s">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="E98" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F98" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
     </row>
     <row r="99">
@@ -2760,19 +2874,19 @@
         <v>41</v>
       </c>
       <c r="B99" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="C99" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="D99" t="s">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="E99" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F99" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
     </row>
     <row r="100">
@@ -2780,19 +2894,19 @@
         <v>41</v>
       </c>
       <c r="B100" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="C100" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="D100" t="s">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="E100" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F100" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="101">
@@ -2800,19 +2914,19 @@
         <v>41</v>
       </c>
       <c r="B101" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="C101" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="D101" t="s">
-        <v>65</v>
+        <v>9</v>
       </c>
       <c r="E101" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F101" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="102">
@@ -2820,19 +2934,19 @@
         <v>41</v>
       </c>
       <c r="B102" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="C102" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="D102" t="s">
-        <v>65</v>
+        <v>9</v>
       </c>
       <c r="E102" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F102" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="103">
@@ -2840,19 +2954,19 @@
         <v>41</v>
       </c>
       <c r="B103" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="C103" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="D103" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="E103" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F103" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="104">
@@ -2860,19 +2974,19 @@
         <v>41</v>
       </c>
       <c r="B104" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="C104" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="D104" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E104" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F104" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="105">
@@ -2880,19 +2994,19 @@
         <v>41</v>
       </c>
       <c r="B105" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="C105" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="D105" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E105" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F105" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="106">
@@ -2900,19 +3014,19 @@
         <v>41</v>
       </c>
       <c r="B106" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C106" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="D106" t="s">
         <v>9</v>
       </c>
       <c r="E106" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F106" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="107">
@@ -2920,10 +3034,10 @@
         <v>41</v>
       </c>
       <c r="B107" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C107" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="D107" t="s">
         <v>14</v>
@@ -2932,7 +3046,7 @@
         <v>10</v>
       </c>
       <c r="F107" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="108">
@@ -2940,19 +3054,19 @@
         <v>41</v>
       </c>
       <c r="B108" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C108" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="D108" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E108" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F108" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="109">
@@ -2960,19 +3074,19 @@
         <v>41</v>
       </c>
       <c r="B109" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="C109" t="s">
-        <v>20</v>
+        <v>59</v>
       </c>
       <c r="D109" t="s">
         <v>14</v>
       </c>
       <c r="E109" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F109" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="110">
@@ -2980,19 +3094,19 @@
         <v>41</v>
       </c>
       <c r="B110" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="C110" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="D110" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E110" t="s">
         <v>10</v>
       </c>
       <c r="F110" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="111">
@@ -3000,10 +3114,10 @@
         <v>41</v>
       </c>
       <c r="B111" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="C111" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="D111" t="s">
         <v>9</v>
@@ -3012,7 +3126,7 @@
         <v>10</v>
       </c>
       <c r="F111" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="112">
@@ -3020,10 +3134,10 @@
         <v>41</v>
       </c>
       <c r="B112" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="C112" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
       <c r="D112" t="s">
         <v>14</v>
@@ -3032,7 +3146,7 @@
         <v>10</v>
       </c>
       <c r="F112" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
     </row>
     <row r="113">
@@ -3040,19 +3154,19 @@
         <v>41</v>
       </c>
       <c r="B113" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="C113" t="s">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="D113" t="s">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="E113" t="s">
         <v>10</v>
       </c>
       <c r="F113" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="114">
@@ -3060,19 +3174,19 @@
         <v>41</v>
       </c>
       <c r="B114" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="C114" t="s">
-        <v>20</v>
+        <v>63</v>
       </c>
       <c r="D114" t="s">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="E114" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F114" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="115">
@@ -3080,19 +3194,19 @@
         <v>41</v>
       </c>
       <c r="B115" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="C115" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="D115" t="s">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="E115" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F115" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="116">
@@ -3100,19 +3214,19 @@
         <v>41</v>
       </c>
       <c r="B116" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="C116" t="s">
-        <v>20</v>
+        <v>65</v>
       </c>
       <c r="D116" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E116" t="s">
         <v>10</v>
       </c>
       <c r="F116" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="117">
@@ -3120,19 +3234,19 @@
         <v>41</v>
       </c>
       <c r="B117" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="C117" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="D117" t="s">
         <v>9</v>
       </c>
       <c r="E117" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F117" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="118">
@@ -3140,19 +3254,19 @@
         <v>41</v>
       </c>
       <c r="B118" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="C118" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="D118" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E118" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F118" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="119">
@@ -3160,13 +3274,13 @@
         <v>41</v>
       </c>
       <c r="B119" t="s">
+        <v>56</v>
+      </c>
+      <c r="C119" t="s">
         <v>69</v>
       </c>
-      <c r="C119" t="s">
-        <v>20</v>
-      </c>
       <c r="D119" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E119" t="s">
         <v>10</v>
@@ -3180,16 +3294,16 @@
         <v>41</v>
       </c>
       <c r="B120" t="s">
+        <v>56</v>
+      </c>
+      <c r="C120" t="s">
         <v>69</v>
       </c>
-      <c r="C120" t="s">
-        <v>20</v>
-      </c>
       <c r="D120" t="s">
         <v>14</v>
       </c>
       <c r="E120" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F120" t="s">
         <v>70</v>
@@ -3200,47 +3314,47 @@
         <v>41</v>
       </c>
       <c r="B121" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="C121" t="s">
-        <v>20</v>
+        <v>71</v>
       </c>
       <c r="D121" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E121" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F121" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
+        <v>41</v>
+      </c>
+      <c r="B122" t="s">
+        <v>56</v>
+      </c>
+      <c r="C122" t="s">
         <v>71</v>
       </c>
-      <c r="B122" t="s">
+      <c r="D122" t="s">
+        <v>14</v>
+      </c>
+      <c r="E122" t="s">
+        <v>10</v>
+      </c>
+      <c r="F122" t="s">
         <v>72</v>
-      </c>
-      <c r="C122" t="s">
-        <v>73</v>
-      </c>
-      <c r="D122" t="s">
-        <v>9</v>
-      </c>
-      <c r="E122" t="s">
-        <v>10</v>
-      </c>
-      <c r="F122" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="B123" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="C123" t="s">
         <v>73</v>
@@ -3249,7 +3363,7 @@
         <v>9</v>
       </c>
       <c r="E123" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F123" t="s">
         <v>74</v>
@@ -3257,19 +3371,19 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="B124" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="C124" t="s">
         <v>73</v>
       </c>
       <c r="D124" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E124" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F124" t="s">
         <v>74</v>
@@ -3277,7 +3391,7 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="B125" t="s">
         <v>75</v>
@@ -3297,7 +3411,7 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="B126" t="s">
         <v>75</v>
@@ -3306,10 +3420,10 @@
         <v>76</v>
       </c>
       <c r="D126" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E126" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F126" t="s">
         <v>77</v>
@@ -3317,10 +3431,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="B127" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C127" t="s">
         <v>76</v>
@@ -3329,24 +3443,24 @@
         <v>9</v>
       </c>
       <c r="E127" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F127" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="B128" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C128" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D128" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E128" t="s">
         <v>10</v>
@@ -3357,173 +3471,173 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="B129" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C129" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D129" t="s">
         <v>9</v>
       </c>
       <c r="E129" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F129" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="B130" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C130" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D130" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E130" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F130" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="B131" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C131" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D131" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E131" t="s">
         <v>10</v>
       </c>
       <c r="F131" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="B132" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C132" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D132" t="s">
         <v>14</v>
       </c>
       <c r="E132" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F132" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B133" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="C133" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="D133" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E133" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F133" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B134" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="C134" t="s">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="D134" t="s">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="E134" t="s">
         <v>10</v>
       </c>
       <c r="F134" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B135" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="C135" t="s">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="D135" t="s">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="E135" t="s">
         <v>12</v>
       </c>
       <c r="F135" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B136" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="C136" t="s">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="D136" t="s">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="E136" t="s">
         <v>13</v>
       </c>
       <c r="F136" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B137" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="C137" t="s">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="D137" t="s">
         <v>9</v>
@@ -3532,18 +3646,18 @@
         <v>10</v>
       </c>
       <c r="F137" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B138" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="C138" t="s">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="D138" t="s">
         <v>9</v>
@@ -3552,18 +3666,18 @@
         <v>12</v>
       </c>
       <c r="F138" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B139" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="C139" t="s">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="D139" t="s">
         <v>9</v>
@@ -3572,18 +3686,18 @@
         <v>13</v>
       </c>
       <c r="F139" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B140" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="C140" t="s">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="D140" t="s">
         <v>14</v>
@@ -3592,18 +3706,18 @@
         <v>10</v>
       </c>
       <c r="F140" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B141" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="C141" t="s">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="D141" t="s">
         <v>14</v>
@@ -3612,18 +3726,18 @@
         <v>12</v>
       </c>
       <c r="F141" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B142" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="C142" t="s">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="D142" t="s">
         <v>14</v>
@@ -3632,18 +3746,18 @@
         <v>13</v>
       </c>
       <c r="F142" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B143" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="C143" t="s">
-        <v>17</v>
+        <v>92</v>
       </c>
       <c r="D143" t="s">
         <v>9</v>
@@ -3652,18 +3766,18 @@
         <v>10</v>
       </c>
       <c r="F143" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B144" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="C144" t="s">
-        <v>17</v>
+        <v>92</v>
       </c>
       <c r="D144" t="s">
         <v>9</v>
@@ -3672,18 +3786,18 @@
         <v>12</v>
       </c>
       <c r="F144" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B145" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="C145" t="s">
-        <v>17</v>
+        <v>92</v>
       </c>
       <c r="D145" t="s">
         <v>9</v>
@@ -3692,18 +3806,18 @@
         <v>13</v>
       </c>
       <c r="F145" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B146" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="C146" t="s">
-        <v>17</v>
+        <v>92</v>
       </c>
       <c r="D146" t="s">
         <v>14</v>
@@ -3712,18 +3826,18 @@
         <v>10</v>
       </c>
       <c r="F146" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B147" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="C147" t="s">
-        <v>17</v>
+        <v>92</v>
       </c>
       <c r="D147" t="s">
         <v>14</v>
@@ -3732,18 +3846,18 @@
         <v>12</v>
       </c>
       <c r="F147" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B148" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="C148" t="s">
-        <v>17</v>
+        <v>92</v>
       </c>
       <c r="D148" t="s">
         <v>14</v>
@@ -3752,18 +3866,18 @@
         <v>13</v>
       </c>
       <c r="F148" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B149" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="C149" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="D149" t="s">
         <v>9</v>
@@ -3772,18 +3886,18 @@
         <v>10</v>
       </c>
       <c r="F149" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B150" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="C150" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="D150" t="s">
         <v>9</v>
@@ -3792,18 +3906,18 @@
         <v>12</v>
       </c>
       <c r="F150" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B151" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="C151" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="D151" t="s">
         <v>9</v>
@@ -3812,18 +3926,18 @@
         <v>13</v>
       </c>
       <c r="F151" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B152" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="C152" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="D152" t="s">
         <v>14</v>
@@ -3832,18 +3946,18 @@
         <v>10</v>
       </c>
       <c r="F152" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B153" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="C153" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="D153" t="s">
         <v>14</v>
@@ -3852,18 +3966,18 @@
         <v>12</v>
       </c>
       <c r="F153" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B154" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="C154" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="D154" t="s">
         <v>14</v>
@@ -3872,18 +3986,18 @@
         <v>13</v>
       </c>
       <c r="F154" t="s">
-        <v>83</v>
+        <v>95</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B155" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="C155" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="D155" t="s">
         <v>9</v>
@@ -3892,18 +4006,18 @@
         <v>10</v>
       </c>
       <c r="F155" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B156" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="C156" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="D156" t="s">
         <v>9</v>
@@ -3912,18 +4026,18 @@
         <v>12</v>
       </c>
       <c r="F156" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B157" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="C157" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="D157" t="s">
         <v>9</v>
@@ -3932,438 +4046,438 @@
         <v>13</v>
       </c>
       <c r="F157" t="s">
-        <v>85</v>
+        <v>96</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B158" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="C158" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="D158" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E158" t="s">
         <v>10</v>
       </c>
       <c r="F158" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B159" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="C159" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="D159" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E159" t="s">
         <v>12</v>
       </c>
       <c r="F159" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B160" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="C160" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="D160" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E160" t="s">
         <v>13</v>
       </c>
       <c r="F160" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B161" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="C161" t="s">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="D161" t="s">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="E161" t="s">
         <v>10</v>
       </c>
       <c r="F161" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B162" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="C162" t="s">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="D162" t="s">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="E162" t="s">
         <v>12</v>
       </c>
       <c r="F162" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B163" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="C163" t="s">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="D163" t="s">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="E163" t="s">
         <v>13</v>
       </c>
       <c r="F163" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B164" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="C164" t="s">
         <v>20</v>
       </c>
       <c r="D164" t="s">
-        <v>65</v>
+        <v>9</v>
       </c>
       <c r="E164" t="s">
         <v>10</v>
       </c>
       <c r="F164" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B165" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="C165" t="s">
         <v>20</v>
       </c>
       <c r="D165" t="s">
-        <v>65</v>
+        <v>9</v>
       </c>
       <c r="E165" t="s">
         <v>12</v>
       </c>
       <c r="F165" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B166" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="C166" t="s">
         <v>20</v>
       </c>
       <c r="D166" t="s">
-        <v>65</v>
+        <v>9</v>
       </c>
       <c r="E166" t="s">
         <v>13</v>
       </c>
       <c r="F166" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B167" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="C167" t="s">
         <v>20</v>
       </c>
       <c r="D167" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E167" t="s">
         <v>10</v>
       </c>
       <c r="F167" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B168" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="C168" t="s">
         <v>20</v>
       </c>
       <c r="D168" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E168" t="s">
         <v>12</v>
       </c>
       <c r="F168" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B169" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="C169" t="s">
         <v>20</v>
       </c>
       <c r="D169" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E169" t="s">
         <v>13</v>
       </c>
       <c r="F169" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B170" t="s">
-        <v>75</v>
+        <v>102</v>
       </c>
       <c r="C170" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="D170" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E170" t="s">
         <v>10</v>
       </c>
       <c r="F170" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B171" t="s">
-        <v>75</v>
+        <v>102</v>
       </c>
       <c r="C171" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="D171" t="s">
         <v>14</v>
       </c>
       <c r="E171" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F171" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B172" t="s">
-        <v>75</v>
+        <v>102</v>
       </c>
       <c r="C172" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D172" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E172" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F172" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B173" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="C173" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="D173" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="E173" t="s">
         <v>10</v>
       </c>
       <c r="F173" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B174" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="C174" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="D174" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="E174" t="s">
         <v>12</v>
       </c>
       <c r="F174" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B175" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="C175" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="D175" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="E175" t="s">
         <v>13</v>
       </c>
       <c r="F175" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B176" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="C176" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="D176" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="E176" t="s">
         <v>10</v>
       </c>
       <c r="F176" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B177" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="C177" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="D177" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="E177" t="s">
         <v>12</v>
       </c>
       <c r="F177" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B178" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="C178" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="D178" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="E178" t="s">
         <v>13</v>
       </c>
       <c r="F178" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B179" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="C179" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="D179" t="s">
         <v>9</v>
@@ -4372,18 +4486,18 @@
         <v>10</v>
       </c>
       <c r="F179" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B180" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="C180" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="D180" t="s">
         <v>9</v>
@@ -4392,18 +4506,18 @@
         <v>12</v>
       </c>
       <c r="F180" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B181" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="C181" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="D181" t="s">
         <v>9</v>
@@ -4412,18 +4526,18 @@
         <v>13</v>
       </c>
       <c r="F181" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B182" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="C182" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="D182" t="s">
         <v>14</v>
@@ -4432,18 +4546,18 @@
         <v>10</v>
       </c>
       <c r="F182" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B183" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="C183" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="D183" t="s">
         <v>14</v>
@@ -4452,18 +4566,18 @@
         <v>12</v>
       </c>
       <c r="F183" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B184" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="C184" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="D184" t="s">
         <v>14</v>
@@ -4472,318 +4586,318 @@
         <v>13</v>
       </c>
       <c r="F184" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B185" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="C185" t="s">
         <v>20</v>
       </c>
       <c r="D185" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E185" t="s">
         <v>10</v>
       </c>
       <c r="F185" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B186" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="C186" t="s">
         <v>20</v>
       </c>
       <c r="D186" t="s">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="E186" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F186" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B187" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="C187" t="s">
         <v>20</v>
       </c>
       <c r="D187" t="s">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="E187" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F187" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B188" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="C188" t="s">
         <v>20</v>
       </c>
       <c r="D188" t="s">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="E188" t="s">
         <v>10</v>
       </c>
       <c r="F188" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B189" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="C189" t="s">
         <v>20</v>
       </c>
       <c r="D189" t="s">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="E189" t="s">
         <v>12</v>
       </c>
       <c r="F189" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B190" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="C190" t="s">
         <v>20</v>
       </c>
       <c r="D190" t="s">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="E190" t="s">
         <v>13</v>
       </c>
       <c r="F190" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B191" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="C191" t="s">
         <v>20</v>
       </c>
       <c r="D191" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E191" t="s">
         <v>10</v>
       </c>
       <c r="F191" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B192" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="C192" t="s">
         <v>20</v>
       </c>
       <c r="D192" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E192" t="s">
         <v>12</v>
       </c>
       <c r="F192" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B193" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="C193" t="s">
         <v>20</v>
       </c>
       <c r="D193" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E193" t="s">
         <v>13</v>
       </c>
       <c r="F193" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B194" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="C194" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D194" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E194" t="s">
         <v>10</v>
       </c>
       <c r="F194" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B195" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="C195" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D195" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E195" t="s">
         <v>12</v>
       </c>
       <c r="F195" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B196" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="C196" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D196" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E196" t="s">
         <v>13</v>
       </c>
       <c r="F196" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B197" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="C197" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="D197" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E197" t="s">
         <v>10</v>
       </c>
       <c r="F197" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B198" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="C198" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="D198" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E198" t="s">
         <v>12</v>
       </c>
       <c r="F198" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B199" t="s">
-        <v>90</v>
+        <v>112</v>
       </c>
       <c r="C199" t="s">
-        <v>17</v>
+        <v>113</v>
       </c>
       <c r="D199" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E199" t="s">
         <v>13</v>
       </c>
       <c r="F199" t="s">
-        <v>92</v>
+        <v>114</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B200" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C200" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="D200" t="s">
         <v>9</v>
@@ -4792,18 +4906,18 @@
         <v>10</v>
       </c>
       <c r="F200" t="s">
-        <v>94</v>
+        <v>117</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B201" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C201" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="D201" t="s">
         <v>9</v>
@@ -4812,18 +4926,18 @@
         <v>12</v>
       </c>
       <c r="F201" t="s">
-        <v>94</v>
+        <v>117</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B202" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C202" t="s">
-        <v>93</v>
+        <v>116</v>
       </c>
       <c r="D202" t="s">
         <v>9</v>
@@ -4832,198 +4946,198 @@
         <v>13</v>
       </c>
       <c r="F202" t="s">
-        <v>94</v>
+        <v>117</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B203" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C203" t="s">
-        <v>93</v>
+        <v>47</v>
       </c>
       <c r="D203" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E203" t="s">
         <v>10</v>
       </c>
       <c r="F203" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B204" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C204" t="s">
-        <v>93</v>
+        <v>47</v>
       </c>
       <c r="D204" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E204" t="s">
         <v>12</v>
       </c>
       <c r="F204" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B205" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C205" t="s">
-        <v>93</v>
+        <v>47</v>
       </c>
       <c r="D205" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E205" t="s">
         <v>13</v>
       </c>
       <c r="F205" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B206" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C206" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="D206" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E206" t="s">
         <v>10</v>
       </c>
       <c r="F206" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B207" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C207" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="D207" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E207" t="s">
         <v>12</v>
       </c>
       <c r="F207" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B208" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C208" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="D208" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E208" t="s">
         <v>13</v>
       </c>
       <c r="F208" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B209" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C209" t="s">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="D209" t="s">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="E209" t="s">
         <v>10</v>
       </c>
       <c r="F209" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B210" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C210" t="s">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="D210" t="s">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="E210" t="s">
         <v>12</v>
       </c>
       <c r="F210" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B211" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C211" t="s">
-        <v>96</v>
+        <v>20</v>
       </c>
       <c r="D211" t="s">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="E211" t="s">
         <v>13</v>
       </c>
       <c r="F211" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B212" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C212" t="s">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="D212" t="s">
         <v>9</v>
@@ -5032,18 +5146,18 @@
         <v>10</v>
       </c>
       <c r="F212" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B213" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C213" t="s">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="D213" t="s">
         <v>9</v>
@@ -5052,18 +5166,18 @@
         <v>12</v>
       </c>
       <c r="F213" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B214" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C214" t="s">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="D214" t="s">
         <v>9</v>
@@ -5072,18 +5186,18 @@
         <v>13</v>
       </c>
       <c r="F214" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B215" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C215" t="s">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="D215" t="s">
         <v>14</v>
@@ -5092,18 +5206,18 @@
         <v>10</v>
       </c>
       <c r="F215" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B216" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C216" t="s">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="D216" t="s">
         <v>14</v>
@@ -5112,18 +5226,18 @@
         <v>12</v>
       </c>
       <c r="F216" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B217" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C217" t="s">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="D217" t="s">
         <v>14</v>
@@ -5132,618 +5246,618 @@
         <v>13</v>
       </c>
       <c r="F217" t="s">
-        <v>98</v>
+        <v>119</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B218" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C218" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D218" t="s">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="E218" t="s">
         <v>10</v>
       </c>
       <c r="F218" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B219" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C219" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D219" t="s">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="E219" t="s">
         <v>12</v>
       </c>
       <c r="F219" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B220" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C220" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D220" t="s">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="E220" t="s">
         <v>13</v>
       </c>
       <c r="F220" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B221" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C221" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D221" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E221" t="s">
         <v>10</v>
       </c>
       <c r="F221" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B222" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C222" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D222" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E222" t="s">
         <v>12</v>
       </c>
       <c r="F222" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B223" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C223" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D223" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E223" t="s">
         <v>13</v>
       </c>
       <c r="F223" t="s">
-        <v>99</v>
+        <v>120</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B224" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C224" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="D224" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E224" t="s">
         <v>10</v>
       </c>
       <c r="F224" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B225" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C225" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="D225" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E225" t="s">
         <v>12</v>
       </c>
       <c r="F225" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B226" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C226" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="D226" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E226" t="s">
         <v>13</v>
       </c>
       <c r="F226" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B227" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C227" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="D227" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E227" t="s">
         <v>10</v>
       </c>
       <c r="F227" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B228" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C228" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="D228" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E228" t="s">
         <v>12</v>
       </c>
       <c r="F228" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B229" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C229" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="D229" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E229" t="s">
         <v>13</v>
       </c>
       <c r="F229" t="s">
-        <v>100</v>
+        <v>121</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B230" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C230" t="s">
-        <v>17</v>
+        <v>122</v>
       </c>
       <c r="D230" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E230" t="s">
         <v>10</v>
       </c>
       <c r="F230" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B231" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C231" t="s">
-        <v>17</v>
+        <v>122</v>
       </c>
       <c r="D231" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E231" t="s">
         <v>12</v>
       </c>
       <c r="F231" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B232" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C232" t="s">
-        <v>17</v>
+        <v>122</v>
       </c>
       <c r="D232" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E232" t="s">
         <v>13</v>
       </c>
       <c r="F232" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B233" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C233" t="s">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="D233" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E233" t="s">
         <v>10</v>
       </c>
       <c r="F233" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B234" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C234" t="s">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="D234" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E234" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F234" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B235" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C235" t="s">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="D235" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E235" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F235" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B236" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C236" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="D236" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="E236" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F236" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B237" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C237" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="D237" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="E237" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F237" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B238" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C238" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="D238" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="E238" t="s">
         <v>13</v>
       </c>
       <c r="F238" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B239" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C239" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="D239" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="E239" t="s">
         <v>10</v>
       </c>
       <c r="F239" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B240" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C240" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="D240" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="E240" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F240" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B241" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C241" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="D241" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="E241" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F241" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B242" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C242" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="D242" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E242" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F242" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B243" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C243" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="D243" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E243" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F243" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B244" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C244" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="D244" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E244" t="s">
         <v>13</v>
       </c>
       <c r="F244" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B245" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C245" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="D245" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E245" t="s">
         <v>10</v>
       </c>
       <c r="F245" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B246" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C246" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="D246" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E246" t="s">
         <v>12</v>
       </c>
       <c r="F246" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B247" t="s">
-        <v>90</v>
+        <v>115</v>
       </c>
       <c r="C247" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="D247" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E247" t="s">
         <v>13</v>
       </c>
       <c r="F247" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B248" t="s">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="C248" t="s">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="D248" t="s">
         <v>9</v>
@@ -5752,67 +5866,67 @@
         <v>10</v>
       </c>
       <c r="F248" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B249" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="C249" t="s">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="D249" t="s">
         <v>9</v>
       </c>
       <c r="E249" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F249" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B250" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="C250" t="s">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="D250" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E250" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F250" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="B251" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="C251" t="s">
-        <v>109</v>
+        <v>52</v>
       </c>
       <c r="D251" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E251" t="s">
         <v>10</v>
       </c>
       <c r="F251" t="s">
-        <v>110</v>
+        <v>126</v>
       </c>
     </row>
     <row r="252">
@@ -5820,19 +5934,19 @@
         <v>111</v>
       </c>
       <c r="B252" t="s">
-        <v>42</v>
+        <v>125</v>
       </c>
       <c r="C252" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="D252" t="s">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="E252" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F252" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
     </row>
     <row r="253">
@@ -5840,19 +5954,19 @@
         <v>111</v>
       </c>
       <c r="B253" t="s">
-        <v>42</v>
+        <v>125</v>
       </c>
       <c r="C253" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="D253" t="s">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="E253" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F253" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
     </row>
     <row r="254">
@@ -5860,19 +5974,19 @@
         <v>111</v>
       </c>
       <c r="B254" t="s">
-        <v>42</v>
+        <v>125</v>
       </c>
       <c r="C254" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="D254" t="s">
-        <v>67</v>
+        <v>9</v>
       </c>
       <c r="E254" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F254" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
     </row>
     <row r="255">
@@ -5880,19 +5994,19 @@
         <v>111</v>
       </c>
       <c r="B255" t="s">
-        <v>42</v>
+        <v>125</v>
       </c>
       <c r="C255" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="D255" t="s">
         <v>9</v>
       </c>
       <c r="E255" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F255" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
     </row>
     <row r="256">
@@ -5900,19 +6014,19 @@
         <v>111</v>
       </c>
       <c r="B256" t="s">
-        <v>42</v>
+        <v>125</v>
       </c>
       <c r="C256" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="D256" t="s">
         <v>9</v>
       </c>
       <c r="E256" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F256" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
     </row>
     <row r="257">
@@ -5920,19 +6034,19 @@
         <v>111</v>
       </c>
       <c r="B257" t="s">
-        <v>42</v>
+        <v>125</v>
       </c>
       <c r="C257" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="D257" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E257" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F257" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
     </row>
     <row r="258">
@@ -5940,19 +6054,19 @@
         <v>111</v>
       </c>
       <c r="B258" t="s">
-        <v>42</v>
+        <v>125</v>
       </c>
       <c r="C258" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="D258" t="s">
         <v>14</v>
       </c>
       <c r="E258" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F258" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
     </row>
     <row r="259">
@@ -5960,19 +6074,19 @@
         <v>111</v>
       </c>
       <c r="B259" t="s">
-        <v>42</v>
+        <v>125</v>
       </c>
       <c r="C259" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="D259" t="s">
         <v>14</v>
       </c>
       <c r="E259" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F259" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
     </row>
     <row r="260">
@@ -5980,19 +6094,19 @@
         <v>111</v>
       </c>
       <c r="B260" t="s">
-        <v>42</v>
+        <v>128</v>
       </c>
       <c r="C260" t="s">
         <v>20</v>
       </c>
       <c r="D260" t="s">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="E260" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F260" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
     </row>
     <row r="261">
@@ -6000,19 +6114,19 @@
         <v>111</v>
       </c>
       <c r="B261" t="s">
-        <v>42</v>
+        <v>128</v>
       </c>
       <c r="C261" t="s">
-        <v>113</v>
+        <v>20</v>
       </c>
       <c r="D261" t="s">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="E261" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F261" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
     </row>
     <row r="262">
@@ -6020,19 +6134,19 @@
         <v>111</v>
       </c>
       <c r="B262" t="s">
-        <v>42</v>
+        <v>128</v>
       </c>
       <c r="C262" t="s">
-        <v>113</v>
+        <v>20</v>
       </c>
       <c r="D262" t="s">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="E262" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F262" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
     </row>
     <row r="263">
@@ -6040,19 +6154,19 @@
         <v>111</v>
       </c>
       <c r="B263" t="s">
-        <v>42</v>
+        <v>128</v>
       </c>
       <c r="C263" t="s">
-        <v>113</v>
+        <v>20</v>
       </c>
       <c r="D263" t="s">
         <v>9</v>
       </c>
       <c r="E263" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F263" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
     </row>
     <row r="264">
@@ -6060,19 +6174,19 @@
         <v>111</v>
       </c>
       <c r="B264" t="s">
-        <v>42</v>
+        <v>128</v>
       </c>
       <c r="C264" t="s">
-        <v>113</v>
+        <v>20</v>
       </c>
       <c r="D264" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E264" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F264" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
     </row>
     <row r="265">
@@ -6080,19 +6194,19 @@
         <v>111</v>
       </c>
       <c r="B265" t="s">
-        <v>42</v>
+        <v>128</v>
       </c>
       <c r="C265" t="s">
-        <v>113</v>
+        <v>20</v>
       </c>
       <c r="D265" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E265" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F265" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
     </row>
     <row r="266">
@@ -6100,19 +6214,19 @@
         <v>111</v>
       </c>
       <c r="B266" t="s">
-        <v>42</v>
+        <v>128</v>
       </c>
       <c r="C266" t="s">
-        <v>113</v>
+        <v>20</v>
       </c>
       <c r="D266" t="s">
         <v>14</v>
       </c>
       <c r="E266" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F266" t="s">
-        <v>114</v>
+        <v>129</v>
       </c>
     </row>
     <row r="267">
@@ -6120,19 +6234,19 @@
         <v>111</v>
       </c>
       <c r="B267" t="s">
-        <v>42</v>
+        <v>128</v>
       </c>
       <c r="C267" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D267" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E267" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F267" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
     </row>
     <row r="268">
@@ -6140,19 +6254,19 @@
         <v>111</v>
       </c>
       <c r="B268" t="s">
-        <v>42</v>
+        <v>128</v>
       </c>
       <c r="C268" t="s">
-        <v>113</v>
+        <v>20</v>
       </c>
       <c r="D268" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E268" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F268" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
     </row>
     <row r="269">
@@ -6160,19 +6274,19 @@
         <v>111</v>
       </c>
       <c r="B269" t="s">
-        <v>42</v>
+        <v>128</v>
       </c>
       <c r="C269" t="s">
-        <v>113</v>
+        <v>17</v>
       </c>
       <c r="D269" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E269" t="s">
         <v>10</v>
       </c>
       <c r="F269" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
     </row>
     <row r="270">
@@ -6180,19 +6294,19 @@
         <v>111</v>
       </c>
       <c r="B270" t="s">
-        <v>42</v>
+        <v>128</v>
       </c>
       <c r="C270" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D270" t="s">
         <v>9</v>
       </c>
       <c r="E270" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F270" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
     </row>
     <row r="271">
@@ -6200,19 +6314,19 @@
         <v>111</v>
       </c>
       <c r="B271" t="s">
-        <v>42</v>
+        <v>128</v>
       </c>
       <c r="C271" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D271" t="s">
         <v>9</v>
       </c>
       <c r="E271" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F271" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
     </row>
     <row r="272">
@@ -6220,19 +6334,19 @@
         <v>111</v>
       </c>
       <c r="B272" t="s">
-        <v>42</v>
+        <v>128</v>
       </c>
       <c r="C272" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D272" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E272" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F272" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
     </row>
     <row r="273">
@@ -6240,19 +6354,19 @@
         <v>111</v>
       </c>
       <c r="B273" t="s">
-        <v>42</v>
+        <v>128</v>
       </c>
       <c r="C273" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D273" t="s">
         <v>14</v>
       </c>
       <c r="E273" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F273" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
     </row>
     <row r="274">
@@ -6260,19 +6374,19 @@
         <v>111</v>
       </c>
       <c r="B274" t="s">
-        <v>42</v>
+        <v>128</v>
       </c>
       <c r="C274" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D274" t="s">
         <v>14</v>
       </c>
       <c r="E274" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F274" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
     </row>
     <row r="275">
@@ -6280,19 +6394,19 @@
         <v>111</v>
       </c>
       <c r="B275" t="s">
-        <v>42</v>
+        <v>128</v>
       </c>
       <c r="C275" t="s">
-        <v>23</v>
+        <v>131</v>
       </c>
       <c r="D275" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E275" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F275" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
     </row>
     <row r="276">
@@ -6300,19 +6414,19 @@
         <v>111</v>
       </c>
       <c r="B276" t="s">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="C276" t="s">
-        <v>23</v>
+        <v>131</v>
       </c>
       <c r="D276" t="s">
         <v>9</v>
       </c>
       <c r="E276" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F276" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
     </row>
     <row r="277">
@@ -6320,19 +6434,19 @@
         <v>111</v>
       </c>
       <c r="B277" t="s">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="C277" t="s">
-        <v>23</v>
+        <v>131</v>
       </c>
       <c r="D277" t="s">
         <v>9</v>
       </c>
       <c r="E277" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F277" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
     </row>
     <row r="278">
@@ -6340,19 +6454,19 @@
         <v>111</v>
       </c>
       <c r="B278" t="s">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="C278" t="s">
-        <v>23</v>
+        <v>131</v>
       </c>
       <c r="D278" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E278" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F278" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
     </row>
     <row r="279">
@@ -6360,19 +6474,19 @@
         <v>111</v>
       </c>
       <c r="B279" t="s">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="C279" t="s">
-        <v>17</v>
+        <v>131</v>
       </c>
       <c r="D279" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E279" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F279" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
     </row>
     <row r="280">
@@ -6380,19 +6494,19 @@
         <v>111</v>
       </c>
       <c r="B280" t="s">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="C280" t="s">
-        <v>17</v>
+        <v>131</v>
       </c>
       <c r="D280" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E280" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F280" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
     </row>
     <row r="281">
@@ -6400,19 +6514,19 @@
         <v>111</v>
       </c>
       <c r="B281" t="s">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="C281" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D281" t="s">
         <v>9</v>
       </c>
       <c r="E281" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F281" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
     </row>
     <row r="282">
@@ -6420,19 +6534,19 @@
         <v>111</v>
       </c>
       <c r="B282" t="s">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="C282" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D282" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E282" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F282" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
     </row>
     <row r="283">
@@ -6440,19 +6554,19 @@
         <v>111</v>
       </c>
       <c r="B283" t="s">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="C283" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D283" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E283" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F283" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
     </row>
     <row r="284">
@@ -6460,19 +6574,19 @@
         <v>111</v>
       </c>
       <c r="B284" t="s">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="C284" t="s">
-        <v>17</v>
+        <v>134</v>
       </c>
       <c r="D284" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E284" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F284" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
     </row>
     <row r="285">
@@ -6480,19 +6594,19 @@
         <v>111</v>
       </c>
       <c r="B285" t="s">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="C285" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="D285" t="s">
         <v>9</v>
       </c>
       <c r="E285" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F285" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
     </row>
     <row r="286">
@@ -6500,19 +6614,19 @@
         <v>111</v>
       </c>
       <c r="B286" t="s">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="C286" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="D286" t="s">
         <v>9</v>
       </c>
       <c r="E286" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F286" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
     </row>
     <row r="287">
@@ -6520,19 +6634,19 @@
         <v>111</v>
       </c>
       <c r="B287" t="s">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="C287" t="s">
-        <v>113</v>
+        <v>47</v>
       </c>
       <c r="D287" t="s">
         <v>9</v>
       </c>
       <c r="E287" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F287" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
     </row>
     <row r="288">
@@ -6540,19 +6654,19 @@
         <v>111</v>
       </c>
       <c r="B288" t="s">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="C288" t="s">
-        <v>113</v>
+        <v>47</v>
       </c>
       <c r="D288" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E288" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F288" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
     </row>
     <row r="289">
@@ -6560,19 +6674,19 @@
         <v>111</v>
       </c>
       <c r="B289" t="s">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="C289" t="s">
-        <v>113</v>
+        <v>47</v>
       </c>
       <c r="D289" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E289" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F289" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
     </row>
     <row r="290">
@@ -6580,19 +6694,19 @@
         <v>111</v>
       </c>
       <c r="B290" t="s">
-        <v>44</v>
+        <v>128</v>
       </c>
       <c r="C290" t="s">
-        <v>113</v>
+        <v>47</v>
       </c>
       <c r="D290" t="s">
         <v>14</v>
       </c>
       <c r="E290" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F290" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
     </row>
     <row r="291">
@@ -6600,19 +6714,19 @@
         <v>111</v>
       </c>
       <c r="B291" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C291" t="s">
-        <v>122</v>
+        <v>47</v>
       </c>
       <c r="D291" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E291" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F291" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
     </row>
     <row r="292">
@@ -6620,19 +6734,19 @@
         <v>111</v>
       </c>
       <c r="B292" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C292" t="s">
-        <v>122</v>
+        <v>47</v>
       </c>
       <c r="D292" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E292" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F292" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
     </row>
     <row r="293">
@@ -6640,19 +6754,19 @@
         <v>111</v>
       </c>
       <c r="B293" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C293" t="s">
-        <v>122</v>
+        <v>20</v>
       </c>
       <c r="D293" t="s">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="E293" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F293" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
     </row>
     <row r="294">
@@ -6660,19 +6774,19 @@
         <v>111</v>
       </c>
       <c r="B294" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C294" t="s">
-        <v>122</v>
+        <v>20</v>
       </c>
       <c r="D294" t="s">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="E294" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F294" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
     </row>
     <row r="295">
@@ -6680,19 +6794,19 @@
         <v>111</v>
       </c>
       <c r="B295" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C295" t="s">
-        <v>122</v>
+        <v>20</v>
       </c>
       <c r="D295" t="s">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="E295" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F295" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
     </row>
     <row r="296">
@@ -6700,19 +6814,19 @@
         <v>111</v>
       </c>
       <c r="B296" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C296" t="s">
-        <v>122</v>
+        <v>20</v>
       </c>
       <c r="D296" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E296" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F296" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
     </row>
     <row r="297">
@@ -6720,19 +6834,19 @@
         <v>111</v>
       </c>
       <c r="B297" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C297" t="s">
-        <v>124</v>
+        <v>20</v>
       </c>
       <c r="D297" t="s">
         <v>9</v>
       </c>
       <c r="E297" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F297" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
     </row>
     <row r="298">
@@ -6740,19 +6854,19 @@
         <v>111</v>
       </c>
       <c r="B298" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C298" t="s">
-        <v>124</v>
+        <v>20</v>
       </c>
       <c r="D298" t="s">
         <v>9</v>
       </c>
       <c r="E298" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F298" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
     </row>
     <row r="299">
@@ -6760,19 +6874,19 @@
         <v>111</v>
       </c>
       <c r="B299" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C299" t="s">
-        <v>124</v>
+        <v>20</v>
       </c>
       <c r="D299" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E299" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F299" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
     </row>
     <row r="300">
@@ -6780,19 +6894,19 @@
         <v>111</v>
       </c>
       <c r="B300" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C300" t="s">
-        <v>124</v>
+        <v>20</v>
       </c>
       <c r="D300" t="s">
         <v>14</v>
       </c>
       <c r="E300" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F300" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
     </row>
     <row r="301">
@@ -6800,19 +6914,19 @@
         <v>111</v>
       </c>
       <c r="B301" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C301" t="s">
-        <v>124</v>
+        <v>20</v>
       </c>
       <c r="D301" t="s">
         <v>14</v>
       </c>
       <c r="E301" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F301" t="s">
-        <v>125</v>
+        <v>137</v>
       </c>
     </row>
     <row r="302">
@@ -6820,19 +6934,19 @@
         <v>111</v>
       </c>
       <c r="B302" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C302" t="s">
-        <v>124</v>
+        <v>17</v>
       </c>
       <c r="D302" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E302" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F302" t="s">
-        <v>125</v>
+        <v>138</v>
       </c>
     </row>
     <row r="303">
@@ -6840,19 +6954,19 @@
         <v>111</v>
       </c>
       <c r="B303" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C303" t="s">
-        <v>126</v>
+        <v>17</v>
       </c>
       <c r="D303" t="s">
         <v>9</v>
       </c>
       <c r="E303" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F303" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
     </row>
     <row r="304">
@@ -6860,19 +6974,19 @@
         <v>111</v>
       </c>
       <c r="B304" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C304" t="s">
-        <v>126</v>
+        <v>17</v>
       </c>
       <c r="D304" t="s">
         <v>9</v>
       </c>
       <c r="E304" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F304" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
     </row>
     <row r="305">
@@ -6880,19 +6994,19 @@
         <v>111</v>
       </c>
       <c r="B305" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C305" t="s">
-        <v>126</v>
+        <v>17</v>
       </c>
       <c r="D305" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E305" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F305" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
     </row>
     <row r="306">
@@ -6900,19 +7014,19 @@
         <v>111</v>
       </c>
       <c r="B306" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C306" t="s">
-        <v>126</v>
+        <v>17</v>
       </c>
       <c r="D306" t="s">
         <v>14</v>
       </c>
       <c r="E306" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F306" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
     </row>
     <row r="307">
@@ -6920,19 +7034,19 @@
         <v>111</v>
       </c>
       <c r="B307" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C307" t="s">
-        <v>126</v>
+        <v>17</v>
       </c>
       <c r="D307" t="s">
         <v>14</v>
       </c>
       <c r="E307" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F307" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
     </row>
     <row r="308">
@@ -6940,30 +7054,30 @@
         <v>111</v>
       </c>
       <c r="B308" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C308" t="s">
-        <v>126</v>
+        <v>52</v>
       </c>
       <c r="D308" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E308" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F308" t="s">
-        <v>127</v>
+        <v>139</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="s">
+        <v>111</v>
+      </c>
+      <c r="B309" t="s">
         <v>128</v>
       </c>
-      <c r="B309" t="s">
-        <v>42</v>
-      </c>
       <c r="C309" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D309" t="s">
         <v>9</v>
@@ -6972,418 +7086,418 @@
         <v>10</v>
       </c>
       <c r="F309" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="s">
+        <v>111</v>
+      </c>
+      <c r="B310" t="s">
         <v>128</v>
       </c>
-      <c r="B310" t="s">
-        <v>42</v>
-      </c>
       <c r="C310" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D310" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E310" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F310" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="s">
+        <v>111</v>
+      </c>
+      <c r="B311" t="s">
         <v>128</v>
       </c>
-      <c r="B311" t="s">
-        <v>42</v>
-      </c>
       <c r="C311" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="D311" t="s">
         <v>9</v>
       </c>
       <c r="E311" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F311" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="s">
+        <v>111</v>
+      </c>
+      <c r="B312" t="s">
         <v>128</v>
       </c>
-      <c r="B312" t="s">
-        <v>44</v>
-      </c>
       <c r="C312" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D312" t="s">
         <v>9</v>
       </c>
       <c r="E312" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F312" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="s">
+        <v>111</v>
+      </c>
+      <c r="B313" t="s">
         <v>128</v>
       </c>
-      <c r="B313" t="s">
-        <v>44</v>
-      </c>
       <c r="C313" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D313" t="s">
         <v>9</v>
       </c>
       <c r="E313" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F313" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="s">
+        <v>111</v>
+      </c>
+      <c r="B314" t="s">
         <v>128</v>
       </c>
-      <c r="B314" t="s">
-        <v>44</v>
-      </c>
       <c r="C314" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D314" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E314" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F314" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="s">
+        <v>111</v>
+      </c>
+      <c r="B315" t="s">
         <v>128</v>
       </c>
-      <c r="B315" t="s">
-        <v>44</v>
-      </c>
       <c r="C315" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D315" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E315" t="s">
         <v>10</v>
       </c>
       <c r="F315" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="s">
+        <v>111</v>
+      </c>
+      <c r="B316" t="s">
         <v>128</v>
       </c>
-      <c r="B316" t="s">
-        <v>44</v>
-      </c>
       <c r="C316" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D316" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E316" t="s">
         <v>12</v>
       </c>
       <c r="F316" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="s">
+        <v>111</v>
+      </c>
+      <c r="B317" t="s">
         <v>128</v>
       </c>
-      <c r="B317" t="s">
-        <v>44</v>
-      </c>
       <c r="C317" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D317" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E317" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F317" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="s">
+        <v>111</v>
+      </c>
+      <c r="B318" t="s">
         <v>128</v>
       </c>
-      <c r="B318" t="s">
-        <v>44</v>
-      </c>
       <c r="C318" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D318" t="s">
         <v>14</v>
       </c>
       <c r="E318" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F318" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="s">
+        <v>111</v>
+      </c>
+      <c r="B319" t="s">
         <v>128</v>
       </c>
-      <c r="B319" t="s">
-        <v>44</v>
-      </c>
       <c r="C319" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D319" t="s">
         <v>14</v>
       </c>
       <c r="E319" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F319" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="s">
+        <v>111</v>
+      </c>
+      <c r="B320" t="s">
         <v>128</v>
       </c>
-      <c r="B320" t="s">
-        <v>44</v>
-      </c>
       <c r="C320" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="D320" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E320" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F320" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="s">
+        <v>111</v>
+      </c>
+      <c r="B321" t="s">
         <v>128</v>
       </c>
-      <c r="B321" t="s">
-        <v>44</v>
-      </c>
       <c r="C321" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D321" t="s">
         <v>9</v>
       </c>
       <c r="E321" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F321" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="s">
+        <v>111</v>
+      </c>
+      <c r="B322" t="s">
         <v>128</v>
       </c>
-      <c r="B322" t="s">
-        <v>44</v>
-      </c>
       <c r="C322" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D322" t="s">
         <v>9</v>
       </c>
       <c r="E322" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F322" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="B323" t="s">
-        <v>44</v>
+        <v>142</v>
       </c>
       <c r="C323" t="s">
-        <v>49</v>
+        <v>142</v>
       </c>
       <c r="D323" t="s">
         <v>9</v>
       </c>
       <c r="E323" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F323" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="B324" t="s">
-        <v>44</v>
+        <v>144</v>
       </c>
       <c r="C324" t="s">
-        <v>49</v>
+        <v>142</v>
       </c>
       <c r="D324" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E324" t="s">
         <v>10</v>
       </c>
       <c r="F324" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="B325" t="s">
-        <v>44</v>
+        <v>144</v>
       </c>
       <c r="C325" t="s">
-        <v>49</v>
+        <v>142</v>
       </c>
       <c r="D325" t="s">
         <v>14</v>
       </c>
       <c r="E325" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F325" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="B326" t="s">
-        <v>44</v>
+        <v>146</v>
       </c>
       <c r="C326" t="s">
-        <v>49</v>
+        <v>147</v>
       </c>
       <c r="D326" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E326" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F326" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="B327" t="s">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="C327" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D327" t="s">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="E327" t="s">
         <v>10</v>
       </c>
       <c r="F327" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="B328" t="s">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="C328" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D328" t="s">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="E328" t="s">
         <v>12</v>
       </c>
       <c r="F328" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="B329" t="s">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="C329" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D329" t="s">
-        <v>9</v>
+        <v>61</v>
       </c>
       <c r="E329" t="s">
         <v>13</v>
       </c>
       <c r="F329" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B330" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="C330" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="D330" t="s">
         <v>9</v>
@@ -7392,18 +7506,18 @@
         <v>10</v>
       </c>
       <c r="F330" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B331" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="C331" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="D331" t="s">
         <v>9</v>
@@ -7412,18 +7526,18 @@
         <v>12</v>
       </c>
       <c r="F331" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B332" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="C332" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="D332" t="s">
         <v>9</v>
@@ -7432,18 +7546,18 @@
         <v>13</v>
       </c>
       <c r="F332" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B333" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="C333" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="D333" t="s">
         <v>14</v>
@@ -7452,18 +7566,18 @@
         <v>10</v>
       </c>
       <c r="F333" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B334" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="C334" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="D334" t="s">
         <v>14</v>
@@ -7472,18 +7586,18 @@
         <v>12</v>
       </c>
       <c r="F334" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B335" t="s">
-        <v>136</v>
+        <v>85</v>
       </c>
       <c r="C335" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="D335" t="s">
         <v>14</v>
@@ -7492,18 +7606,18 @@
         <v>13</v>
       </c>
       <c r="F335" t="s">
-        <v>137</v>
+        <v>150</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B336" t="s">
-        <v>138</v>
+        <v>85</v>
       </c>
       <c r="C336" t="s">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="D336" t="s">
         <v>9</v>
@@ -7512,18 +7626,18 @@
         <v>10</v>
       </c>
       <c r="F336" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B337" t="s">
-        <v>138</v>
+        <v>85</v>
       </c>
       <c r="C337" t="s">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="D337" t="s">
         <v>9</v>
@@ -7532,18 +7646,18 @@
         <v>12</v>
       </c>
       <c r="F337" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B338" t="s">
-        <v>138</v>
+        <v>85</v>
       </c>
       <c r="C338" t="s">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="D338" t="s">
         <v>9</v>
@@ -7552,18 +7666,18 @@
         <v>13</v>
       </c>
       <c r="F338" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B339" t="s">
-        <v>138</v>
+        <v>85</v>
       </c>
       <c r="C339" t="s">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="D339" t="s">
         <v>14</v>
@@ -7572,18 +7686,18 @@
         <v>10</v>
       </c>
       <c r="F339" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B340" t="s">
-        <v>138</v>
+        <v>85</v>
       </c>
       <c r="C340" t="s">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="D340" t="s">
         <v>14</v>
@@ -7592,18 +7706,18 @@
         <v>12</v>
       </c>
       <c r="F340" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B341" t="s">
-        <v>138</v>
+        <v>85</v>
       </c>
       <c r="C341" t="s">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="D341" t="s">
         <v>14</v>
@@ -7612,18 +7726,18 @@
         <v>13</v>
       </c>
       <c r="F341" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B342" t="s">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="C342" t="s">
-        <v>82</v>
+        <v>23</v>
       </c>
       <c r="D342" t="s">
         <v>9</v>
@@ -7632,227 +7746,1727 @@
         <v>10</v>
       </c>
       <c r="F342" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B343" t="s">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="C343" t="s">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="D343" t="s">
         <v>9</v>
       </c>
       <c r="E343" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F343" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B344" t="s">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="C344" t="s">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="D344" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E344" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F344" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B345" t="s">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="C345" t="s">
-        <v>82</v>
+        <v>23</v>
       </c>
       <c r="D345" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E345" t="s">
         <v>10</v>
       </c>
       <c r="F345" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B346" t="s">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="C346" t="s">
-        <v>82</v>
+        <v>23</v>
       </c>
       <c r="D346" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E346" t="s">
         <v>12</v>
       </c>
       <c r="F346" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B347" t="s">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="C347" t="s">
-        <v>82</v>
+        <v>23</v>
       </c>
       <c r="D347" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E347" t="s">
         <v>13</v>
       </c>
       <c r="F347" t="s">
-        <v>141</v>
+        <v>155</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B348" t="s">
-        <v>142</v>
+        <v>85</v>
       </c>
       <c r="C348" t="s">
-        <v>82</v>
+        <v>23</v>
       </c>
       <c r="D348" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E348" t="s">
         <v>10</v>
       </c>
       <c r="F348" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B349" t="s">
-        <v>142</v>
+        <v>85</v>
       </c>
       <c r="C349" t="s">
-        <v>82</v>
+        <v>23</v>
       </c>
       <c r="D349" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E349" t="s">
         <v>12</v>
       </c>
       <c r="F349" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B350" t="s">
-        <v>142</v>
+        <v>85</v>
       </c>
       <c r="C350" t="s">
-        <v>82</v>
+        <v>23</v>
       </c>
       <c r="D350" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E350" t="s">
         <v>13</v>
       </c>
       <c r="F350" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B351" t="s">
-        <v>142</v>
+        <v>87</v>
       </c>
       <c r="C351" t="s">
-        <v>82</v>
+        <v>23</v>
       </c>
       <c r="D351" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E351" t="s">
         <v>10</v>
       </c>
       <c r="F351" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B352" t="s">
-        <v>142</v>
+        <v>87</v>
       </c>
       <c r="C352" t="s">
-        <v>82</v>
+        <v>23</v>
       </c>
       <c r="D352" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E352" t="s">
         <v>12</v>
       </c>
       <c r="F352" t="s">
-        <v>143</v>
+        <v>156</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B353" t="s">
-        <v>142</v>
+        <v>87</v>
       </c>
       <c r="C353" t="s">
-        <v>82</v>
+        <v>23</v>
       </c>
       <c r="D353" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E353" t="s">
         <v>13</v>
       </c>
       <c r="F353" t="s">
-        <v>143</v>
+        <v>156</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="s">
+        <v>149</v>
+      </c>
+      <c r="B354" t="s">
+        <v>87</v>
+      </c>
+      <c r="C354" t="s">
+        <v>17</v>
+      </c>
+      <c r="D354" t="s">
+        <v>9</v>
+      </c>
+      <c r="E354" t="s">
+        <v>10</v>
+      </c>
+      <c r="F354" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="s">
+        <v>149</v>
+      </c>
+      <c r="B355" t="s">
+        <v>87</v>
+      </c>
+      <c r="C355" t="s">
+        <v>17</v>
+      </c>
+      <c r="D355" t="s">
+        <v>9</v>
+      </c>
+      <c r="E355" t="s">
+        <v>12</v>
+      </c>
+      <c r="F355" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="s">
+        <v>149</v>
+      </c>
+      <c r="B356" t="s">
+        <v>87</v>
+      </c>
+      <c r="C356" t="s">
+        <v>17</v>
+      </c>
+      <c r="D356" t="s">
+        <v>9</v>
+      </c>
+      <c r="E356" t="s">
+        <v>13</v>
+      </c>
+      <c r="F356" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="s">
+        <v>149</v>
+      </c>
+      <c r="B357" t="s">
+        <v>87</v>
+      </c>
+      <c r="C357" t="s">
+        <v>17</v>
+      </c>
+      <c r="D357" t="s">
+        <v>14</v>
+      </c>
+      <c r="E357" t="s">
+        <v>10</v>
+      </c>
+      <c r="F357" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="s">
+        <v>149</v>
+      </c>
+      <c r="B358" t="s">
+        <v>87</v>
+      </c>
+      <c r="C358" t="s">
+        <v>17</v>
+      </c>
+      <c r="D358" t="s">
+        <v>14</v>
+      </c>
+      <c r="E358" t="s">
+        <v>12</v>
+      </c>
+      <c r="F358" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="s">
+        <v>149</v>
+      </c>
+      <c r="B359" t="s">
+        <v>87</v>
+      </c>
+      <c r="C359" t="s">
+        <v>17</v>
+      </c>
+      <c r="D359" t="s">
+        <v>14</v>
+      </c>
+      <c r="E359" t="s">
+        <v>13</v>
+      </c>
+      <c r="F359" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="s">
+        <v>149</v>
+      </c>
+      <c r="B360" t="s">
+        <v>87</v>
+      </c>
+      <c r="C360" t="s">
+        <v>151</v>
+      </c>
+      <c r="D360" t="s">
+        <v>9</v>
+      </c>
+      <c r="E360" t="s">
+        <v>10</v>
+      </c>
+      <c r="F360" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="s">
+        <v>149</v>
+      </c>
+      <c r="B361" t="s">
+        <v>87</v>
+      </c>
+      <c r="C361" t="s">
+        <v>151</v>
+      </c>
+      <c r="D361" t="s">
+        <v>9</v>
+      </c>
+      <c r="E361" t="s">
+        <v>12</v>
+      </c>
+      <c r="F361" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="s">
+        <v>149</v>
+      </c>
+      <c r="B362" t="s">
+        <v>87</v>
+      </c>
+      <c r="C362" t="s">
+        <v>151</v>
+      </c>
+      <c r="D362" t="s">
+        <v>9</v>
+      </c>
+      <c r="E362" t="s">
+        <v>13</v>
+      </c>
+      <c r="F362" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="s">
+        <v>149</v>
+      </c>
+      <c r="B363" t="s">
+        <v>87</v>
+      </c>
+      <c r="C363" t="s">
+        <v>151</v>
+      </c>
+      <c r="D363" t="s">
+        <v>14</v>
+      </c>
+      <c r="E363" t="s">
+        <v>10</v>
+      </c>
+      <c r="F363" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="s">
+        <v>149</v>
+      </c>
+      <c r="B364" t="s">
+        <v>87</v>
+      </c>
+      <c r="C364" t="s">
+        <v>151</v>
+      </c>
+      <c r="D364" t="s">
+        <v>14</v>
+      </c>
+      <c r="E364" t="s">
+        <v>12</v>
+      </c>
+      <c r="F364" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="s">
+        <v>149</v>
+      </c>
+      <c r="B365" t="s">
+        <v>87</v>
+      </c>
+      <c r="C365" t="s">
+        <v>151</v>
+      </c>
+      <c r="D365" t="s">
+        <v>14</v>
+      </c>
+      <c r="E365" t="s">
+        <v>13</v>
+      </c>
+      <c r="F365" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="s">
+        <v>149</v>
+      </c>
+      <c r="B366" t="s">
+        <v>159</v>
+      </c>
+      <c r="C366" t="s">
+        <v>160</v>
+      </c>
+      <c r="D366" t="s">
+        <v>9</v>
+      </c>
+      <c r="E366" t="s">
+        <v>10</v>
+      </c>
+      <c r="F366" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="s">
+        <v>149</v>
+      </c>
+      <c r="B367" t="s">
+        <v>159</v>
+      </c>
+      <c r="C367" t="s">
+        <v>160</v>
+      </c>
+      <c r="D367" t="s">
+        <v>9</v>
+      </c>
+      <c r="E367" t="s">
+        <v>12</v>
+      </c>
+      <c r="F367" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="s">
+        <v>149</v>
+      </c>
+      <c r="B368" t="s">
+        <v>159</v>
+      </c>
+      <c r="C368" t="s">
+        <v>160</v>
+      </c>
+      <c r="D368" t="s">
+        <v>9</v>
+      </c>
+      <c r="E368" t="s">
+        <v>13</v>
+      </c>
+      <c r="F368" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="s">
+        <v>149</v>
+      </c>
+      <c r="B369" t="s">
+        <v>159</v>
+      </c>
+      <c r="C369" t="s">
+        <v>160</v>
+      </c>
+      <c r="D369" t="s">
+        <v>14</v>
+      </c>
+      <c r="E369" t="s">
+        <v>10</v>
+      </c>
+      <c r="F369" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="s">
+        <v>149</v>
+      </c>
+      <c r="B370" t="s">
+        <v>159</v>
+      </c>
+      <c r="C370" t="s">
+        <v>160</v>
+      </c>
+      <c r="D370" t="s">
+        <v>14</v>
+      </c>
+      <c r="E370" t="s">
+        <v>12</v>
+      </c>
+      <c r="F370" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="s">
+        <v>149</v>
+      </c>
+      <c r="B371" t="s">
+        <v>159</v>
+      </c>
+      <c r="C371" t="s">
+        <v>160</v>
+      </c>
+      <c r="D371" t="s">
+        <v>14</v>
+      </c>
+      <c r="E371" t="s">
+        <v>13</v>
+      </c>
+      <c r="F371" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="s">
+        <v>149</v>
+      </c>
+      <c r="B372" t="s">
+        <v>159</v>
+      </c>
+      <c r="C372" t="s">
+        <v>162</v>
+      </c>
+      <c r="D372" t="s">
+        <v>9</v>
+      </c>
+      <c r="E372" t="s">
+        <v>10</v>
+      </c>
+      <c r="F372" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="s">
+        <v>149</v>
+      </c>
+      <c r="B373" t="s">
+        <v>159</v>
+      </c>
+      <c r="C373" t="s">
+        <v>162</v>
+      </c>
+      <c r="D373" t="s">
+        <v>9</v>
+      </c>
+      <c r="E373" t="s">
+        <v>12</v>
+      </c>
+      <c r="F373" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="s">
+        <v>149</v>
+      </c>
+      <c r="B374" t="s">
+        <v>159</v>
+      </c>
+      <c r="C374" t="s">
+        <v>162</v>
+      </c>
+      <c r="D374" t="s">
+        <v>9</v>
+      </c>
+      <c r="E374" t="s">
+        <v>13</v>
+      </c>
+      <c r="F374" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="s">
+        <v>149</v>
+      </c>
+      <c r="B375" t="s">
+        <v>159</v>
+      </c>
+      <c r="C375" t="s">
+        <v>162</v>
+      </c>
+      <c r="D375" t="s">
+        <v>14</v>
+      </c>
+      <c r="E375" t="s">
+        <v>10</v>
+      </c>
+      <c r="F375" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="s">
+        <v>149</v>
+      </c>
+      <c r="B376" t="s">
+        <v>159</v>
+      </c>
+      <c r="C376" t="s">
+        <v>162</v>
+      </c>
+      <c r="D376" t="s">
+        <v>14</v>
+      </c>
+      <c r="E376" t="s">
+        <v>12</v>
+      </c>
+      <c r="F376" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="s">
+        <v>149</v>
+      </c>
+      <c r="B377" t="s">
+        <v>159</v>
+      </c>
+      <c r="C377" t="s">
+        <v>162</v>
+      </c>
+      <c r="D377" t="s">
+        <v>14</v>
+      </c>
+      <c r="E377" t="s">
+        <v>13</v>
+      </c>
+      <c r="F377" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="s">
+        <v>149</v>
+      </c>
+      <c r="B378" t="s">
+        <v>159</v>
+      </c>
+      <c r="C378" t="s">
+        <v>164</v>
+      </c>
+      <c r="D378" t="s">
+        <v>9</v>
+      </c>
+      <c r="E378" t="s">
+        <v>10</v>
+      </c>
+      <c r="F378" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="s">
+        <v>149</v>
+      </c>
+      <c r="B379" t="s">
+        <v>159</v>
+      </c>
+      <c r="C379" t="s">
+        <v>164</v>
+      </c>
+      <c r="D379" t="s">
+        <v>9</v>
+      </c>
+      <c r="E379" t="s">
+        <v>12</v>
+      </c>
+      <c r="F379" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="s">
+        <v>149</v>
+      </c>
+      <c r="B380" t="s">
+        <v>159</v>
+      </c>
+      <c r="C380" t="s">
+        <v>164</v>
+      </c>
+      <c r="D380" t="s">
+        <v>9</v>
+      </c>
+      <c r="E380" t="s">
+        <v>13</v>
+      </c>
+      <c r="F380" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="s">
+        <v>149</v>
+      </c>
+      <c r="B381" t="s">
+        <v>159</v>
+      </c>
+      <c r="C381" t="s">
+        <v>164</v>
+      </c>
+      <c r="D381" t="s">
+        <v>14</v>
+      </c>
+      <c r="E381" t="s">
+        <v>10</v>
+      </c>
+      <c r="F381" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="s">
+        <v>149</v>
+      </c>
+      <c r="B382" t="s">
+        <v>159</v>
+      </c>
+      <c r="C382" t="s">
+        <v>164</v>
+      </c>
+      <c r="D382" t="s">
+        <v>14</v>
+      </c>
+      <c r="E382" t="s">
+        <v>12</v>
+      </c>
+      <c r="F382" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="s">
+        <v>149</v>
+      </c>
+      <c r="B383" t="s">
+        <v>159</v>
+      </c>
+      <c r="C383" t="s">
+        <v>164</v>
+      </c>
+      <c r="D383" t="s">
+        <v>14</v>
+      </c>
+      <c r="E383" t="s">
+        <v>13</v>
+      </c>
+      <c r="F383" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="s">
+        <v>166</v>
+      </c>
+      <c r="B384" t="s">
+        <v>85</v>
+      </c>
+      <c r="C384" t="s">
+        <v>92</v>
+      </c>
+      <c r="D384" t="s">
+        <v>9</v>
+      </c>
+      <c r="E384" t="s">
+        <v>10</v>
+      </c>
+      <c r="F384" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="s">
+        <v>166</v>
+      </c>
+      <c r="B385" t="s">
+        <v>85</v>
+      </c>
+      <c r="C385" t="s">
+        <v>92</v>
+      </c>
+      <c r="D385" t="s">
+        <v>14</v>
+      </c>
+      <c r="E385" t="s">
+        <v>10</v>
+      </c>
+      <c r="F385" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="s">
+        <v>166</v>
+      </c>
+      <c r="B386" t="s">
+        <v>85</v>
+      </c>
+      <c r="C386" t="s">
+        <v>23</v>
+      </c>
+      <c r="D386" t="s">
+        <v>9</v>
+      </c>
+      <c r="E386" t="s">
+        <v>10</v>
+      </c>
+      <c r="F386" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="s">
+        <v>166</v>
+      </c>
+      <c r="B387" t="s">
+        <v>87</v>
+      </c>
+      <c r="C387" t="s">
+        <v>88</v>
+      </c>
+      <c r="D387" t="s">
+        <v>9</v>
+      </c>
+      <c r="E387" t="s">
+        <v>10</v>
+      </c>
+      <c r="F387" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="s">
+        <v>166</v>
+      </c>
+      <c r="B388" t="s">
+        <v>87</v>
+      </c>
+      <c r="C388" t="s">
+        <v>88</v>
+      </c>
+      <c r="D388" t="s">
+        <v>9</v>
+      </c>
+      <c r="E388" t="s">
+        <v>12</v>
+      </c>
+      <c r="F388" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="s">
+        <v>166</v>
+      </c>
+      <c r="B389" t="s">
+        <v>87</v>
+      </c>
+      <c r="C389" t="s">
+        <v>88</v>
+      </c>
+      <c r="D389" t="s">
+        <v>9</v>
+      </c>
+      <c r="E389" t="s">
+        <v>13</v>
+      </c>
+      <c r="F389" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="s">
+        <v>166</v>
+      </c>
+      <c r="B390" t="s">
+        <v>87</v>
+      </c>
+      <c r="C390" t="s">
+        <v>90</v>
+      </c>
+      <c r="D390" t="s">
+        <v>9</v>
+      </c>
+      <c r="E390" t="s">
+        <v>10</v>
+      </c>
+      <c r="F390" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="s">
+        <v>166</v>
+      </c>
+      <c r="B391" t="s">
+        <v>87</v>
+      </c>
+      <c r="C391" t="s">
+        <v>90</v>
+      </c>
+      <c r="D391" t="s">
+        <v>9</v>
+      </c>
+      <c r="E391" t="s">
+        <v>12</v>
+      </c>
+      <c r="F391" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="s">
+        <v>166</v>
+      </c>
+      <c r="B392" t="s">
+        <v>87</v>
+      </c>
+      <c r="C392" t="s">
+        <v>90</v>
+      </c>
+      <c r="D392" t="s">
+        <v>9</v>
+      </c>
+      <c r="E392" t="s">
+        <v>13</v>
+      </c>
+      <c r="F392" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="s">
+        <v>166</v>
+      </c>
+      <c r="B393" t="s">
+        <v>87</v>
+      </c>
+      <c r="C393" t="s">
+        <v>90</v>
+      </c>
+      <c r="D393" t="s">
+        <v>14</v>
+      </c>
+      <c r="E393" t="s">
+        <v>10</v>
+      </c>
+      <c r="F393" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="s">
+        <v>166</v>
+      </c>
+      <c r="B394" t="s">
+        <v>87</v>
+      </c>
+      <c r="C394" t="s">
+        <v>90</v>
+      </c>
+      <c r="D394" t="s">
+        <v>14</v>
+      </c>
+      <c r="E394" t="s">
+        <v>12</v>
+      </c>
+      <c r="F394" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="s">
+        <v>166</v>
+      </c>
+      <c r="B395" t="s">
+        <v>87</v>
+      </c>
+      <c r="C395" t="s">
+        <v>90</v>
+      </c>
+      <c r="D395" t="s">
+        <v>14</v>
+      </c>
+      <c r="E395" t="s">
+        <v>13</v>
+      </c>
+      <c r="F395" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="s">
+        <v>166</v>
+      </c>
+      <c r="B396" t="s">
+        <v>87</v>
+      </c>
+      <c r="C396" t="s">
+        <v>92</v>
+      </c>
+      <c r="D396" t="s">
+        <v>9</v>
+      </c>
+      <c r="E396" t="s">
+        <v>10</v>
+      </c>
+      <c r="F396" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="s">
+        <v>166</v>
+      </c>
+      <c r="B397" t="s">
+        <v>87</v>
+      </c>
+      <c r="C397" t="s">
+        <v>92</v>
+      </c>
+      <c r="D397" t="s">
+        <v>9</v>
+      </c>
+      <c r="E397" t="s">
+        <v>12</v>
+      </c>
+      <c r="F397" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="s">
+        <v>166</v>
+      </c>
+      <c r="B398" t="s">
+        <v>87</v>
+      </c>
+      <c r="C398" t="s">
+        <v>92</v>
+      </c>
+      <c r="D398" t="s">
+        <v>9</v>
+      </c>
+      <c r="E398" t="s">
+        <v>13</v>
+      </c>
+      <c r="F398" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="s">
+        <v>166</v>
+      </c>
+      <c r="B399" t="s">
+        <v>87</v>
+      </c>
+      <c r="C399" t="s">
+        <v>92</v>
+      </c>
+      <c r="D399" t="s">
+        <v>14</v>
+      </c>
+      <c r="E399" t="s">
+        <v>10</v>
+      </c>
+      <c r="F399" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="s">
+        <v>166</v>
+      </c>
+      <c r="B400" t="s">
+        <v>87</v>
+      </c>
+      <c r="C400" t="s">
+        <v>92</v>
+      </c>
+      <c r="D400" t="s">
+        <v>14</v>
+      </c>
+      <c r="E400" t="s">
+        <v>12</v>
+      </c>
+      <c r="F400" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="s">
+        <v>166</v>
+      </c>
+      <c r="B401" t="s">
+        <v>87</v>
+      </c>
+      <c r="C401" t="s">
+        <v>92</v>
+      </c>
+      <c r="D401" t="s">
+        <v>14</v>
+      </c>
+      <c r="E401" t="s">
+        <v>13</v>
+      </c>
+      <c r="F401" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="s">
+        <v>166</v>
+      </c>
+      <c r="B402" t="s">
+        <v>87</v>
+      </c>
+      <c r="C402" t="s">
+        <v>23</v>
+      </c>
+      <c r="D402" t="s">
+        <v>9</v>
+      </c>
+      <c r="E402" t="s">
+        <v>10</v>
+      </c>
+      <c r="F402" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="s">
+        <v>166</v>
+      </c>
+      <c r="B403" t="s">
+        <v>87</v>
+      </c>
+      <c r="C403" t="s">
+        <v>23</v>
+      </c>
+      <c r="D403" t="s">
+        <v>9</v>
+      </c>
+      <c r="E403" t="s">
+        <v>12</v>
+      </c>
+      <c r="F403" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="s">
+        <v>166</v>
+      </c>
+      <c r="B404" t="s">
+        <v>87</v>
+      </c>
+      <c r="C404" t="s">
+        <v>23</v>
+      </c>
+      <c r="D404" t="s">
+        <v>9</v>
+      </c>
+      <c r="E404" t="s">
+        <v>13</v>
+      </c>
+      <c r="F404" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="s">
+        <v>173</v>
+      </c>
+      <c r="B405" t="s">
+        <v>174</v>
+      </c>
+      <c r="C405" t="s">
+        <v>52</v>
+      </c>
+      <c r="D405" t="s">
+        <v>9</v>
+      </c>
+      <c r="E405" t="s">
+        <v>10</v>
+      </c>
+      <c r="F405" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="s">
+        <v>173</v>
+      </c>
+      <c r="B406" t="s">
+        <v>174</v>
+      </c>
+      <c r="C406" t="s">
+        <v>52</v>
+      </c>
+      <c r="D406" t="s">
+        <v>9</v>
+      </c>
+      <c r="E406" t="s">
+        <v>12</v>
+      </c>
+      <c r="F406" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="s">
+        <v>173</v>
+      </c>
+      <c r="B407" t="s">
+        <v>174</v>
+      </c>
+      <c r="C407" t="s">
+        <v>52</v>
+      </c>
+      <c r="D407" t="s">
+        <v>9</v>
+      </c>
+      <c r="E407" t="s">
+        <v>13</v>
+      </c>
+      <c r="F407" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="s">
+        <v>173</v>
+      </c>
+      <c r="B408" t="s">
+        <v>174</v>
+      </c>
+      <c r="C408" t="s">
+        <v>52</v>
+      </c>
+      <c r="D408" t="s">
+        <v>14</v>
+      </c>
+      <c r="E408" t="s">
+        <v>10</v>
+      </c>
+      <c r="F408" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="s">
+        <v>173</v>
+      </c>
+      <c r="B409" t="s">
+        <v>174</v>
+      </c>
+      <c r="C409" t="s">
+        <v>52</v>
+      </c>
+      <c r="D409" t="s">
+        <v>14</v>
+      </c>
+      <c r="E409" t="s">
+        <v>12</v>
+      </c>
+      <c r="F409" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="s">
+        <v>173</v>
+      </c>
+      <c r="B410" t="s">
+        <v>174</v>
+      </c>
+      <c r="C410" t="s">
+        <v>52</v>
+      </c>
+      <c r="D410" t="s">
+        <v>14</v>
+      </c>
+      <c r="E410" t="s">
+        <v>13</v>
+      </c>
+      <c r="F410" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="s">
+        <v>173</v>
+      </c>
+      <c r="B411" t="s">
+        <v>176</v>
+      </c>
+      <c r="C411" t="s">
+        <v>52</v>
+      </c>
+      <c r="D411" t="s">
+        <v>9</v>
+      </c>
+      <c r="E411" t="s">
+        <v>10</v>
+      </c>
+      <c r="F411" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="s">
+        <v>173</v>
+      </c>
+      <c r="B412" t="s">
+        <v>176</v>
+      </c>
+      <c r="C412" t="s">
+        <v>52</v>
+      </c>
+      <c r="D412" t="s">
+        <v>9</v>
+      </c>
+      <c r="E412" t="s">
+        <v>12</v>
+      </c>
+      <c r="F412" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="s">
+        <v>173</v>
+      </c>
+      <c r="B413" t="s">
+        <v>176</v>
+      </c>
+      <c r="C413" t="s">
+        <v>52</v>
+      </c>
+      <c r="D413" t="s">
+        <v>9</v>
+      </c>
+      <c r="E413" t="s">
+        <v>13</v>
+      </c>
+      <c r="F413" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="s">
+        <v>173</v>
+      </c>
+      <c r="B414" t="s">
+        <v>176</v>
+      </c>
+      <c r="C414" t="s">
+        <v>52</v>
+      </c>
+      <c r="D414" t="s">
+        <v>14</v>
+      </c>
+      <c r="E414" t="s">
+        <v>10</v>
+      </c>
+      <c r="F414" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="s">
+        <v>173</v>
+      </c>
+      <c r="B415" t="s">
+        <v>176</v>
+      </c>
+      <c r="C415" t="s">
+        <v>52</v>
+      </c>
+      <c r="D415" t="s">
+        <v>14</v>
+      </c>
+      <c r="E415" t="s">
+        <v>12</v>
+      </c>
+      <c r="F415" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="s">
+        <v>173</v>
+      </c>
+      <c r="B416" t="s">
+        <v>176</v>
+      </c>
+      <c r="C416" t="s">
+        <v>52</v>
+      </c>
+      <c r="D416" t="s">
+        <v>14</v>
+      </c>
+      <c r="E416" t="s">
+        <v>13</v>
+      </c>
+      <c r="F416" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="s">
+        <v>173</v>
+      </c>
+      <c r="B417" t="s">
+        <v>178</v>
+      </c>
+      <c r="C417" t="s">
+        <v>52</v>
+      </c>
+      <c r="D417" t="s">
+        <v>9</v>
+      </c>
+      <c r="E417" t="s">
+        <v>10</v>
+      </c>
+      <c r="F417" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="s">
+        <v>173</v>
+      </c>
+      <c r="B418" t="s">
+        <v>178</v>
+      </c>
+      <c r="C418" t="s">
+        <v>52</v>
+      </c>
+      <c r="D418" t="s">
+        <v>9</v>
+      </c>
+      <c r="E418" t="s">
+        <v>12</v>
+      </c>
+      <c r="F418" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="s">
+        <v>173</v>
+      </c>
+      <c r="B419" t="s">
+        <v>178</v>
+      </c>
+      <c r="C419" t="s">
+        <v>52</v>
+      </c>
+      <c r="D419" t="s">
+        <v>9</v>
+      </c>
+      <c r="E419" t="s">
+        <v>13</v>
+      </c>
+      <c r="F419" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="s">
+        <v>173</v>
+      </c>
+      <c r="B420" t="s">
+        <v>178</v>
+      </c>
+      <c r="C420" t="s">
+        <v>52</v>
+      </c>
+      <c r="D420" t="s">
+        <v>14</v>
+      </c>
+      <c r="E420" t="s">
+        <v>10</v>
+      </c>
+      <c r="F420" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="s">
+        <v>173</v>
+      </c>
+      <c r="B421" t="s">
+        <v>178</v>
+      </c>
+      <c r="C421" t="s">
+        <v>52</v>
+      </c>
+      <c r="D421" t="s">
+        <v>14</v>
+      </c>
+      <c r="E421" t="s">
+        <v>12</v>
+      </c>
+      <c r="F421" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="s">
+        <v>173</v>
+      </c>
+      <c r="B422" t="s">
+        <v>178</v>
+      </c>
+      <c r="C422" t="s">
+        <v>52</v>
+      </c>
+      <c r="D422" t="s">
+        <v>14</v>
+      </c>
+      <c r="E422" t="s">
+        <v>13</v>
+      </c>
+      <c r="F422" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="s">
+        <v>173</v>
+      </c>
+      <c r="B423" t="s">
+        <v>180</v>
+      </c>
+      <c r="C423" t="s">
+        <v>52</v>
+      </c>
+      <c r="D423" t="s">
+        <v>9</v>
+      </c>
+      <c r="E423" t="s">
+        <v>10</v>
+      </c>
+      <c r="F423" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="s">
+        <v>173</v>
+      </c>
+      <c r="B424" t="s">
+        <v>180</v>
+      </c>
+      <c r="C424" t="s">
+        <v>52</v>
+      </c>
+      <c r="D424" t="s">
+        <v>9</v>
+      </c>
+      <c r="E424" t="s">
+        <v>12</v>
+      </c>
+      <c r="F424" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="s">
+        <v>173</v>
+      </c>
+      <c r="B425" t="s">
+        <v>180</v>
+      </c>
+      <c r="C425" t="s">
+        <v>52</v>
+      </c>
+      <c r="D425" t="s">
+        <v>9</v>
+      </c>
+      <c r="E425" t="s">
+        <v>13</v>
+      </c>
+      <c r="F425" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="s">
+        <v>173</v>
+      </c>
+      <c r="B426" t="s">
+        <v>180</v>
+      </c>
+      <c r="C426" t="s">
+        <v>52</v>
+      </c>
+      <c r="D426" t="s">
+        <v>14</v>
+      </c>
+      <c r="E426" t="s">
+        <v>10</v>
+      </c>
+      <c r="F426" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="s">
+        <v>173</v>
+      </c>
+      <c r="B427" t="s">
+        <v>180</v>
+      </c>
+      <c r="C427" t="s">
+        <v>52</v>
+      </c>
+      <c r="D427" t="s">
+        <v>14</v>
+      </c>
+      <c r="E427" t="s">
+        <v>12</v>
+      </c>
+      <c r="F427" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="s">
+        <v>173</v>
+      </c>
+      <c r="B428" t="s">
+        <v>180</v>
+      </c>
+      <c r="C428" t="s">
+        <v>52</v>
+      </c>
+      <c r="D428" t="s">
+        <v>14</v>
+      </c>
+      <c r="E428" t="s">
+        <v>13</v>
+      </c>
+      <c r="F428" t="s">
+        <v>181</v>
       </c>
     </row>
   </sheetData>
